--- a/HE_Database_PRO_FINAL.xlsx
+++ b/HE_Database_PRO_FINAL.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E726E0F4-49FC-4350-8DE0-2061B19E1F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FC6119-94D0-4A17-895B-F5383C571064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="1" r:id="rId1"/>
     <sheet name="TIME" sheetId="2" r:id="rId2"/>
-    <sheet name="PRICE_UNIT" sheetId="3" r:id="rId3"/>
+    <sheet name="PRICE_MASTER" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/HE_Database_PRO_FINAL.xlsx
+++ b/HE_Database_PRO_FINAL.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAA38EB-7561-4922-A512-AE29CC3F071B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79BD917-C904-4BDC-91D8-5C3FE4DB46B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Spec" sheetId="7" r:id="rId1"/>
-    <sheet name="Time" sheetId="3" r:id="rId2"/>
+    <sheet name="SPEC" sheetId="7" r:id="rId1"/>
+    <sheet name="TIME" sheetId="3" r:id="rId2"/>
     <sheet name="PRICE_MASTER" sheetId="9" r:id="rId3"/>
   </sheets>
   <externalReferences>
@@ -5779,9 +5779,6 @@
     <t>Tube_Qty</t>
   </si>
   <si>
-    <t>Description2</t>
-  </si>
-  <si>
     <t>2E-2507</t>
   </si>
   <si>
@@ -6497,6 +6494,9 @@
   </si>
   <si>
     <t>#</t>
+  </si>
+  <si>
+    <t>Tube Spec</t>
   </si>
 </sst>
 </file>
@@ -6505,7 +6505,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -6667,7 +6667,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -7034,7 +7034,7 @@
     <tableColumn id="11" xr3:uid="{9CF69EB9-0910-4132-AAED-0EA35A0F1586}" name="Mat.Tube" dataDxfId="3"/>
     <tableColumn id="12" xr3:uid="{3B833DAF-8FDC-4EBF-940A-29A9353119DA}" name="Size.Shell" dataDxfId="2"/>
     <tableColumn id="13" xr3:uid="{905FAE86-0F80-497A-A381-2CAAC5E7F799}" name="tr. " dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{AF581786-BA51-4270-919B-78BB99D6A475}" name="Description2" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{AF581786-BA51-4270-919B-78BB99D6A475}" name="Tube Spec" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{0ADA4734-C09E-4472-8FE9-88E06CCD731E}" name="Tube_OD"/>
     <tableColumn id="27" xr3:uid="{8EA71C05-F27B-4F84-B73B-41A2FC4950B7}" name="Tube_Thk"/>
     <tableColumn id="17" xr3:uid="{FE2E1669-B0C9-4049-B58F-A17D18292C5C}" name="Tube_Length_mm"/>
@@ -7339,7 +7339,7 @@
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="2"/>
+    <col min="3" max="3" width="65.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="13" style="2" customWidth="1"/>
     <col min="6" max="6" width="11.140625" style="2" bestFit="1" customWidth="1"/>
@@ -7365,7 +7365,7 @@
       <c r="B1" t="s">
         <v>1643</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -7399,13 +7399,13 @@
         <v>2</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>1893</v>
+        <v>2132</v>
       </c>
       <c r="O1" s="15" t="s">
         <v>1890</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>1891</v>
@@ -7464,7 +7464,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="O2">
         <v>19</v>
@@ -7529,7 +7529,7 @@
         <v>86</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="O3">
         <v>19</v>
@@ -7594,7 +7594,7 @@
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="O4">
         <v>19</v>
@@ -7724,7 +7724,7 @@
         <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="O6">
         <v>19</v>
@@ -7789,7 +7789,7 @@
         <v>86</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="O7">
         <v>19</v>
@@ -7854,7 +7854,7 @@
         <v>177</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="O8">
         <v>19</v>
@@ -8374,7 +8374,7 @@
         <v>213</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="O16">
         <v>19</v>
@@ -10285,7 +10285,7 @@
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="16" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B46" t="s">
         <v>1759</v>
@@ -10350,7 +10350,7 @@
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="16" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B47" t="s">
         <v>1759</v>
@@ -10415,7 +10415,7 @@
     </row>
     <row r="48" spans="1:21">
       <c r="A48" s="16" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B48" t="s">
         <v>1759</v>
@@ -10454,7 +10454,7 @@
         <v>11</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="O48">
         <v>19</v>
@@ -10740,7 +10740,7 @@
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="16" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B53" t="s">
         <v>1759</v>
@@ -10861,7 +10861,7 @@
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="16" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B55" t="s">
         <v>1759</v>
@@ -10900,7 +10900,7 @@
         <v>330</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="O55">
         <v>19</v>
@@ -10926,7 +10926,7 @@
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="16" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B56" t="s">
         <v>1759</v>
@@ -10965,7 +10965,7 @@
         <v>11</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="O56">
         <v>19</v>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="16" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B57" t="s">
         <v>1759</v>
@@ -11027,7 +11027,7 @@
         <v>192</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="O57">
         <v>19</v>
@@ -11053,7 +11053,7 @@
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="16" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B58" t="s">
         <v>1759</v>
@@ -11092,7 +11092,7 @@
         <v>5</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O58">
         <v>19</v>
@@ -11118,7 +11118,7 @@
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="16" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B59" t="s">
         <v>1759</v>
@@ -11157,7 +11157,7 @@
         <v>5</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O59">
         <v>19</v>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="16" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B60" t="s">
         <v>1759</v>
@@ -11222,7 +11222,7 @@
         <v>13</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="O60">
         <v>19</v>
@@ -11248,7 +11248,7 @@
     </row>
     <row r="61" spans="1:21">
       <c r="A61" s="16" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B61" t="s">
         <v>1759</v>
@@ -11313,7 +11313,7 @@
     </row>
     <row r="62" spans="1:21">
       <c r="A62" s="16" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B62" t="s">
         <v>1759</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="63" spans="1:21">
       <c r="A63" s="16" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B63" t="s">
         <v>1759</v>
@@ -11443,7 +11443,7 @@
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="16" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B64" t="s">
         <v>1759</v>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="16" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B65" t="s">
         <v>1759</v>
@@ -11547,7 +11547,7 @@
         <v>11</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="O65">
         <v>19</v>
@@ -11573,7 +11573,7 @@
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="16" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B66" t="s">
         <v>1759</v>
@@ -11612,7 +11612,7 @@
         <v>11</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="O66">
         <v>19</v>
@@ -11638,7 +11638,7 @@
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="16" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B67" t="s">
         <v>1759</v>
@@ -11677,7 +11677,7 @@
         <v>11</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="O67">
         <v>19</v>
@@ -11703,7 +11703,7 @@
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="16" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B68" t="s">
         <v>1759</v>
@@ -11742,7 +11742,7 @@
         <v>11</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="O68">
         <v>19</v>
@@ -11768,7 +11768,7 @@
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="16" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B69" t="s">
         <v>1759</v>
@@ -11807,7 +11807,7 @@
         <v>13</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="O69">
         <v>19</v>
@@ -11833,7 +11833,7 @@
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="16" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B70" t="s">
         <v>1759</v>
@@ -11872,7 +11872,7 @@
         <v>370</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="O70">
         <v>1</v>
@@ -11898,7 +11898,7 @@
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="16" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B71" t="s">
         <v>1759</v>
@@ -11937,7 +11937,7 @@
         <v>380</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="O71">
         <v>33</v>
@@ -11963,7 +11963,7 @@
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="16" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B72" t="s">
         <v>1759</v>
@@ -12002,7 +12002,7 @@
         <v>5</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="O72">
         <v>31</v>
@@ -12028,7 +12028,7 @@
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="16" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B73" t="s">
         <v>1759</v>
@@ -12067,7 +12067,7 @@
         <v>5</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="O73">
         <v>31</v>
@@ -12093,7 +12093,7 @@
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="16" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B74" t="s">
         <v>1759</v>
@@ -12132,7 +12132,7 @@
         <v>5</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="O74">
         <v>31</v>
@@ -12223,7 +12223,7 @@
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="16" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B76" t="s">
         <v>1759</v>
@@ -12285,7 +12285,7 @@
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="16" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B77" t="s">
         <v>1644</v>
@@ -12350,7 +12350,7 @@
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="16" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B78" t="s">
         <v>1759</v>
@@ -12409,7 +12409,7 @@
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="16" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B79" t="s">
         <v>1759</v>
@@ -12474,7 +12474,7 @@
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="16" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B80" t="s">
         <v>1759</v>
@@ -12539,7 +12539,7 @@
     </row>
     <row r="81" spans="1:21">
       <c r="A81" s="16" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B81" t="s">
         <v>1759</v>
@@ -12604,7 +12604,7 @@
     </row>
     <row r="82" spans="1:21">
       <c r="A82" s="16" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B82" t="s">
         <v>1759</v>
@@ -12734,7 +12734,7 @@
     </row>
     <row r="84" spans="1:21">
       <c r="A84" s="16" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B84" t="s">
         <v>1759</v>
@@ -12799,7 +12799,7 @@
     </row>
     <row r="85" spans="1:21">
       <c r="A85" s="16" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B85" t="s">
         <v>1644</v>
@@ -12864,7 +12864,7 @@
     </row>
     <row r="86" spans="1:21">
       <c r="A86" s="16" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B86" t="s">
         <v>1759</v>
@@ -12923,7 +12923,7 @@
     </row>
     <row r="87" spans="1:21">
       <c r="A87" s="16" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B87" t="s">
         <v>1759</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="88" spans="1:21">
       <c r="A88" s="16" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B88" t="s">
         <v>1759</v>
@@ -13053,7 +13053,7 @@
     </row>
     <row r="89" spans="1:21">
       <c r="A89" s="16" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B89" t="s">
         <v>1759</v>
@@ -13118,7 +13118,7 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="16" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B90" t="s">
         <v>1759</v>
@@ -13183,7 +13183,7 @@
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="16" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B91" t="s">
         <v>1759</v>
@@ -13236,7 +13236,7 @@
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="16" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B92" t="s">
         <v>1759</v>
@@ -13301,7 +13301,7 @@
     </row>
     <row r="93" spans="1:21">
       <c r="A93" s="16" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B93" t="s">
         <v>1759</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="94" spans="1:21">
       <c r="A94" s="16" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B94" t="s">
         <v>1759</v>
@@ -13431,7 +13431,7 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="16" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B95" t="s">
         <v>1644</v>
@@ -13496,7 +13496,7 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="16" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B96" t="s">
         <v>1759</v>
@@ -13561,7 +13561,7 @@
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="16" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B97" t="s">
         <v>1759</v>
@@ -13626,7 +13626,7 @@
     </row>
     <row r="98" spans="1:21">
       <c r="A98" s="16" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B98" t="s">
         <v>1759</v>
@@ -13691,7 +13691,7 @@
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="16" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B99" t="s">
         <v>1759</v>
@@ -13756,7 +13756,7 @@
     </row>
     <row r="100" spans="1:21">
       <c r="A100" s="16" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B100" t="s">
         <v>1759</v>
@@ -13795,7 +13795,7 @@
         <v>303</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="O100">
         <v>19</v>
@@ -13821,7 +13821,7 @@
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="16" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B101" t="s">
         <v>1759</v>
@@ -13860,7 +13860,7 @@
         <v>11</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="O101">
         <v>19</v>
@@ -13886,7 +13886,7 @@
     </row>
     <row r="102" spans="1:21">
       <c r="A102" s="16" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B102" t="s">
         <v>1759</v>
@@ -13925,7 +13925,7 @@
         <v>5</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="O102">
         <v>19</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="103" spans="1:21">
       <c r="A103" s="16" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B103" t="s">
         <v>1759</v>
@@ -13990,7 +13990,7 @@
         <v>11</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="O103">
         <v>19</v>
@@ -14016,7 +14016,7 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="16" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B104" t="s">
         <v>1759</v>
@@ -14055,10 +14055,10 @@
         <v>512</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="O104" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P104">
         <v>2.77</v>
@@ -14081,7 +14081,7 @@
     </row>
     <row r="105" spans="1:21">
       <c r="A105" s="16" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B105" t="s">
         <v>1759</v>
@@ -14120,10 +14120,10 @@
         <v>512</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="O105" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P105">
         <v>2.77</v>
@@ -14146,7 +14146,7 @@
     </row>
     <row r="106" spans="1:21">
       <c r="A106" s="16" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B106" t="s">
         <v>1759</v>
@@ -14185,10 +14185,10 @@
         <v>512</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="O106" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P106">
         <v>2.77</v>
@@ -14211,7 +14211,7 @@
     </row>
     <row r="107" spans="1:21">
       <c r="A107" s="16" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B107" t="s">
         <v>1759</v>
@@ -14250,7 +14250,7 @@
         <v>297</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="O107">
         <v>19</v>
@@ -14276,7 +14276,7 @@
     </row>
     <row r="108" spans="1:21">
       <c r="A108" s="16" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B108" t="s">
         <v>1759</v>
@@ -14315,7 +14315,7 @@
         <v>297</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="O108">
         <v>19</v>
@@ -14341,7 +14341,7 @@
     </row>
     <row r="109" spans="1:21">
       <c r="A109" s="16" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B109" t="s">
         <v>1759</v>
@@ -14380,10 +14380,10 @@
         <v>297</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="O109" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P109">
         <v>2.11</v>
@@ -14406,7 +14406,7 @@
     </row>
     <row r="110" spans="1:21">
       <c r="A110" s="16" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B110" t="s">
         <v>1759</v>
@@ -14445,7 +14445,7 @@
         <v>13</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="O110">
         <v>19</v>
@@ -14471,7 +14471,7 @@
     </row>
     <row r="111" spans="1:21">
       <c r="A111" s="16" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B111" t="s">
         <v>1759</v>
@@ -14510,7 +14510,7 @@
         <v>13</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="O111">
         <v>25</v>
@@ -14536,7 +14536,7 @@
     </row>
     <row r="112" spans="1:21">
       <c r="A112" s="16" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B112" t="s">
         <v>1759</v>
@@ -14575,7 +14575,7 @@
         <v>13</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="O112">
         <v>25</v>
@@ -14601,7 +14601,7 @@
     </row>
     <row r="113" spans="1:21">
       <c r="A113" s="16" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B113" t="s">
         <v>1759</v>
@@ -14640,7 +14640,7 @@
         <v>65</v>
       </c>
       <c r="N113" s="34" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="O113">
         <v>19</v>
@@ -14666,7 +14666,7 @@
     </row>
     <row r="114" spans="1:21">
       <c r="A114" s="16" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B114" t="s">
         <v>1759</v>
@@ -14705,7 +14705,7 @@
         <v>11</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="O114">
         <v>19</v>
@@ -14731,7 +14731,7 @@
     </row>
     <row r="115" spans="1:21">
       <c r="A115" s="16" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B115" t="s">
         <v>1759</v>
@@ -14770,7 +14770,7 @@
         <v>53</v>
       </c>
       <c r="N115" s="34" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="O115">
         <v>19</v>
@@ -14796,7 +14796,7 @@
     </row>
     <row r="116" spans="1:21">
       <c r="A116" s="16" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B116" t="s">
         <v>1759</v>
@@ -14835,7 +14835,7 @@
         <v>5</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="O116">
         <v>19</v>
@@ -14861,7 +14861,7 @@
     </row>
     <row r="117" spans="1:21">
       <c r="A117" s="16" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B117" t="s">
         <v>1759</v>
@@ -14900,13 +14900,13 @@
         <v>11</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="O117">
         <v>3</v>
       </c>
       <c r="P117" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="Q117">
         <v>6000</v>
@@ -14926,7 +14926,7 @@
     </row>
     <row r="118" spans="1:21">
       <c r="A118" s="16" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B118" t="s">
         <v>1759</v>
@@ -14959,7 +14959,7 @@
         <v>561</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="O118">
         <v>19</v>
@@ -14985,7 +14985,7 @@
     </row>
     <row r="119" spans="1:21">
       <c r="A119" s="16" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B119" t="s">
         <v>1759</v>
@@ -15024,7 +15024,7 @@
         <v>71</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="O119">
         <v>19</v>
@@ -15050,7 +15050,7 @@
     </row>
     <row r="120" spans="1:21">
       <c r="A120" s="16" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B120" t="s">
         <v>1759</v>
@@ -15091,7 +15091,7 @@
     </row>
     <row r="121" spans="1:21">
       <c r="A121" s="16" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B121" t="s">
         <v>1759</v>
@@ -15132,7 +15132,7 @@
     </row>
     <row r="122" spans="1:21">
       <c r="A122" s="16" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="B122" t="s">
         <v>1759</v>
@@ -15141,12 +15141,12 @@
         <v>575</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="123" spans="1:21">
       <c r="A123" s="16" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B123" t="s">
         <v>1759</v>
@@ -15185,7 +15185,7 @@
         <v>11</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="O123">
         <v>25</v>
@@ -15211,7 +15211,7 @@
     </row>
     <row r="124" spans="1:21">
       <c r="A124" s="16" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B124" t="s">
         <v>1759</v>
@@ -15250,7 +15250,7 @@
         <v>11</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="O124">
         <v>19</v>
@@ -15315,7 +15315,7 @@
         <v>11</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="O125">
         <v>25</v>
@@ -15386,7 +15386,7 @@
         <v>19</v>
       </c>
       <c r="P126" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Q126">
         <v>3000</v>
@@ -15640,7 +15640,7 @@
         <v>2.5</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="O130">
         <v>1</v>
@@ -16912,7 +16912,7 @@
     </row>
     <row r="151" spans="1:21">
       <c r="A151" s="16" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B151" t="s">
         <v>1759</v>
@@ -16977,7 +16977,7 @@
     </row>
     <row r="152" spans="1:21">
       <c r="A152" s="16" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B152" t="s">
         <v>1759</v>
@@ -17042,7 +17042,7 @@
     </row>
     <row r="153" spans="1:21">
       <c r="A153" s="16" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B153" t="s">
         <v>1759</v>
@@ -17107,7 +17107,7 @@
     </row>
     <row r="154" spans="1:21">
       <c r="A154" s="16" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B154" t="s">
         <v>1759</v>
@@ -17172,7 +17172,7 @@
     </row>
     <row r="155" spans="1:21">
       <c r="A155" s="17" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="B155" t="s">
         <v>1759</v>
@@ -17237,7 +17237,7 @@
     </row>
     <row r="156" spans="1:21">
       <c r="A156" s="16" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B156" t="s">
         <v>1759</v>
@@ -17302,7 +17302,7 @@
     </row>
     <row r="157" spans="1:21">
       <c r="A157" s="16" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B157" t="s">
         <v>1759</v>
@@ -17367,7 +17367,7 @@
     </row>
     <row r="158" spans="1:21">
       <c r="A158" s="16" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B158" t="s">
         <v>1759</v>
@@ -17432,7 +17432,7 @@
     </row>
     <row r="159" spans="1:21">
       <c r="A159" s="16" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B159" t="s">
         <v>1759</v>
@@ -17497,7 +17497,7 @@
     </row>
     <row r="160" spans="1:21">
       <c r="A160" s="16" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B160" t="s">
         <v>1759</v>
@@ -17562,7 +17562,7 @@
     </row>
     <row r="161" spans="1:21">
       <c r="A161" s="16" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B161" t="s">
         <v>1759</v>
@@ -17627,7 +17627,7 @@
     </row>
     <row r="162" spans="1:21">
       <c r="A162" s="16" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="B162" t="s">
         <v>1759</v>
@@ -17692,7 +17692,7 @@
     </row>
     <row r="163" spans="1:21">
       <c r="A163" s="16" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B163" t="s">
         <v>1759</v>
@@ -17757,7 +17757,7 @@
     </row>
     <row r="164" spans="1:21">
       <c r="A164" s="16" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B164" t="s">
         <v>1759</v>
@@ -17952,7 +17952,7 @@
     </row>
     <row r="167" spans="1:21">
       <c r="A167" s="16" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B167" t="s">
         <v>1759</v>
@@ -18017,7 +18017,7 @@
     </row>
     <row r="168" spans="1:21">
       <c r="A168" s="16" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B168" t="s">
         <v>1759</v>
@@ -18082,7 +18082,7 @@
     </row>
     <row r="169" spans="1:21">
       <c r="A169" s="16" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B169" t="s">
         <v>1759</v>
@@ -18147,7 +18147,7 @@
     </row>
     <row r="170" spans="1:21">
       <c r="A170" s="16" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B170" t="s">
         <v>1759</v>
@@ -18212,7 +18212,7 @@
     </row>
     <row r="171" spans="1:21">
       <c r="A171" s="16" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B171" t="s">
         <v>1759</v>
@@ -18407,7 +18407,7 @@
     </row>
     <row r="174" spans="1:21">
       <c r="A174" s="16" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B174" t="s">
         <v>1759</v>
@@ -18472,7 +18472,7 @@
     </row>
     <row r="175" spans="1:21">
       <c r="A175" s="16" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B175" t="s">
         <v>1759</v>
@@ -18537,7 +18537,7 @@
     </row>
     <row r="176" spans="1:21">
       <c r="A176" s="16" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B176" t="s">
         <v>1759</v>
@@ -18602,7 +18602,7 @@
     </row>
     <row r="177" spans="1:21">
       <c r="A177" s="16" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B177" t="s">
         <v>1759</v>
@@ -18667,7 +18667,7 @@
     </row>
     <row r="178" spans="1:21">
       <c r="A178" s="16" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B178" t="s">
         <v>1759</v>
@@ -18732,7 +18732,7 @@
     </row>
     <row r="179" spans="1:21">
       <c r="A179" s="16" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B179" t="s">
         <v>1759</v>
@@ -18797,7 +18797,7 @@
     </row>
     <row r="180" spans="1:21">
       <c r="A180" s="16" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B180" t="s">
         <v>1759</v>
@@ -18862,7 +18862,7 @@
     </row>
     <row r="181" spans="1:21">
       <c r="A181" s="16" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B181" t="s">
         <v>1759</v>
@@ -18992,7 +18992,7 @@
     </row>
     <row r="183" spans="1:21">
       <c r="A183" s="16" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B183" t="s">
         <v>1759</v>
@@ -19057,7 +19057,7 @@
     </row>
     <row r="184" spans="1:21">
       <c r="A184" s="16" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B184" t="s">
         <v>1759</v>
@@ -19122,7 +19122,7 @@
     </row>
     <row r="185" spans="1:21">
       <c r="A185" s="16" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B185" t="s">
         <v>1759</v>
@@ -19187,7 +19187,7 @@
     </row>
     <row r="186" spans="1:21">
       <c r="A186" s="16" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B186" t="s">
         <v>1759</v>
@@ -19252,7 +19252,7 @@
     </row>
     <row r="187" spans="1:21">
       <c r="A187" s="16" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B187" t="s">
         <v>1759</v>
@@ -19317,7 +19317,7 @@
     </row>
     <row r="188" spans="1:21">
       <c r="A188" s="16" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B188" t="s">
         <v>1759</v>
@@ -19382,7 +19382,7 @@
     </row>
     <row r="189" spans="1:21">
       <c r="A189" s="16" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B189" t="s">
         <v>1759</v>
@@ -19447,7 +19447,7 @@
     </row>
     <row r="190" spans="1:21">
       <c r="A190" s="16" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B190" t="s">
         <v>1759</v>
@@ -19512,7 +19512,7 @@
     </row>
     <row r="191" spans="1:21">
       <c r="A191" s="16" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B191" t="s">
         <v>1759</v>
@@ -19577,7 +19577,7 @@
     </row>
     <row r="192" spans="1:21">
       <c r="A192" s="16" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B192" t="s">
         <v>1759</v>
@@ -19642,7 +19642,7 @@
     </row>
     <row r="193" spans="1:21">
       <c r="A193" s="16" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B193" t="s">
         <v>1759</v>
@@ -19707,7 +19707,7 @@
     </row>
     <row r="194" spans="1:21">
       <c r="A194" s="16" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B194" t="s">
         <v>1759</v>
@@ -19746,7 +19746,7 @@
         <v>2.5</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="O194">
         <v>1</v>
@@ -19772,7 +19772,7 @@
     </row>
     <row r="195" spans="1:21">
       <c r="A195" s="16" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B195" t="s">
         <v>1759</v>
@@ -19811,7 +19811,7 @@
         <v>2.5</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="O195">
         <v>1</v>
@@ -19837,7 +19837,7 @@
     </row>
     <row r="196" spans="1:21">
       <c r="A196" s="16" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B196" t="s">
         <v>1759</v>
@@ -19876,7 +19876,7 @@
         <v>2.5</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="O196">
         <v>1</v>
@@ -19902,7 +19902,7 @@
     </row>
     <row r="197" spans="1:21">
       <c r="A197" s="16" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B197" t="s">
         <v>1759</v>
@@ -19967,7 +19967,7 @@
     </row>
     <row r="198" spans="1:21">
       <c r="A198" s="16" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B198" t="s">
         <v>1759</v>
@@ -20032,7 +20032,7 @@
     </row>
     <row r="199" spans="1:21">
       <c r="A199" s="16" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B199" t="s">
         <v>1759</v>
@@ -20097,7 +20097,7 @@
     </row>
     <row r="200" spans="1:21">
       <c r="A200" s="16" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B200" t="s">
         <v>1759</v>
@@ -20162,7 +20162,7 @@
     </row>
     <row r="201" spans="1:21">
       <c r="A201" s="16" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B201" t="s">
         <v>1759</v>
@@ -20227,7 +20227,7 @@
     </row>
     <row r="202" spans="1:21">
       <c r="A202" s="16" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B202" t="s">
         <v>1759</v>
@@ -20292,7 +20292,7 @@
     </row>
     <row r="203" spans="1:21">
       <c r="A203" s="16" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B203" t="s">
         <v>1759</v>
@@ -20357,7 +20357,7 @@
     </row>
     <row r="204" spans="1:21">
       <c r="A204" s="16" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B204" t="s">
         <v>1759</v>
@@ -20422,7 +20422,7 @@
     </row>
     <row r="205" spans="1:21">
       <c r="A205" s="16" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B205" t="s">
         <v>1759</v>
@@ -20487,7 +20487,7 @@
     </row>
     <row r="206" spans="1:21">
       <c r="A206" s="16" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B206" t="s">
         <v>1759</v>
@@ -20552,7 +20552,7 @@
     </row>
     <row r="207" spans="1:21">
       <c r="A207" s="16" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B207" t="s">
         <v>1759</v>
@@ -20617,7 +20617,7 @@
     </row>
     <row r="208" spans="1:21">
       <c r="A208" s="16" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B208" t="s">
         <v>1759</v>
@@ -20682,7 +20682,7 @@
     </row>
     <row r="209" spans="1:21">
       <c r="A209" s="16" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B209" t="s">
         <v>1759</v>
@@ -20747,7 +20747,7 @@
     </row>
     <row r="210" spans="1:21">
       <c r="A210" s="16" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B210" t="s">
         <v>1759</v>
@@ -20758,7 +20758,7 @@
     </row>
     <row r="211" spans="1:21">
       <c r="A211" s="16" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B211" t="s">
         <v>1759</v>
@@ -20823,7 +20823,7 @@
     </row>
     <row r="212" spans="1:21">
       <c r="A212" s="16" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B212" t="s">
         <v>1759</v>
@@ -20888,7 +20888,7 @@
     </row>
     <row r="213" spans="1:21">
       <c r="A213" s="16" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B213" t="s">
         <v>1759</v>
@@ -20953,7 +20953,7 @@
     </row>
     <row r="214" spans="1:21">
       <c r="A214" s="16" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B214" t="s">
         <v>1759</v>
@@ -21018,7 +21018,7 @@
     </row>
     <row r="215" spans="1:21">
       <c r="A215" s="16" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B215" t="s">
         <v>1759</v>
@@ -21083,7 +21083,7 @@
     </row>
     <row r="216" spans="1:21">
       <c r="A216" s="16" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B216" t="s">
         <v>1759</v>
@@ -21122,7 +21122,7 @@
         <v>286</v>
       </c>
       <c r="N216" s="2" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="O216">
         <v>19</v>
@@ -21148,7 +21148,7 @@
     </row>
     <row r="217" spans="1:21">
       <c r="A217" s="16" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B217" t="s">
         <v>1759</v>
@@ -21213,7 +21213,7 @@
     </row>
     <row r="218" spans="1:21">
       <c r="A218" s="16" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B218" t="s">
         <v>1759</v>
@@ -21278,7 +21278,7 @@
     </row>
     <row r="219" spans="1:21">
       <c r="A219" s="16" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B219" t="s">
         <v>1759</v>
@@ -21343,7 +21343,7 @@
     </row>
     <row r="220" spans="1:21">
       <c r="A220" s="16" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B220" t="s">
         <v>1759</v>
@@ -21408,7 +21408,7 @@
     </row>
     <row r="221" spans="1:21">
       <c r="A221" s="16" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B221" t="s">
         <v>1759</v>
@@ -21473,7 +21473,7 @@
     </row>
     <row r="222" spans="1:21">
       <c r="A222" s="16" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B222" t="s">
         <v>1759</v>
@@ -21538,7 +21538,7 @@
     </row>
     <row r="223" spans="1:21">
       <c r="A223" s="16" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B223" t="s">
         <v>1759</v>
@@ -21603,7 +21603,7 @@
     </row>
     <row r="224" spans="1:21">
       <c r="A224" s="16" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B224" t="s">
         <v>1759</v>
@@ -21668,7 +21668,7 @@
     </row>
     <row r="225" spans="1:21">
       <c r="A225" s="16" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B225" t="s">
         <v>1759</v>
@@ -21733,7 +21733,7 @@
     </row>
     <row r="226" spans="1:21">
       <c r="A226" s="16" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B226" t="s">
         <v>1759</v>
@@ -21798,7 +21798,7 @@
     </row>
     <row r="227" spans="1:21">
       <c r="A227" s="16" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B227" t="s">
         <v>1759</v>
@@ -21824,7 +21824,7 @@
     </row>
     <row r="228" spans="1:21">
       <c r="A228" s="16" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B228" t="s">
         <v>1759</v>
@@ -21866,7 +21866,7 @@
         <v>3</v>
       </c>
       <c r="P228" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="Q228">
         <v>3440</v>
@@ -21883,7 +21883,7 @@
     </row>
     <row r="229" spans="1:21">
       <c r="A229" s="16" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B229" t="s">
         <v>1759</v>
@@ -21928,7 +21928,7 @@
         <v>3</v>
       </c>
       <c r="P229" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="Q229">
         <v>3320</v>
@@ -21948,7 +21948,7 @@
     </row>
     <row r="230" spans="1:21">
       <c r="A230" s="16" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B230" t="s">
         <v>1759</v>
@@ -22010,7 +22010,7 @@
     </row>
     <row r="231" spans="1:21">
       <c r="A231" s="16" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B231" t="s">
         <v>1759</v>
@@ -22072,7 +22072,7 @@
     </row>
     <row r="232" spans="1:21">
       <c r="A232" s="16" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B232" t="s">
         <v>1759</v>
@@ -22134,7 +22134,7 @@
     </row>
     <row r="233" spans="1:21">
       <c r="A233" s="16" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B233" t="s">
         <v>1759</v>
@@ -22196,7 +22196,7 @@
     </row>
     <row r="234" spans="1:21">
       <c r="A234" s="16" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B234" t="s">
         <v>1759</v>
@@ -22258,7 +22258,7 @@
     </row>
     <row r="235" spans="1:21">
       <c r="A235" s="16" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B235" t="s">
         <v>1759</v>
@@ -22323,7 +22323,7 @@
     </row>
     <row r="236" spans="1:21">
       <c r="A236" s="16" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B236" t="s">
         <v>1759</v>
@@ -22388,7 +22388,7 @@
     </row>
     <row r="237" spans="1:21">
       <c r="A237" s="16" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B237" t="s">
         <v>1759</v>
@@ -22453,7 +22453,7 @@
     </row>
     <row r="238" spans="1:21">
       <c r="A238" s="16" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B238" t="s">
         <v>1759</v>
@@ -22713,7 +22713,7 @@
     </row>
     <row r="242" spans="1:21">
       <c r="A242" s="16" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B242" t="s">
         <v>1759</v>
@@ -22778,7 +22778,7 @@
     </row>
     <row r="243" spans="1:21">
       <c r="A243" s="16" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B243" t="s">
         <v>1759</v>
@@ -22843,7 +22843,7 @@
     </row>
     <row r="244" spans="1:21">
       <c r="A244" s="16" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B244" t="s">
         <v>1759</v>
@@ -22908,7 +22908,7 @@
     </row>
     <row r="245" spans="1:21">
       <c r="A245" s="16" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B245" t="s">
         <v>1759</v>
@@ -22973,7 +22973,7 @@
     </row>
     <row r="246" spans="1:21">
       <c r="A246" s="16" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B246" t="s">
         <v>1759</v>
@@ -23026,7 +23026,7 @@
     </row>
     <row r="247" spans="1:21">
       <c r="A247" s="16" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B247" t="s">
         <v>1759</v>
@@ -23091,7 +23091,7 @@
     </row>
     <row r="248" spans="1:21">
       <c r="A248" s="16" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B248" t="s">
         <v>1759</v>
@@ -23156,7 +23156,7 @@
     </row>
     <row r="249" spans="1:21">
       <c r="A249" s="16" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B249" t="s">
         <v>1759</v>
@@ -23221,7 +23221,7 @@
     </row>
     <row r="250" spans="1:21">
       <c r="A250" s="16" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B250" t="s">
         <v>1759</v>
@@ -23286,7 +23286,7 @@
     </row>
     <row r="251" spans="1:21">
       <c r="A251" s="16" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B251" t="s">
         <v>1759</v>
@@ -29446,7 +29446,7 @@
     </row>
     <row r="346" spans="1:21">
       <c r="A346" s="16" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B346" t="s">
         <v>1644</v>
@@ -29487,7 +29487,7 @@
     </row>
     <row r="347" spans="1:21">
       <c r="A347" s="16" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B347" t="s">
         <v>1644</v>
@@ -29528,7 +29528,7 @@
     </row>
     <row r="348" spans="1:21">
       <c r="A348" s="16" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="B348" t="s">
         <v>1759</v>
@@ -29539,7 +29539,7 @@
     </row>
     <row r="349" spans="1:21">
       <c r="A349" s="16" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="B349" t="s">
         <v>1759</v>
@@ -29550,7 +29550,7 @@
     </row>
     <row r="350" spans="1:21">
       <c r="A350" s="16" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B350" t="s">
         <v>1644</v>
@@ -29568,13 +29568,13 @@
         <v>6</v>
       </c>
       <c r="O350" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="P350" t="s">
+        <v>2117</v>
+      </c>
+      <c r="R350" t="s">
         <v>2118</v>
-      </c>
-      <c r="R350" t="s">
-        <v>2119</v>
       </c>
       <c r="S350" t="s">
         <v>7</v>
@@ -29588,7 +29588,7 @@
     </row>
     <row r="351" spans="1:21">
       <c r="A351" s="16" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B351" t="s">
         <v>1644</v>
@@ -29606,13 +29606,13 @@
         <v>6</v>
       </c>
       <c r="O351" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="P351" t="s">
+        <v>2117</v>
+      </c>
+      <c r="R351" t="s">
         <v>2118</v>
-      </c>
-      <c r="R351" t="s">
-        <v>2119</v>
       </c>
       <c r="S351" t="s">
         <v>7</v>
@@ -29626,7 +29626,7 @@
     </row>
     <row r="352" spans="1:21">
       <c r="A352" s="16" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B352" t="s">
         <v>1644</v>
@@ -29644,13 +29644,13 @@
         <v>6</v>
       </c>
       <c r="O352" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="P352" t="s">
+        <v>2117</v>
+      </c>
+      <c r="R352" t="s">
         <v>2118</v>
-      </c>
-      <c r="R352" t="s">
-        <v>2119</v>
       </c>
       <c r="S352" t="s">
         <v>7</v>
@@ -29664,7 +29664,7 @@
     </row>
     <row r="353" spans="1:21">
       <c r="A353" s="16" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B353" t="s">
         <v>1644</v>
@@ -29682,13 +29682,13 @@
         <v>6</v>
       </c>
       <c r="O353" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="P353" t="s">
+        <v>2117</v>
+      </c>
+      <c r="R353" t="s">
         <v>2118</v>
-      </c>
-      <c r="R353" t="s">
-        <v>2119</v>
       </c>
       <c r="S353" t="s">
         <v>7</v>
@@ -29720,7 +29720,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15">
       <c r="A1" s="15" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>1646</v>
@@ -29738,10 +29738,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="B2" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -29755,7 +29755,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="B3" t="s">
         <v>1722</v>
@@ -29772,10 +29772,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B4" t="s">
         <v>2120</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2121</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -29789,7 +29789,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B5" t="s">
         <v>1722</v>
@@ -29842,13 +29842,13 @@
   <sheetData>
     <row r="1" spans="1:23" ht="38.25" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>1642</v>
@@ -29860,7 +29860,7 @@
         <v>1643</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>1887</v>
@@ -29881,13 +29881,13 @@
         <v>0</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="O1" s="11" t="s">
         <v>1692</v>
       </c>
       <c r="P1" s="31" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="7" customFormat="1">
@@ -29904,10 +29904,10 @@
         <v>2.0000000000000001E-101</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>1652</v>
@@ -29923,7 +29923,7 @@
         <v>20</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>1682</v>
@@ -29951,10 +29951,10 @@
         <v>2.0000000000000001E-101</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>1652</v>
@@ -29970,7 +29970,7 @@
         <v>21</v>
       </c>
       <c r="N3" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>1650</v>
@@ -29993,10 +29993,10 @@
         <v>1691</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>1652</v>
@@ -30012,7 +30012,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>1653</v>
@@ -30036,10 +30036,10 @@
         <v>1691</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>1652</v>
@@ -30055,7 +30055,7 @@
         <v>27</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>1671</v>
@@ -30078,10 +30078,10 @@
         <v>1688</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>1652</v>
@@ -30097,7 +30097,7 @@
         <v>70</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>1653</v>
@@ -30120,10 +30120,10 @@
         <v>1688</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>1652</v>
@@ -30139,7 +30139,7 @@
         <v>72</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>1671</v>
@@ -30162,10 +30162,10 @@
         <v>1687</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>1652</v>
@@ -30181,7 +30181,7 @@
         <v>70</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>1653</v>
@@ -30204,10 +30204,10 @@
         <v>1687</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>1652</v>
@@ -30223,7 +30223,7 @@
         <v>72</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>1671</v>
@@ -30246,10 +30246,10 @@
         <v>1686</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>1652</v>
@@ -30265,7 +30265,7 @@
         <v>75</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>1653</v>
@@ -30288,10 +30288,10 @@
         <v>1686</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>1652</v>
@@ -30307,7 +30307,7 @@
         <v>77</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>1671</v>
@@ -30330,10 +30330,10 @@
         <v>1685</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>1652</v>
@@ -30349,7 +30349,7 @@
         <v>75</v>
       </c>
       <c r="N12" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>1653</v>
@@ -30372,10 +30372,10 @@
         <v>1685</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>1652</v>
@@ -30391,7 +30391,7 @@
         <v>77</v>
       </c>
       <c r="N13" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>1671</v>
@@ -30414,10 +30414,10 @@
         <v>1684</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>1652</v>
@@ -30433,7 +30433,7 @@
         <v>119</v>
       </c>
       <c r="N14" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>1653</v>
@@ -30457,10 +30457,10 @@
         <v>1684</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>1652</v>
@@ -30476,7 +30476,7 @@
         <v>120</v>
       </c>
       <c r="N15" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>1671</v>
@@ -30499,10 +30499,10 @@
         <v>1683</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>1652</v>
@@ -30518,7 +30518,7 @@
         <v>122</v>
       </c>
       <c r="N16" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O16" s="24" t="s">
         <v>1682</v>
@@ -30541,10 +30541,10 @@
         <v>1683</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>1652</v>
@@ -30560,7 +30560,7 @@
         <v>123</v>
       </c>
       <c r="N17" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O17" s="24" t="s">
         <v>1650</v>
@@ -30584,10 +30584,10 @@
         <v>1689</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>1652</v>
@@ -30603,7 +30603,7 @@
         <v>230</v>
       </c>
       <c r="N18" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O18" s="8" t="s">
         <v>1653</v>
@@ -30626,10 +30626,10 @@
         <v>1689</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>1652</v>
@@ -30645,7 +30645,7 @@
         <v>231</v>
       </c>
       <c r="N19" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O19" s="8" t="s">
         <v>1671</v>
@@ -30668,10 +30668,10 @@
         <v>1690</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>1652</v>
@@ -30687,7 +30687,7 @@
         <v>236</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O20" s="24" t="s">
         <v>1653</v>
@@ -30711,10 +30711,10 @@
         <v>1690</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>1652</v>
@@ -30730,7 +30730,7 @@
         <v>187</v>
       </c>
       <c r="N21" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O21" s="24" t="s">
         <v>1671</v>
@@ -30756,7 +30756,7 @@
         <v>1722</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>1652</v>
@@ -30770,7 +30770,7 @@
       <c r="L22" s="26"/>
       <c r="M22" s="22"/>
       <c r="N22" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O22" s="24" t="s">
         <v>1682</v>
@@ -30796,7 +30796,7 @@
         <v>1722</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>1652</v>
@@ -30810,7 +30810,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="22"/>
       <c r="N23" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O23" s="24" t="s">
         <v>1650</v>
@@ -30837,7 +30837,7 @@
         <v>1694</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G24" s="26"/>
       <c r="H24" s="26"/>
@@ -30847,7 +30847,7 @@
       <c r="L24" s="26"/>
       <c r="M24" s="22"/>
       <c r="N24" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O24" s="24"/>
       <c r="P24" s="28">
@@ -30871,7 +30871,7 @@
         <v>1722</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>1652</v>
@@ -30885,7 +30885,7 @@
       <c r="L25" s="26"/>
       <c r="M25" s="22"/>
       <c r="N25" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O25" s="24" t="s">
         <v>1653</v>
@@ -30911,7 +30911,7 @@
         <v>1722</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>1652</v>
@@ -30925,7 +30925,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="22"/>
       <c r="N26" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O26" s="24" t="s">
         <v>1671</v>
@@ -30951,7 +30951,7 @@
         <v>1694</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
@@ -30961,7 +30961,7 @@
       <c r="L27" s="26"/>
       <c r="M27" s="22"/>
       <c r="N27" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O27" s="24"/>
       <c r="P27" s="28">
@@ -30985,7 +30985,7 @@
         <v>1722</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>1652</v>
@@ -30999,7 +30999,7 @@
       <c r="L28" s="26"/>
       <c r="M28" s="22"/>
       <c r="N28" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O28" s="24" t="s">
         <v>1671</v>
@@ -31025,7 +31025,7 @@
         <v>1722</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>1652</v>
@@ -31039,7 +31039,7 @@
       <c r="L29" s="21"/>
       <c r="M29" s="22"/>
       <c r="N29" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O29" s="24" t="s">
         <v>1700</v>
@@ -31065,7 +31065,7 @@
         <v>1694</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -31075,7 +31075,7 @@
       <c r="L30" s="26"/>
       <c r="M30" s="22"/>
       <c r="N30" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O30" s="24"/>
       <c r="P30" s="28">
@@ -31099,7 +31099,7 @@
         <v>1722</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>1652</v>
@@ -31113,7 +31113,7 @@
       <c r="L31" s="26"/>
       <c r="M31" s="22"/>
       <c r="N31" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O31" s="24" t="s">
         <v>1653</v>
@@ -31139,7 +31139,7 @@
         <v>1722</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>1652</v>
@@ -31153,7 +31153,7 @@
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
       <c r="N32" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O32" s="24" t="s">
         <v>1671</v>
@@ -31181,7 +31181,7 @@
         <v>1694</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
@@ -31191,7 +31191,7 @@
       <c r="L33" s="26"/>
       <c r="M33" s="22"/>
       <c r="N33" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O33" s="24"/>
       <c r="P33" s="28">
@@ -31218,10 +31218,10 @@
         <v>1681</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G34" s="25" t="s">
         <v>1652</v>
@@ -31237,7 +31237,7 @@
         <v>627</v>
       </c>
       <c r="N34" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O34" s="8" t="s">
         <v>1653</v>
@@ -31266,10 +31266,10 @@
         <v>1681</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G35" s="25" t="s">
         <v>1652</v>
@@ -31285,7 +31285,7 @@
         <v>628</v>
       </c>
       <c r="N35" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O35" s="8" t="s">
         <v>1650</v>
@@ -31310,10 +31310,10 @@
         <v>1680</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G36" s="25" t="s">
         <v>1652</v>
@@ -31329,7 +31329,7 @@
         <v>627</v>
       </c>
       <c r="N36" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O36" s="8" t="s">
         <v>1653</v>
@@ -31358,10 +31358,10 @@
         <v>1680</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G37" s="25" t="s">
         <v>1652</v>
@@ -31377,7 +31377,7 @@
         <v>628</v>
       </c>
       <c r="N37" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O37" s="8" t="s">
         <v>1650</v>
@@ -31406,10 +31406,10 @@
         <v>1679</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G38" s="26" t="s">
         <v>1652</v>
@@ -31425,7 +31425,7 @@
         <v>648</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O38" s="24" t="s">
         <v>1653</v>
@@ -31448,10 +31448,10 @@
         <v>1679</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>1652</v>
@@ -31467,7 +31467,7 @@
         <v>649</v>
       </c>
       <c r="N39" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O39" s="24" t="s">
         <v>1650</v>
@@ -31490,10 +31490,10 @@
         <v>1678</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>1652</v>
@@ -31509,7 +31509,7 @@
         <v>648</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O40" s="24" t="s">
         <v>1653</v>
@@ -31532,10 +31532,10 @@
         <v>1678</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>1652</v>
@@ -31551,7 +31551,7 @@
         <v>649</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O41" s="24" t="s">
         <v>1650</v>
@@ -31574,10 +31574,10 @@
         <v>1677</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G42" s="25" t="s">
         <v>1652</v>
@@ -31593,7 +31593,7 @@
         <v>1676</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O42" s="8" t="s">
         <v>1672</v>
@@ -31616,10 +31616,10 @@
         <v>1677</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G43" s="25" t="s">
         <v>1652</v>
@@ -31635,7 +31635,7 @@
         <v>1675</v>
       </c>
       <c r="N43" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O43" s="8" t="s">
         <v>1671</v>
@@ -31658,10 +31658,10 @@
         <v>1674</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G44" s="25" t="s">
         <v>1652</v>
@@ -31677,7 +31677,7 @@
         <v>653</v>
       </c>
       <c r="N44" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O44" s="8" t="s">
         <v>1653</v>
@@ -31702,10 +31702,10 @@
         <v>1674</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G45" s="25" t="s">
         <v>1652</v>
@@ -31721,7 +31721,7 @@
         <v>655</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O45" s="8" t="s">
         <v>1650</v>
@@ -31748,10 +31748,10 @@
         <v>1673</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G46" s="25" t="s">
         <v>1652</v>
@@ -31767,7 +31767,7 @@
         <v>686</v>
       </c>
       <c r="N46" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O46" s="8" t="s">
         <v>1672</v>
@@ -31794,10 +31794,10 @@
         <v>1673</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G47" s="25" t="s">
         <v>1652</v>
@@ -31813,7 +31813,7 @@
         <v>688</v>
       </c>
       <c r="N47" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O47" s="8" t="s">
         <v>1671</v>
@@ -31838,10 +31838,10 @@
         <v>1670</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G48" s="25" t="s">
         <v>1652</v>
@@ -31857,7 +31857,7 @@
         <v>692</v>
       </c>
       <c r="N48" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O48" s="8" t="s">
         <v>1653</v>
@@ -31884,10 +31884,10 @@
         <v>1670</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G49" s="25" t="s">
         <v>1652</v>
@@ -31903,7 +31903,7 @@
         <v>693</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O49" s="8" t="s">
         <v>1650</v>
@@ -31930,10 +31930,10 @@
         <v>1666</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G50" s="25" t="s">
         <v>1652</v>
@@ -31949,7 +31949,7 @@
         <v>926</v>
       </c>
       <c r="N50" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O50" s="8" t="s">
         <v>1653</v>
@@ -31972,10 +31972,10 @@
         <v>1666</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G51" s="25" t="s">
         <v>1652</v>
@@ -31991,7 +31991,7 @@
         <v>927</v>
       </c>
       <c r="N51" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O51" s="8" t="s">
         <v>1650</v>
@@ -32015,10 +32015,10 @@
         <v>1669</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>1652</v>
@@ -32034,7 +32034,7 @@
         <v>866</v>
       </c>
       <c r="N52" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O52" s="24" t="s">
         <v>1653</v>
@@ -32058,10 +32058,10 @@
         <v>1669</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>1652</v>
@@ -32077,7 +32077,7 @@
         <v>867</v>
       </c>
       <c r="N53" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O53" s="24" t="s">
         <v>1650</v>
@@ -32100,10 +32100,10 @@
         <v>1668</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F54" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>1652</v>
@@ -32119,7 +32119,7 @@
         <v>869</v>
       </c>
       <c r="N54" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O54" s="24" t="s">
         <v>1653</v>
@@ -32142,10 +32142,10 @@
         <v>1668</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>1652</v>
@@ -32161,7 +32161,7 @@
         <v>867</v>
       </c>
       <c r="N55" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O55" s="24" t="s">
         <v>1650</v>
@@ -32184,10 +32184,10 @@
         <v>1667</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>1652</v>
@@ -32203,7 +32203,7 @@
         <v>870</v>
       </c>
       <c r="N56" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O56" s="8" t="s">
         <v>1653</v>
@@ -32226,10 +32226,10 @@
         <v>1667</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>1652</v>
@@ -32245,7 +32245,7 @@
         <v>48</v>
       </c>
       <c r="N57" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O57" s="8" t="s">
         <v>1650</v>
@@ -32271,7 +32271,7 @@
         <v>1722</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>1696</v>
@@ -32285,7 +32285,7 @@
       <c r="L58" s="26"/>
       <c r="M58" s="22"/>
       <c r="N58" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O58" s="24" t="s">
         <v>1682</v>
@@ -32311,7 +32311,7 @@
         <v>1722</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>1696</v>
@@ -32325,7 +32325,7 @@
       <c r="L59" s="21"/>
       <c r="M59" s="22"/>
       <c r="N59" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O59" s="24" t="s">
         <v>1650</v>
@@ -32351,7 +32351,7 @@
         <v>1694</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>1696</v>
@@ -32363,7 +32363,7 @@
       <c r="L60" s="26"/>
       <c r="M60" s="22"/>
       <c r="N60" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O60" s="24"/>
       <c r="P60" s="28">
@@ -32387,7 +32387,7 @@
         <v>1722</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>1696</v>
@@ -32401,7 +32401,7 @@
       <c r="L61" s="26"/>
       <c r="M61" s="22"/>
       <c r="N61" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O61" s="24" t="s">
         <v>1682</v>
@@ -32427,7 +32427,7 @@
         <v>1722</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>1696</v>
@@ -32441,7 +32441,7 @@
       <c r="L62" s="21"/>
       <c r="M62" s="22"/>
       <c r="N62" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O62" s="24" t="s">
         <v>1650</v>
@@ -32467,7 +32467,7 @@
         <v>1694</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>1696</v>
@@ -32479,7 +32479,7 @@
       <c r="L63" s="26"/>
       <c r="M63" s="22"/>
       <c r="N63" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O63" s="24"/>
       <c r="P63" s="28">
@@ -32503,7 +32503,7 @@
         <v>1722</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>1652</v>
@@ -32517,7 +32517,7 @@
       <c r="L64" s="26"/>
       <c r="M64" s="22"/>
       <c r="N64" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O64" s="24" t="s">
         <v>1653</v>
@@ -32543,7 +32543,7 @@
         <v>1722</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>1652</v>
@@ -32557,7 +32557,7 @@
       <c r="L65" s="21"/>
       <c r="M65" s="22"/>
       <c r="N65" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O65" s="24" t="s">
         <v>1650</v>
@@ -32583,7 +32583,7 @@
         <v>1695</v>
       </c>
       <c r="F66" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G66" s="26" t="s">
         <v>1652</v>
@@ -32595,7 +32595,7 @@
       <c r="L66" s="21"/>
       <c r="M66" s="22"/>
       <c r="N66" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O66" s="20"/>
       <c r="P66" s="28">
@@ -32619,7 +32619,7 @@
         <v>1694</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>1652</v>
@@ -32631,7 +32631,7 @@
       <c r="L67" s="26"/>
       <c r="M67" s="22"/>
       <c r="N67" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O67" s="24"/>
       <c r="P67" s="28">
@@ -32655,7 +32655,7 @@
         <v>1694</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>1652</v>
@@ -32667,7 +32667,7 @@
       <c r="L68" s="21"/>
       <c r="M68" s="22"/>
       <c r="N68" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O68" s="20"/>
       <c r="P68" s="28">
@@ -32691,7 +32691,7 @@
         <v>1722</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>1652</v>
@@ -32705,7 +32705,7 @@
       <c r="L69" s="26"/>
       <c r="M69" s="22"/>
       <c r="N69" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O69" s="24" t="s">
         <v>1653</v>
@@ -32731,7 +32731,7 @@
         <v>1722</v>
       </c>
       <c r="F70" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>1652</v>
@@ -32745,7 +32745,7 @@
       <c r="L70" s="21"/>
       <c r="M70" s="22"/>
       <c r="N70" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O70" s="24" t="s">
         <v>1650</v>
@@ -32771,7 +32771,7 @@
         <v>1695</v>
       </c>
       <c r="F71" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>1652</v>
@@ -32783,7 +32783,7 @@
       <c r="L71" s="21"/>
       <c r="M71" s="22"/>
       <c r="N71" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O71" s="20"/>
       <c r="P71" s="28">
@@ -32807,7 +32807,7 @@
         <v>1694</v>
       </c>
       <c r="F72" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>1652</v>
@@ -32819,7 +32819,7 @@
       <c r="L72" s="26"/>
       <c r="M72" s="22"/>
       <c r="N72" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O72" s="24"/>
       <c r="P72" s="28">
@@ -32843,7 +32843,7 @@
         <v>1694</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>1652</v>
@@ -32855,7 +32855,7 @@
       <c r="L73" s="21"/>
       <c r="M73" s="22"/>
       <c r="N73" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O73" s="20"/>
       <c r="P73" s="28">
@@ -32879,7 +32879,7 @@
         <v>1722</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>1652</v>
@@ -32893,7 +32893,7 @@
       <c r="L74" s="26"/>
       <c r="M74" s="22"/>
       <c r="N74" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O74" s="24" t="s">
         <v>1653</v>
@@ -32919,7 +32919,7 @@
         <v>1722</v>
       </c>
       <c r="F75" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>1652</v>
@@ -32933,7 +32933,7 @@
       <c r="L75" s="21"/>
       <c r="M75" s="22"/>
       <c r="N75" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O75" s="24" t="s">
         <v>1650</v>
@@ -32959,7 +32959,7 @@
         <v>1695</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>1652</v>
@@ -32971,7 +32971,7 @@
       <c r="L76" s="21"/>
       <c r="M76" s="22"/>
       <c r="N76" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O76" s="20"/>
       <c r="P76" s="28">
@@ -32995,7 +32995,7 @@
         <v>1694</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>1652</v>
@@ -33007,7 +33007,7 @@
       <c r="L77" s="26"/>
       <c r="M77" s="22"/>
       <c r="N77" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O77" s="24"/>
       <c r="P77" s="28">
@@ -33028,10 +33028,10 @@
         <v>1665</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>1652</v>
@@ -33047,7 +33047,7 @@
         <v>1343</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O78" s="24" t="s">
         <v>1653</v>
@@ -33070,10 +33070,10 @@
         <v>1665</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>1652</v>
@@ -33089,7 +33089,7 @@
         <v>1344</v>
       </c>
       <c r="N79" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O79" s="24" t="s">
         <v>1650</v>
@@ -33112,10 +33112,10 @@
         <v>1664</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>1652</v>
@@ -33131,7 +33131,7 @@
         <v>1343</v>
       </c>
       <c r="N80" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O80" s="24" t="s">
         <v>1653</v>
@@ -33154,10 +33154,10 @@
         <v>1664</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>1652</v>
@@ -33173,7 +33173,7 @@
         <v>1344</v>
       </c>
       <c r="N81" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O81" s="24" t="s">
         <v>1650</v>
@@ -33196,10 +33196,10 @@
         <v>1663</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>1652</v>
@@ -33215,7 +33215,7 @@
         <v>1343</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O82" s="24" t="s">
         <v>1653</v>
@@ -33238,10 +33238,10 @@
         <v>1663</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>1652</v>
@@ -33257,7 +33257,7 @@
         <v>1344</v>
       </c>
       <c r="N83" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O83" s="24" t="s">
         <v>1650</v>
@@ -33280,10 +33280,10 @@
         <v>1662</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G84" s="26" t="s">
         <v>1652</v>
@@ -33299,7 +33299,7 @@
         <v>1343</v>
       </c>
       <c r="N84" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O84" s="24" t="s">
         <v>1653</v>
@@ -33322,10 +33322,10 @@
         <v>1662</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F85" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>1652</v>
@@ -33341,7 +33341,7 @@
         <v>1344</v>
       </c>
       <c r="N85" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O85" s="24" t="s">
         <v>1650</v>
@@ -33364,10 +33364,10 @@
         <v>1661</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F86" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G86" s="26" t="s">
         <v>1652</v>
@@ -33383,7 +33383,7 @@
         <v>1355</v>
       </c>
       <c r="N86" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O86" s="24" t="s">
         <v>1653</v>
@@ -33406,10 +33406,10 @@
         <v>1661</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G87" s="26" t="s">
         <v>1652</v>
@@ -33425,7 +33425,7 @@
         <v>1356</v>
       </c>
       <c r="N87" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O87" s="24" t="s">
         <v>1650</v>
@@ -33448,10 +33448,10 @@
         <v>1660</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>1652</v>
@@ -33467,7 +33467,7 @@
         <v>1355</v>
       </c>
       <c r="N88" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O88" s="24" t="s">
         <v>1653</v>
@@ -33490,10 +33490,10 @@
         <v>1660</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>1652</v>
@@ -33509,7 +33509,7 @@
         <v>1356</v>
       </c>
       <c r="N89" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O89" s="24" t="s">
         <v>1650</v>
@@ -33532,10 +33532,10 @@
         <v>1659</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>1652</v>
@@ -33551,7 +33551,7 @@
         <v>1363</v>
       </c>
       <c r="N90" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O90" s="24" t="s">
         <v>1653</v>
@@ -33574,10 +33574,10 @@
         <v>1659</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F91" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>1652</v>
@@ -33593,7 +33593,7 @@
         <v>1364</v>
       </c>
       <c r="N91" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O91" s="24" t="s">
         <v>1650</v>
@@ -33616,10 +33616,10 @@
         <v>1658</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F92" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G92" s="26" t="s">
         <v>1652</v>
@@ -33635,7 +33635,7 @@
         <v>1363</v>
       </c>
       <c r="N92" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O92" s="24" t="s">
         <v>1653</v>
@@ -33658,10 +33658,10 @@
         <v>1658</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F93" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G93" s="26" t="s">
         <v>1652</v>
@@ -33677,7 +33677,7 @@
         <v>1364</v>
       </c>
       <c r="N93" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O93" s="24" t="s">
         <v>1650</v>
@@ -33700,10 +33700,10 @@
         <v>1657</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F94" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>1652</v>
@@ -33719,7 +33719,7 @@
         <v>1371</v>
       </c>
       <c r="N94" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O94" s="24" t="s">
         <v>1653</v>
@@ -33742,10 +33742,10 @@
         <v>1657</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F95" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>1652</v>
@@ -33761,7 +33761,7 @@
         <v>1372</v>
       </c>
       <c r="N95" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O95" s="24" t="s">
         <v>1650</v>
@@ -33784,10 +33784,10 @@
         <v>1656</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G96" s="26" t="s">
         <v>1652</v>
@@ -33803,7 +33803,7 @@
         <v>1371</v>
       </c>
       <c r="N96" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O96" s="24" t="s">
         <v>1653</v>
@@ -33826,10 +33826,10 @@
         <v>1656</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>1652</v>
@@ -33845,7 +33845,7 @@
         <v>1372</v>
       </c>
       <c r="N97" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O97" s="24" t="s">
         <v>1650</v>
@@ -33868,10 +33868,10 @@
         <v>1382</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>1652</v>
@@ -33887,7 +33887,7 @@
         <v>1655</v>
       </c>
       <c r="N98" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O98" s="24" t="s">
         <v>1653</v>
@@ -33910,10 +33910,10 @@
         <v>1382</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>1652</v>
@@ -33929,7 +33929,7 @@
         <v>1655</v>
       </c>
       <c r="N99" s="25" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="O99" s="24" t="s">
         <v>1650</v>
@@ -43416,7 +43416,7 @@
       <c r="K323" s="21"/>
       <c r="L323" s="21"/>
       <c r="M323" s="22" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="N323" s="21" t="s">
         <v>1693</v>

--- a/HE_Database_PRO_FINAL.xlsx
+++ b/HE_Database_PRO_FINAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79BD917-C904-4BDC-91D8-5C3FE4DB46B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7358DEBA-9627-4413-87E6-6A7F82E4D318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="7" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7506" uniqueCount="2133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7506" uniqueCount="2132">
   <si>
     <t>Description</t>
   </si>
@@ -5762,9 +5762,6 @@
   </si>
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Act.</t>
   </si>
   <si>
     <t xml:space="preserve"> WASTE HEAT EXCHANGER</t>
@@ -7338,7 +7335,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="65.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="13" style="2" customWidth="1"/>
@@ -7399,19 +7396,19 @@
         <v>2</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="O1" s="15" t="s">
+        <v>1889</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>2110</v>
+      </c>
+      <c r="Q1" s="15" t="s">
         <v>1890</v>
       </c>
-      <c r="P1" s="15" t="s">
-        <v>2111</v>
-      </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>1891</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>1892</v>
       </c>
       <c r="S1" t="s">
         <v>1645</v>
@@ -7464,7 +7461,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="O2">
         <v>19</v>
@@ -7529,7 +7526,7 @@
         <v>86</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="O3">
         <v>19</v>
@@ -7594,7 +7591,7 @@
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="O4">
         <v>19</v>
@@ -7724,7 +7721,7 @@
         <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="O6">
         <v>19</v>
@@ -7789,7 +7786,7 @@
         <v>86</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="O7">
         <v>19</v>
@@ -7854,7 +7851,7 @@
         <v>177</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="O8">
         <v>19</v>
@@ -8374,7 +8371,7 @@
         <v>213</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="O16">
         <v>19</v>
@@ -10285,7 +10282,7 @@
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="16" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B46" t="s">
         <v>1759</v>
@@ -10350,7 +10347,7 @@
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="16" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B47" t="s">
         <v>1759</v>
@@ -10415,7 +10412,7 @@
     </row>
     <row r="48" spans="1:21">
       <c r="A48" s="16" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B48" t="s">
         <v>1759</v>
@@ -10454,7 +10451,7 @@
         <v>11</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="O48">
         <v>19</v>
@@ -10740,7 +10737,7 @@
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="16" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B53" t="s">
         <v>1759</v>
@@ -10861,7 +10858,7 @@
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="16" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B55" t="s">
         <v>1759</v>
@@ -10900,7 +10897,7 @@
         <v>330</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="O55">
         <v>19</v>
@@ -10926,7 +10923,7 @@
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="16" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B56" t="s">
         <v>1759</v>
@@ -10965,7 +10962,7 @@
         <v>11</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="O56">
         <v>19</v>
@@ -10988,7 +10985,7 @@
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="16" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B57" t="s">
         <v>1759</v>
@@ -11027,7 +11024,7 @@
         <v>192</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="O57">
         <v>19</v>
@@ -11053,7 +11050,7 @@
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="16" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B58" t="s">
         <v>1759</v>
@@ -11092,7 +11089,7 @@
         <v>5</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="O58">
         <v>19</v>
@@ -11118,7 +11115,7 @@
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="16" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B59" t="s">
         <v>1759</v>
@@ -11157,7 +11154,7 @@
         <v>5</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="O59">
         <v>19</v>
@@ -11183,7 +11180,7 @@
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="16" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B60" t="s">
         <v>1759</v>
@@ -11222,7 +11219,7 @@
         <v>13</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O60">
         <v>19</v>
@@ -11248,7 +11245,7 @@
     </row>
     <row r="61" spans="1:21">
       <c r="A61" s="16" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B61" t="s">
         <v>1759</v>
@@ -11313,7 +11310,7 @@
     </row>
     <row r="62" spans="1:21">
       <c r="A62" s="16" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B62" t="s">
         <v>1759</v>
@@ -11378,7 +11375,7 @@
     </row>
     <row r="63" spans="1:21">
       <c r="A63" s="16" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B63" t="s">
         <v>1759</v>
@@ -11443,7 +11440,7 @@
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="16" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B64" t="s">
         <v>1759</v>
@@ -11508,7 +11505,7 @@
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="16" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B65" t="s">
         <v>1759</v>
@@ -11547,7 +11544,7 @@
         <v>11</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="O65">
         <v>19</v>
@@ -11573,7 +11570,7 @@
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="16" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B66" t="s">
         <v>1759</v>
@@ -11612,7 +11609,7 @@
         <v>11</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="O66">
         <v>19</v>
@@ -11638,7 +11635,7 @@
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="16" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B67" t="s">
         <v>1759</v>
@@ -11677,7 +11674,7 @@
         <v>11</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="O67">
         <v>19</v>
@@ -11703,7 +11700,7 @@
     </row>
     <row r="68" spans="1:21">
       <c r="A68" s="16" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B68" t="s">
         <v>1759</v>
@@ -11742,7 +11739,7 @@
         <v>11</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="O68">
         <v>19</v>
@@ -11768,7 +11765,7 @@
     </row>
     <row r="69" spans="1:21">
       <c r="A69" s="16" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B69" t="s">
         <v>1759</v>
@@ -11807,7 +11804,7 @@
         <v>13</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="O69">
         <v>19</v>
@@ -11833,7 +11830,7 @@
     </row>
     <row r="70" spans="1:21">
       <c r="A70" s="16" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B70" t="s">
         <v>1759</v>
@@ -11872,7 +11869,7 @@
         <v>370</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="O70">
         <v>1</v>
@@ -11898,7 +11895,7 @@
     </row>
     <row r="71" spans="1:21">
       <c r="A71" s="16" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="B71" t="s">
         <v>1759</v>
@@ -11937,7 +11934,7 @@
         <v>380</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="O71">
         <v>33</v>
@@ -11963,7 +11960,7 @@
     </row>
     <row r="72" spans="1:21">
       <c r="A72" s="16" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B72" t="s">
         <v>1759</v>
@@ -12002,7 +11999,7 @@
         <v>5</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="O72">
         <v>31</v>
@@ -12028,7 +12025,7 @@
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="16" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B73" t="s">
         <v>1759</v>
@@ -12067,7 +12064,7 @@
         <v>5</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="O73">
         <v>31</v>
@@ -12093,7 +12090,7 @@
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="16" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B74" t="s">
         <v>1759</v>
@@ -12132,7 +12129,7 @@
         <v>5</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="O74">
         <v>31</v>
@@ -12223,7 +12220,7 @@
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="16" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B76" t="s">
         <v>1759</v>
@@ -12285,7 +12282,7 @@
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="16" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B77" t="s">
         <v>1644</v>
@@ -12350,7 +12347,7 @@
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="16" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B78" t="s">
         <v>1759</v>
@@ -12409,7 +12406,7 @@
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="16" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B79" t="s">
         <v>1759</v>
@@ -12474,7 +12471,7 @@
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="16" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B80" t="s">
         <v>1759</v>
@@ -12539,7 +12536,7 @@
     </row>
     <row r="81" spans="1:21">
       <c r="A81" s="16" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B81" t="s">
         <v>1759</v>
@@ -12604,7 +12601,7 @@
     </row>
     <row r="82" spans="1:21">
       <c r="A82" s="16" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="B82" t="s">
         <v>1759</v>
@@ -12734,7 +12731,7 @@
     </row>
     <row r="84" spans="1:21">
       <c r="A84" s="16" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B84" t="s">
         <v>1759</v>
@@ -12799,7 +12796,7 @@
     </row>
     <row r="85" spans="1:21">
       <c r="A85" s="16" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B85" t="s">
         <v>1644</v>
@@ -12864,7 +12861,7 @@
     </row>
     <row r="86" spans="1:21">
       <c r="A86" s="16" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B86" t="s">
         <v>1759</v>
@@ -12923,7 +12920,7 @@
     </row>
     <row r="87" spans="1:21">
       <c r="A87" s="16" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B87" t="s">
         <v>1759</v>
@@ -12988,7 +12985,7 @@
     </row>
     <row r="88" spans="1:21">
       <c r="A88" s="16" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B88" t="s">
         <v>1759</v>
@@ -13053,7 +13050,7 @@
     </row>
     <row r="89" spans="1:21">
       <c r="A89" s="16" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B89" t="s">
         <v>1759</v>
@@ -13118,7 +13115,7 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="16" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B90" t="s">
         <v>1759</v>
@@ -13183,7 +13180,7 @@
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="16" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B91" t="s">
         <v>1759</v>
@@ -13236,7 +13233,7 @@
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="16" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B92" t="s">
         <v>1759</v>
@@ -13301,7 +13298,7 @@
     </row>
     <row r="93" spans="1:21">
       <c r="A93" s="16" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B93" t="s">
         <v>1759</v>
@@ -13366,7 +13363,7 @@
     </row>
     <row r="94" spans="1:21">
       <c r="A94" s="16" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B94" t="s">
         <v>1759</v>
@@ -13431,7 +13428,7 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="16" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B95" t="s">
         <v>1644</v>
@@ -13496,7 +13493,7 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="16" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B96" t="s">
         <v>1759</v>
@@ -13561,7 +13558,7 @@
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="16" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="B97" t="s">
         <v>1759</v>
@@ -13626,7 +13623,7 @@
     </row>
     <row r="98" spans="1:21">
       <c r="A98" s="16" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B98" t="s">
         <v>1759</v>
@@ -13691,7 +13688,7 @@
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="16" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="B99" t="s">
         <v>1759</v>
@@ -13756,7 +13753,7 @@
     </row>
     <row r="100" spans="1:21">
       <c r="A100" s="16" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B100" t="s">
         <v>1759</v>
@@ -13795,7 +13792,7 @@
         <v>303</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="O100">
         <v>19</v>
@@ -13821,7 +13818,7 @@
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="16" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B101" t="s">
         <v>1759</v>
@@ -13860,7 +13857,7 @@
         <v>11</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="O101">
         <v>19</v>
@@ -13886,7 +13883,7 @@
     </row>
     <row r="102" spans="1:21">
       <c r="A102" s="16" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B102" t="s">
         <v>1759</v>
@@ -13925,7 +13922,7 @@
         <v>5</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="O102">
         <v>19</v>
@@ -13951,7 +13948,7 @@
     </row>
     <row r="103" spans="1:21">
       <c r="A103" s="16" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B103" t="s">
         <v>1759</v>
@@ -13990,7 +13987,7 @@
         <v>11</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="O103">
         <v>19</v>
@@ -14016,7 +14013,7 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="16" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B104" t="s">
         <v>1759</v>
@@ -14055,10 +14052,10 @@
         <v>512</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="O104" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="P104">
         <v>2.77</v>
@@ -14081,7 +14078,7 @@
     </row>
     <row r="105" spans="1:21">
       <c r="A105" s="16" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B105" t="s">
         <v>1759</v>
@@ -14120,10 +14117,10 @@
         <v>512</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="O105" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="P105">
         <v>2.77</v>
@@ -14146,7 +14143,7 @@
     </row>
     <row r="106" spans="1:21">
       <c r="A106" s="16" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B106" t="s">
         <v>1759</v>
@@ -14185,10 +14182,10 @@
         <v>512</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="O106" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="P106">
         <v>2.77</v>
@@ -14211,7 +14208,7 @@
     </row>
     <row r="107" spans="1:21">
       <c r="A107" s="16" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B107" t="s">
         <v>1759</v>
@@ -14250,7 +14247,7 @@
         <v>297</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="O107">
         <v>19</v>
@@ -14276,7 +14273,7 @@
     </row>
     <row r="108" spans="1:21">
       <c r="A108" s="16" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B108" t="s">
         <v>1759</v>
@@ -14315,7 +14312,7 @@
         <v>297</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="O108">
         <v>19</v>
@@ -14341,7 +14338,7 @@
     </row>
     <row r="109" spans="1:21">
       <c r="A109" s="16" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B109" t="s">
         <v>1759</v>
@@ -14380,10 +14377,10 @@
         <v>297</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="O109" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="P109">
         <v>2.11</v>
@@ -14406,7 +14403,7 @@
     </row>
     <row r="110" spans="1:21">
       <c r="A110" s="16" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B110" t="s">
         <v>1759</v>
@@ -14445,7 +14442,7 @@
         <v>13</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="O110">
         <v>19</v>
@@ -14471,7 +14468,7 @@
     </row>
     <row r="111" spans="1:21">
       <c r="A111" s="16" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B111" t="s">
         <v>1759</v>
@@ -14510,7 +14507,7 @@
         <v>13</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="O111">
         <v>25</v>
@@ -14536,7 +14533,7 @@
     </row>
     <row r="112" spans="1:21">
       <c r="A112" s="16" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B112" t="s">
         <v>1759</v>
@@ -14575,7 +14572,7 @@
         <v>13</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="O112">
         <v>25</v>
@@ -14601,7 +14598,7 @@
     </row>
     <row r="113" spans="1:21">
       <c r="A113" s="16" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B113" t="s">
         <v>1759</v>
@@ -14640,7 +14637,7 @@
         <v>65</v>
       </c>
       <c r="N113" s="34" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="O113">
         <v>19</v>
@@ -14666,7 +14663,7 @@
     </row>
     <row r="114" spans="1:21">
       <c r="A114" s="16" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B114" t="s">
         <v>1759</v>
@@ -14705,7 +14702,7 @@
         <v>11</v>
       </c>
       <c r="N114" s="34" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="O114">
         <v>19</v>
@@ -14731,7 +14728,7 @@
     </row>
     <row r="115" spans="1:21">
       <c r="A115" s="16" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B115" t="s">
         <v>1759</v>
@@ -14770,7 +14767,7 @@
         <v>53</v>
       </c>
       <c r="N115" s="34" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="O115">
         <v>19</v>
@@ -14796,7 +14793,7 @@
     </row>
     <row r="116" spans="1:21">
       <c r="A116" s="16" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B116" t="s">
         <v>1759</v>
@@ -14835,7 +14832,7 @@
         <v>5</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="O116">
         <v>19</v>
@@ -14861,7 +14858,7 @@
     </row>
     <row r="117" spans="1:21">
       <c r="A117" s="16" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B117" t="s">
         <v>1759</v>
@@ -14900,13 +14897,13 @@
         <v>11</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="O117">
         <v>3</v>
       </c>
       <c r="P117" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="Q117">
         <v>6000</v>
@@ -14926,7 +14923,7 @@
     </row>
     <row r="118" spans="1:21">
       <c r="A118" s="16" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B118" t="s">
         <v>1759</v>
@@ -14959,7 +14956,7 @@
         <v>561</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="O118">
         <v>19</v>
@@ -14985,7 +14982,7 @@
     </row>
     <row r="119" spans="1:21">
       <c r="A119" s="16" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B119" t="s">
         <v>1759</v>
@@ -15024,7 +15021,7 @@
         <v>71</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="O119">
         <v>19</v>
@@ -15050,7 +15047,7 @@
     </row>
     <row r="120" spans="1:21">
       <c r="A120" s="16" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B120" t="s">
         <v>1759</v>
@@ -15091,7 +15088,7 @@
     </row>
     <row r="121" spans="1:21">
       <c r="A121" s="16" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B121" t="s">
         <v>1759</v>
@@ -15132,7 +15129,7 @@
     </row>
     <row r="122" spans="1:21">
       <c r="A122" s="16" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="B122" t="s">
         <v>1759</v>
@@ -15141,12 +15138,12 @@
         <v>575</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="123" spans="1:21">
       <c r="A123" s="16" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B123" t="s">
         <v>1759</v>
@@ -15185,7 +15182,7 @@
         <v>11</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="O123">
         <v>25</v>
@@ -15211,7 +15208,7 @@
     </row>
     <row r="124" spans="1:21">
       <c r="A124" s="16" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B124" t="s">
         <v>1759</v>
@@ -15250,7 +15247,7 @@
         <v>11</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="O124">
         <v>19</v>
@@ -15315,7 +15312,7 @@
         <v>11</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="O125">
         <v>25</v>
@@ -15386,7 +15383,7 @@
         <v>19</v>
       </c>
       <c r="P126" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="Q126">
         <v>3000</v>
@@ -15640,7 +15637,7 @@
         <v>2.5</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="O130">
         <v>1</v>
@@ -16912,7 +16909,7 @@
     </row>
     <row r="151" spans="1:21">
       <c r="A151" s="16" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B151" t="s">
         <v>1759</v>
@@ -16977,7 +16974,7 @@
     </row>
     <row r="152" spans="1:21">
       <c r="A152" s="16" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B152" t="s">
         <v>1759</v>
@@ -17042,7 +17039,7 @@
     </row>
     <row r="153" spans="1:21">
       <c r="A153" s="16" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B153" t="s">
         <v>1759</v>
@@ -17107,7 +17104,7 @@
     </row>
     <row r="154" spans="1:21">
       <c r="A154" s="16" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B154" t="s">
         <v>1759</v>
@@ -17172,7 +17169,7 @@
     </row>
     <row r="155" spans="1:21">
       <c r="A155" s="17" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="B155" t="s">
         <v>1759</v>
@@ -17237,7 +17234,7 @@
     </row>
     <row r="156" spans="1:21">
       <c r="A156" s="16" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B156" t="s">
         <v>1759</v>
@@ -17302,7 +17299,7 @@
     </row>
     <row r="157" spans="1:21">
       <c r="A157" s="16" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B157" t="s">
         <v>1759</v>
@@ -17367,7 +17364,7 @@
     </row>
     <row r="158" spans="1:21">
       <c r="A158" s="16" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B158" t="s">
         <v>1759</v>
@@ -17432,7 +17429,7 @@
     </row>
     <row r="159" spans="1:21">
       <c r="A159" s="16" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B159" t="s">
         <v>1759</v>
@@ -17497,7 +17494,7 @@
     </row>
     <row r="160" spans="1:21">
       <c r="A160" s="16" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B160" t="s">
         <v>1759</v>
@@ -17562,7 +17559,7 @@
     </row>
     <row r="161" spans="1:21">
       <c r="A161" s="16" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="B161" t="s">
         <v>1759</v>
@@ -17627,7 +17624,7 @@
     </row>
     <row r="162" spans="1:21">
       <c r="A162" s="16" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B162" t="s">
         <v>1759</v>
@@ -17692,7 +17689,7 @@
     </row>
     <row r="163" spans="1:21">
       <c r="A163" s="16" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B163" t="s">
         <v>1759</v>
@@ -17757,7 +17754,7 @@
     </row>
     <row r="164" spans="1:21">
       <c r="A164" s="16" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B164" t="s">
         <v>1759</v>
@@ -17952,7 +17949,7 @@
     </row>
     <row r="167" spans="1:21">
       <c r="A167" s="16" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B167" t="s">
         <v>1759</v>
@@ -18017,7 +18014,7 @@
     </row>
     <row r="168" spans="1:21">
       <c r="A168" s="16" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B168" t="s">
         <v>1759</v>
@@ -18082,7 +18079,7 @@
     </row>
     <row r="169" spans="1:21">
       <c r="A169" s="16" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B169" t="s">
         <v>1759</v>
@@ -18147,7 +18144,7 @@
     </row>
     <row r="170" spans="1:21">
       <c r="A170" s="16" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B170" t="s">
         <v>1759</v>
@@ -18212,7 +18209,7 @@
     </row>
     <row r="171" spans="1:21">
       <c r="A171" s="16" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B171" t="s">
         <v>1759</v>
@@ -18407,7 +18404,7 @@
     </row>
     <row r="174" spans="1:21">
       <c r="A174" s="16" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B174" t="s">
         <v>1759</v>
@@ -18472,7 +18469,7 @@
     </row>
     <row r="175" spans="1:21">
       <c r="A175" s="16" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B175" t="s">
         <v>1759</v>
@@ -18537,7 +18534,7 @@
     </row>
     <row r="176" spans="1:21">
       <c r="A176" s="16" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B176" t="s">
         <v>1759</v>
@@ -18602,7 +18599,7 @@
     </row>
     <row r="177" spans="1:21">
       <c r="A177" s="16" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B177" t="s">
         <v>1759</v>
@@ -18667,7 +18664,7 @@
     </row>
     <row r="178" spans="1:21">
       <c r="A178" s="16" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B178" t="s">
         <v>1759</v>
@@ -18732,7 +18729,7 @@
     </row>
     <row r="179" spans="1:21">
       <c r="A179" s="16" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B179" t="s">
         <v>1759</v>
@@ -18797,7 +18794,7 @@
     </row>
     <row r="180" spans="1:21">
       <c r="A180" s="16" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B180" t="s">
         <v>1759</v>
@@ -18862,7 +18859,7 @@
     </row>
     <row r="181" spans="1:21">
       <c r="A181" s="16" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B181" t="s">
         <v>1759</v>
@@ -18992,7 +18989,7 @@
     </row>
     <row r="183" spans="1:21">
       <c r="A183" s="16" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B183" t="s">
         <v>1759</v>
@@ -19057,7 +19054,7 @@
     </row>
     <row r="184" spans="1:21">
       <c r="A184" s="16" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B184" t="s">
         <v>1759</v>
@@ -19122,7 +19119,7 @@
     </row>
     <row r="185" spans="1:21">
       <c r="A185" s="16" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B185" t="s">
         <v>1759</v>
@@ -19187,7 +19184,7 @@
     </row>
     <row r="186" spans="1:21">
       <c r="A186" s="16" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B186" t="s">
         <v>1759</v>
@@ -19252,7 +19249,7 @@
     </row>
     <row r="187" spans="1:21">
       <c r="A187" s="16" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B187" t="s">
         <v>1759</v>
@@ -19317,7 +19314,7 @@
     </row>
     <row r="188" spans="1:21">
       <c r="A188" s="16" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B188" t="s">
         <v>1759</v>
@@ -19382,7 +19379,7 @@
     </row>
     <row r="189" spans="1:21">
       <c r="A189" s="16" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B189" t="s">
         <v>1759</v>
@@ -19447,7 +19444,7 @@
     </row>
     <row r="190" spans="1:21">
       <c r="A190" s="16" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B190" t="s">
         <v>1759</v>
@@ -19512,7 +19509,7 @@
     </row>
     <row r="191" spans="1:21">
       <c r="A191" s="16" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B191" t="s">
         <v>1759</v>
@@ -19577,7 +19574,7 @@
     </row>
     <row r="192" spans="1:21">
       <c r="A192" s="16" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B192" t="s">
         <v>1759</v>
@@ -19642,7 +19639,7 @@
     </row>
     <row r="193" spans="1:21">
       <c r="A193" s="16" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B193" t="s">
         <v>1759</v>
@@ -19707,7 +19704,7 @@
     </row>
     <row r="194" spans="1:21">
       <c r="A194" s="16" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B194" t="s">
         <v>1759</v>
@@ -19746,7 +19743,7 @@
         <v>2.5</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="O194">
         <v>1</v>
@@ -19772,7 +19769,7 @@
     </row>
     <row r="195" spans="1:21">
       <c r="A195" s="16" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B195" t="s">
         <v>1759</v>
@@ -19811,7 +19808,7 @@
         <v>2.5</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="O195">
         <v>1</v>
@@ -19837,7 +19834,7 @@
     </row>
     <row r="196" spans="1:21">
       <c r="A196" s="16" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="B196" t="s">
         <v>1759</v>
@@ -19876,7 +19873,7 @@
         <v>2.5</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="O196">
         <v>1</v>
@@ -19902,7 +19899,7 @@
     </row>
     <row r="197" spans="1:21">
       <c r="A197" s="16" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B197" t="s">
         <v>1759</v>
@@ -19967,7 +19964,7 @@
     </row>
     <row r="198" spans="1:21">
       <c r="A198" s="16" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B198" t="s">
         <v>1759</v>
@@ -20032,7 +20029,7 @@
     </row>
     <row r="199" spans="1:21">
       <c r="A199" s="16" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B199" t="s">
         <v>1759</v>
@@ -20097,7 +20094,7 @@
     </row>
     <row r="200" spans="1:21">
       <c r="A200" s="16" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B200" t="s">
         <v>1759</v>
@@ -20162,7 +20159,7 @@
     </row>
     <row r="201" spans="1:21">
       <c r="A201" s="16" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B201" t="s">
         <v>1759</v>
@@ -20227,7 +20224,7 @@
     </row>
     <row r="202" spans="1:21">
       <c r="A202" s="16" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B202" t="s">
         <v>1759</v>
@@ -20292,7 +20289,7 @@
     </row>
     <row r="203" spans="1:21">
       <c r="A203" s="16" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B203" t="s">
         <v>1759</v>
@@ -20357,7 +20354,7 @@
     </row>
     <row r="204" spans="1:21">
       <c r="A204" s="16" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B204" t="s">
         <v>1759</v>
@@ -20422,7 +20419,7 @@
     </row>
     <row r="205" spans="1:21">
       <c r="A205" s="16" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B205" t="s">
         <v>1759</v>
@@ -20487,7 +20484,7 @@
     </row>
     <row r="206" spans="1:21">
       <c r="A206" s="16" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B206" t="s">
         <v>1759</v>
@@ -20552,7 +20549,7 @@
     </row>
     <row r="207" spans="1:21">
       <c r="A207" s="16" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B207" t="s">
         <v>1759</v>
@@ -20617,7 +20614,7 @@
     </row>
     <row r="208" spans="1:21">
       <c r="A208" s="16" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B208" t="s">
         <v>1759</v>
@@ -20682,7 +20679,7 @@
     </row>
     <row r="209" spans="1:21">
       <c r="A209" s="16" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B209" t="s">
         <v>1759</v>
@@ -20747,7 +20744,7 @@
     </row>
     <row r="210" spans="1:21">
       <c r="A210" s="16" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="B210" t="s">
         <v>1759</v>
@@ -20758,7 +20755,7 @@
     </row>
     <row r="211" spans="1:21">
       <c r="A211" s="16" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B211" t="s">
         <v>1759</v>
@@ -20823,7 +20820,7 @@
     </row>
     <row r="212" spans="1:21">
       <c r="A212" s="16" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="B212" t="s">
         <v>1759</v>
@@ -20888,7 +20885,7 @@
     </row>
     <row r="213" spans="1:21">
       <c r="A213" s="16" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="B213" t="s">
         <v>1759</v>
@@ -20953,7 +20950,7 @@
     </row>
     <row r="214" spans="1:21">
       <c r="A214" s="16" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B214" t="s">
         <v>1759</v>
@@ -21018,7 +21015,7 @@
     </row>
     <row r="215" spans="1:21">
       <c r="A215" s="16" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B215" t="s">
         <v>1759</v>
@@ -21083,7 +21080,7 @@
     </row>
     <row r="216" spans="1:21">
       <c r="A216" s="16" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B216" t="s">
         <v>1759</v>
@@ -21122,7 +21119,7 @@
         <v>286</v>
       </c>
       <c r="N216" s="2" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="O216">
         <v>19</v>
@@ -21148,7 +21145,7 @@
     </row>
     <row r="217" spans="1:21">
       <c r="A217" s="16" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B217" t="s">
         <v>1759</v>
@@ -21213,7 +21210,7 @@
     </row>
     <row r="218" spans="1:21">
       <c r="A218" s="16" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B218" t="s">
         <v>1759</v>
@@ -21278,7 +21275,7 @@
     </row>
     <row r="219" spans="1:21">
       <c r="A219" s="16" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B219" t="s">
         <v>1759</v>
@@ -21343,7 +21340,7 @@
     </row>
     <row r="220" spans="1:21">
       <c r="A220" s="16" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B220" t="s">
         <v>1759</v>
@@ -21408,7 +21405,7 @@
     </row>
     <row r="221" spans="1:21">
       <c r="A221" s="16" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B221" t="s">
         <v>1759</v>
@@ -21473,7 +21470,7 @@
     </row>
     <row r="222" spans="1:21">
       <c r="A222" s="16" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B222" t="s">
         <v>1759</v>
@@ -21538,7 +21535,7 @@
     </row>
     <row r="223" spans="1:21">
       <c r="A223" s="16" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B223" t="s">
         <v>1759</v>
@@ -21603,7 +21600,7 @@
     </row>
     <row r="224" spans="1:21">
       <c r="A224" s="16" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B224" t="s">
         <v>1759</v>
@@ -21668,7 +21665,7 @@
     </row>
     <row r="225" spans="1:21">
       <c r="A225" s="16" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B225" t="s">
         <v>1759</v>
@@ -21733,7 +21730,7 @@
     </row>
     <row r="226" spans="1:21">
       <c r="A226" s="16" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B226" t="s">
         <v>1759</v>
@@ -21798,7 +21795,7 @@
     </row>
     <row r="227" spans="1:21">
       <c r="A227" s="16" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B227" t="s">
         <v>1759</v>
@@ -21824,7 +21821,7 @@
     </row>
     <row r="228" spans="1:21">
       <c r="A228" s="16" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B228" t="s">
         <v>1759</v>
@@ -21866,7 +21863,7 @@
         <v>3</v>
       </c>
       <c r="P228" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Q228">
         <v>3440</v>
@@ -21883,7 +21880,7 @@
     </row>
     <row r="229" spans="1:21">
       <c r="A229" s="16" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B229" t="s">
         <v>1759</v>
@@ -21928,7 +21925,7 @@
         <v>3</v>
       </c>
       <c r="P229" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Q229">
         <v>3320</v>
@@ -21948,7 +21945,7 @@
     </row>
     <row r="230" spans="1:21">
       <c r="A230" s="16" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B230" t="s">
         <v>1759</v>
@@ -22010,7 +22007,7 @@
     </row>
     <row r="231" spans="1:21">
       <c r="A231" s="16" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B231" t="s">
         <v>1759</v>
@@ -22072,7 +22069,7 @@
     </row>
     <row r="232" spans="1:21">
       <c r="A232" s="16" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B232" t="s">
         <v>1759</v>
@@ -22134,7 +22131,7 @@
     </row>
     <row r="233" spans="1:21">
       <c r="A233" s="16" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B233" t="s">
         <v>1759</v>
@@ -22196,7 +22193,7 @@
     </row>
     <row r="234" spans="1:21">
       <c r="A234" s="16" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B234" t="s">
         <v>1759</v>
@@ -22258,7 +22255,7 @@
     </row>
     <row r="235" spans="1:21">
       <c r="A235" s="16" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B235" t="s">
         <v>1759</v>
@@ -22323,7 +22320,7 @@
     </row>
     <row r="236" spans="1:21">
       <c r="A236" s="16" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B236" t="s">
         <v>1759</v>
@@ -22388,7 +22385,7 @@
     </row>
     <row r="237" spans="1:21">
       <c r="A237" s="16" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B237" t="s">
         <v>1759</v>
@@ -22453,7 +22450,7 @@
     </row>
     <row r="238" spans="1:21">
       <c r="A238" s="16" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B238" t="s">
         <v>1759</v>
@@ -22713,7 +22710,7 @@
     </row>
     <row r="242" spans="1:21">
       <c r="A242" s="16" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B242" t="s">
         <v>1759</v>
@@ -22778,7 +22775,7 @@
     </row>
     <row r="243" spans="1:21">
       <c r="A243" s="16" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B243" t="s">
         <v>1759</v>
@@ -22843,7 +22840,7 @@
     </row>
     <row r="244" spans="1:21">
       <c r="A244" s="16" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B244" t="s">
         <v>1759</v>
@@ -22908,7 +22905,7 @@
     </row>
     <row r="245" spans="1:21">
       <c r="A245" s="16" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B245" t="s">
         <v>1759</v>
@@ -22973,7 +22970,7 @@
     </row>
     <row r="246" spans="1:21">
       <c r="A246" s="16" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B246" t="s">
         <v>1759</v>
@@ -23026,7 +23023,7 @@
     </row>
     <row r="247" spans="1:21">
       <c r="A247" s="16" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B247" t="s">
         <v>1759</v>
@@ -23091,7 +23088,7 @@
     </row>
     <row r="248" spans="1:21">
       <c r="A248" s="16" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B248" t="s">
         <v>1759</v>
@@ -23156,7 +23153,7 @@
     </row>
     <row r="249" spans="1:21">
       <c r="A249" s="16" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B249" t="s">
         <v>1759</v>
@@ -23221,7 +23218,7 @@
     </row>
     <row r="250" spans="1:21">
       <c r="A250" s="16" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B250" t="s">
         <v>1759</v>
@@ -23286,7 +23283,7 @@
     </row>
     <row r="251" spans="1:21">
       <c r="A251" s="16" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B251" t="s">
         <v>1759</v>
@@ -28802,7 +28799,7 @@
         <v>1759</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>374</v>
@@ -29446,7 +29443,7 @@
     </row>
     <row r="346" spans="1:21">
       <c r="A346" s="16" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B346" t="s">
         <v>1644</v>
@@ -29487,7 +29484,7 @@
     </row>
     <row r="347" spans="1:21">
       <c r="A347" s="16" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B347" t="s">
         <v>1644</v>
@@ -29528,7 +29525,7 @@
     </row>
     <row r="348" spans="1:21">
       <c r="A348" s="16" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B348" t="s">
         <v>1759</v>
@@ -29539,7 +29536,7 @@
     </row>
     <row r="349" spans="1:21">
       <c r="A349" s="16" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="B349" t="s">
         <v>1759</v>
@@ -29550,7 +29547,7 @@
     </row>
     <row r="350" spans="1:21">
       <c r="A350" s="16" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B350" t="s">
         <v>1644</v>
@@ -29568,13 +29565,13 @@
         <v>6</v>
       </c>
       <c r="O350" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P350" t="s">
+        <v>2116</v>
+      </c>
+      <c r="R350" t="s">
         <v>2117</v>
-      </c>
-      <c r="R350" t="s">
-        <v>2118</v>
       </c>
       <c r="S350" t="s">
         <v>7</v>
@@ -29588,7 +29585,7 @@
     </row>
     <row r="351" spans="1:21">
       <c r="A351" s="16" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B351" t="s">
         <v>1644</v>
@@ -29606,13 +29603,13 @@
         <v>6</v>
       </c>
       <c r="O351" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P351" t="s">
+        <v>2116</v>
+      </c>
+      <c r="R351" t="s">
         <v>2117</v>
-      </c>
-      <c r="R351" t="s">
-        <v>2118</v>
       </c>
       <c r="S351" t="s">
         <v>7</v>
@@ -29626,7 +29623,7 @@
     </row>
     <row r="352" spans="1:21">
       <c r="A352" s="16" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B352" t="s">
         <v>1644</v>
@@ -29644,13 +29641,13 @@
         <v>6</v>
       </c>
       <c r="O352" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P352" t="s">
+        <v>2116</v>
+      </c>
+      <c r="R352" t="s">
         <v>2117</v>
-      </c>
-      <c r="R352" t="s">
-        <v>2118</v>
       </c>
       <c r="S352" t="s">
         <v>7</v>
@@ -29664,7 +29661,7 @@
     </row>
     <row r="353" spans="1:21">
       <c r="A353" s="16" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B353" t="s">
         <v>1644</v>
@@ -29682,13 +29679,13 @@
         <v>6</v>
       </c>
       <c r="O353" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="P353" t="s">
+        <v>2116</v>
+      </c>
+      <c r="R353" t="s">
         <v>2117</v>
-      </c>
-      <c r="R353" t="s">
-        <v>2118</v>
       </c>
       <c r="S353" t="s">
         <v>7</v>
@@ -29720,7 +29717,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15">
       <c r="A1" s="15" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>1646</v>
@@ -29738,10 +29735,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B2" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -29755,7 +29752,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B3" t="s">
         <v>1722</v>
@@ -29772,10 +29769,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B4" t="s">
         <v>2119</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2120</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -29789,7 +29786,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B5" t="s">
         <v>1722</v>
@@ -29842,25 +29839,25 @@
   <sheetData>
     <row r="1" spans="1:23" ht="38.25" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>1642</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>1888</v>
+        <v>1646</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>1643</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>1887</v>
@@ -29881,13 +29878,13 @@
         <v>0</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="O1" s="11" t="s">
         <v>1692</v>
       </c>
       <c r="P1" s="31" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="7" customFormat="1">
@@ -29904,10 +29901,10 @@
         <v>2.0000000000000001E-101</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>1652</v>
@@ -29923,7 +29920,7 @@
         <v>20</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>1682</v>
@@ -29951,10 +29948,10 @@
         <v>2.0000000000000001E-101</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>1652</v>
@@ -29970,7 +29967,7 @@
         <v>21</v>
       </c>
       <c r="N3" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>1650</v>
@@ -29993,10 +29990,10 @@
         <v>1691</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>1652</v>
@@ -30012,7 +30009,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>1653</v>
@@ -30036,10 +30033,10 @@
         <v>1691</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>1652</v>
@@ -30055,7 +30052,7 @@
         <v>27</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>1671</v>
@@ -30078,10 +30075,10 @@
         <v>1688</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>1652</v>
@@ -30097,7 +30094,7 @@
         <v>70</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>1653</v>
@@ -30120,10 +30117,10 @@
         <v>1688</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>1652</v>
@@ -30139,7 +30136,7 @@
         <v>72</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>1671</v>
@@ -30162,10 +30159,10 @@
         <v>1687</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G8" s="25" t="s">
         <v>1652</v>
@@ -30181,7 +30178,7 @@
         <v>70</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>1653</v>
@@ -30204,10 +30201,10 @@
         <v>1687</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>1652</v>
@@ -30223,7 +30220,7 @@
         <v>72</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>1671</v>
@@ -30246,10 +30243,10 @@
         <v>1686</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>1652</v>
@@ -30265,7 +30262,7 @@
         <v>75</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>1653</v>
@@ -30288,10 +30285,10 @@
         <v>1686</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G11" s="25" t="s">
         <v>1652</v>
@@ -30307,7 +30304,7 @@
         <v>77</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>1671</v>
@@ -30330,10 +30327,10 @@
         <v>1685</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G12" s="25" t="s">
         <v>1652</v>
@@ -30349,7 +30346,7 @@
         <v>75</v>
       </c>
       <c r="N12" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>1653</v>
@@ -30372,10 +30369,10 @@
         <v>1685</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>1652</v>
@@ -30391,7 +30388,7 @@
         <v>77</v>
       </c>
       <c r="N13" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>1671</v>
@@ -30414,10 +30411,10 @@
         <v>1684</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>1652</v>
@@ -30433,7 +30430,7 @@
         <v>119</v>
       </c>
       <c r="N14" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>1653</v>
@@ -30457,10 +30454,10 @@
         <v>1684</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>1652</v>
@@ -30476,7 +30473,7 @@
         <v>120</v>
       </c>
       <c r="N15" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>1671</v>
@@ -30499,10 +30496,10 @@
         <v>1683</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>1652</v>
@@ -30518,7 +30515,7 @@
         <v>122</v>
       </c>
       <c r="N16" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O16" s="24" t="s">
         <v>1682</v>
@@ -30541,10 +30538,10 @@
         <v>1683</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>1652</v>
@@ -30560,7 +30557,7 @@
         <v>123</v>
       </c>
       <c r="N17" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O17" s="24" t="s">
         <v>1650</v>
@@ -30584,10 +30581,10 @@
         <v>1689</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>1652</v>
@@ -30603,7 +30600,7 @@
         <v>230</v>
       </c>
       <c r="N18" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O18" s="8" t="s">
         <v>1653</v>
@@ -30626,10 +30623,10 @@
         <v>1689</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>1652</v>
@@ -30645,7 +30642,7 @@
         <v>231</v>
       </c>
       <c r="N19" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O19" s="8" t="s">
         <v>1671</v>
@@ -30668,10 +30665,10 @@
         <v>1690</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>1652</v>
@@ -30687,7 +30684,7 @@
         <v>236</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O20" s="24" t="s">
         <v>1653</v>
@@ -30711,10 +30708,10 @@
         <v>1690</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>1652</v>
@@ -30730,7 +30727,7 @@
         <v>187</v>
       </c>
       <c r="N21" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O21" s="24" t="s">
         <v>1671</v>
@@ -30756,7 +30753,7 @@
         <v>1722</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>1652</v>
@@ -30770,7 +30767,7 @@
       <c r="L22" s="26"/>
       <c r="M22" s="22"/>
       <c r="N22" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O22" s="24" t="s">
         <v>1682</v>
@@ -30796,7 +30793,7 @@
         <v>1722</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>1652</v>
@@ -30810,7 +30807,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="22"/>
       <c r="N23" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O23" s="24" t="s">
         <v>1650</v>
@@ -30837,7 +30834,7 @@
         <v>1694</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G24" s="26"/>
       <c r="H24" s="26"/>
@@ -30847,7 +30844,7 @@
       <c r="L24" s="26"/>
       <c r="M24" s="22"/>
       <c r="N24" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O24" s="24"/>
       <c r="P24" s="28">
@@ -30871,7 +30868,7 @@
         <v>1722</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>1652</v>
@@ -30885,7 +30882,7 @@
       <c r="L25" s="26"/>
       <c r="M25" s="22"/>
       <c r="N25" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O25" s="24" t="s">
         <v>1653</v>
@@ -30911,7 +30908,7 @@
         <v>1722</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>1652</v>
@@ -30925,7 +30922,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="22"/>
       <c r="N26" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O26" s="24" t="s">
         <v>1671</v>
@@ -30951,7 +30948,7 @@
         <v>1694</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G27" s="26"/>
       <c r="H27" s="26"/>
@@ -30961,7 +30958,7 @@
       <c r="L27" s="26"/>
       <c r="M27" s="22"/>
       <c r="N27" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O27" s="24"/>
       <c r="P27" s="28">
@@ -30985,7 +30982,7 @@
         <v>1722</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>1652</v>
@@ -30999,7 +30996,7 @@
       <c r="L28" s="26"/>
       <c r="M28" s="22"/>
       <c r="N28" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O28" s="24" t="s">
         <v>1671</v>
@@ -31025,7 +31022,7 @@
         <v>1722</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>1652</v>
@@ -31039,7 +31036,7 @@
       <c r="L29" s="21"/>
       <c r="M29" s="22"/>
       <c r="N29" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O29" s="24" t="s">
         <v>1700</v>
@@ -31065,7 +31062,7 @@
         <v>1694</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="26"/>
@@ -31075,7 +31072,7 @@
       <c r="L30" s="26"/>
       <c r="M30" s="22"/>
       <c r="N30" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O30" s="24"/>
       <c r="P30" s="28">
@@ -31099,7 +31096,7 @@
         <v>1722</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>1652</v>
@@ -31113,7 +31110,7 @@
       <c r="L31" s="26"/>
       <c r="M31" s="22"/>
       <c r="N31" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O31" s="24" t="s">
         <v>1653</v>
@@ -31139,7 +31136,7 @@
         <v>1722</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>1652</v>
@@ -31153,7 +31150,7 @@
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
       <c r="N32" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O32" s="24" t="s">
         <v>1671</v>
@@ -31181,7 +31178,7 @@
         <v>1694</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
@@ -31191,7 +31188,7 @@
       <c r="L33" s="26"/>
       <c r="M33" s="22"/>
       <c r="N33" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O33" s="24"/>
       <c r="P33" s="28">
@@ -31218,10 +31215,10 @@
         <v>1681</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G34" s="25" t="s">
         <v>1652</v>
@@ -31237,7 +31234,7 @@
         <v>627</v>
       </c>
       <c r="N34" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O34" s="8" t="s">
         <v>1653</v>
@@ -31266,10 +31263,10 @@
         <v>1681</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G35" s="25" t="s">
         <v>1652</v>
@@ -31285,7 +31282,7 @@
         <v>628</v>
       </c>
       <c r="N35" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O35" s="8" t="s">
         <v>1650</v>
@@ -31310,10 +31307,10 @@
         <v>1680</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G36" s="25" t="s">
         <v>1652</v>
@@ -31329,7 +31326,7 @@
         <v>627</v>
       </c>
       <c r="N36" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O36" s="8" t="s">
         <v>1653</v>
@@ -31358,10 +31355,10 @@
         <v>1680</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G37" s="25" t="s">
         <v>1652</v>
@@ -31377,7 +31374,7 @@
         <v>628</v>
       </c>
       <c r="N37" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O37" s="8" t="s">
         <v>1650</v>
@@ -31406,10 +31403,10 @@
         <v>1679</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G38" s="26" t="s">
         <v>1652</v>
@@ -31425,7 +31422,7 @@
         <v>648</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O38" s="24" t="s">
         <v>1653</v>
@@ -31448,10 +31445,10 @@
         <v>1679</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>1652</v>
@@ -31467,7 +31464,7 @@
         <v>649</v>
       </c>
       <c r="N39" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O39" s="24" t="s">
         <v>1650</v>
@@ -31490,10 +31487,10 @@
         <v>1678</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>1652</v>
@@ -31509,7 +31506,7 @@
         <v>648</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O40" s="24" t="s">
         <v>1653</v>
@@ -31532,10 +31529,10 @@
         <v>1678</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>1652</v>
@@ -31551,7 +31548,7 @@
         <v>649</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O41" s="24" t="s">
         <v>1650</v>
@@ -31574,10 +31571,10 @@
         <v>1677</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G42" s="25" t="s">
         <v>1652</v>
@@ -31593,7 +31590,7 @@
         <v>1676</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O42" s="8" t="s">
         <v>1672</v>
@@ -31616,10 +31613,10 @@
         <v>1677</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G43" s="25" t="s">
         <v>1652</v>
@@ -31635,7 +31632,7 @@
         <v>1675</v>
       </c>
       <c r="N43" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O43" s="8" t="s">
         <v>1671</v>
@@ -31658,10 +31655,10 @@
         <v>1674</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G44" s="25" t="s">
         <v>1652</v>
@@ -31677,7 +31674,7 @@
         <v>653</v>
       </c>
       <c r="N44" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O44" s="8" t="s">
         <v>1653</v>
@@ -31702,10 +31699,10 @@
         <v>1674</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G45" s="25" t="s">
         <v>1652</v>
@@ -31721,7 +31718,7 @@
         <v>655</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O45" s="8" t="s">
         <v>1650</v>
@@ -31748,10 +31745,10 @@
         <v>1673</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G46" s="25" t="s">
         <v>1652</v>
@@ -31767,7 +31764,7 @@
         <v>686</v>
       </c>
       <c r="N46" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O46" s="8" t="s">
         <v>1672</v>
@@ -31794,10 +31791,10 @@
         <v>1673</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G47" s="25" t="s">
         <v>1652</v>
@@ -31813,7 +31810,7 @@
         <v>688</v>
       </c>
       <c r="N47" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O47" s="8" t="s">
         <v>1671</v>
@@ -31838,10 +31835,10 @@
         <v>1670</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G48" s="25" t="s">
         <v>1652</v>
@@ -31857,7 +31854,7 @@
         <v>692</v>
       </c>
       <c r="N48" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O48" s="8" t="s">
         <v>1653</v>
@@ -31884,10 +31881,10 @@
         <v>1670</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G49" s="25" t="s">
         <v>1652</v>
@@ -31903,7 +31900,7 @@
         <v>693</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O49" s="8" t="s">
         <v>1650</v>
@@ -31930,10 +31927,10 @@
         <v>1666</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G50" s="25" t="s">
         <v>1652</v>
@@ -31949,7 +31946,7 @@
         <v>926</v>
       </c>
       <c r="N50" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O50" s="8" t="s">
         <v>1653</v>
@@ -31972,10 +31969,10 @@
         <v>1666</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G51" s="25" t="s">
         <v>1652</v>
@@ -31991,7 +31988,7 @@
         <v>927</v>
       </c>
       <c r="N51" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O51" s="8" t="s">
         <v>1650</v>
@@ -32015,10 +32012,10 @@
         <v>1669</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>1652</v>
@@ -32034,7 +32031,7 @@
         <v>866</v>
       </c>
       <c r="N52" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O52" s="24" t="s">
         <v>1653</v>
@@ -32058,10 +32055,10 @@
         <v>1669</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>1652</v>
@@ -32077,7 +32074,7 @@
         <v>867</v>
       </c>
       <c r="N53" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O53" s="24" t="s">
         <v>1650</v>
@@ -32100,10 +32097,10 @@
         <v>1668</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F54" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>1652</v>
@@ -32119,7 +32116,7 @@
         <v>869</v>
       </c>
       <c r="N54" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O54" s="24" t="s">
         <v>1653</v>
@@ -32142,10 +32139,10 @@
         <v>1668</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>1652</v>
@@ -32161,7 +32158,7 @@
         <v>867</v>
       </c>
       <c r="N55" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O55" s="24" t="s">
         <v>1650</v>
@@ -32184,10 +32181,10 @@
         <v>1667</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>1652</v>
@@ -32203,7 +32200,7 @@
         <v>870</v>
       </c>
       <c r="N56" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O56" s="8" t="s">
         <v>1653</v>
@@ -32226,10 +32223,10 @@
         <v>1667</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>1652</v>
@@ -32245,7 +32242,7 @@
         <v>48</v>
       </c>
       <c r="N57" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O57" s="8" t="s">
         <v>1650</v>
@@ -32271,7 +32268,7 @@
         <v>1722</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>1696</v>
@@ -32285,7 +32282,7 @@
       <c r="L58" s="26"/>
       <c r="M58" s="22"/>
       <c r="N58" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O58" s="24" t="s">
         <v>1682</v>
@@ -32311,7 +32308,7 @@
         <v>1722</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>1696</v>
@@ -32325,7 +32322,7 @@
       <c r="L59" s="21"/>
       <c r="M59" s="22"/>
       <c r="N59" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O59" s="24" t="s">
         <v>1650</v>
@@ -32351,7 +32348,7 @@
         <v>1694</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>1696</v>
@@ -32363,7 +32360,7 @@
       <c r="L60" s="26"/>
       <c r="M60" s="22"/>
       <c r="N60" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O60" s="24"/>
       <c r="P60" s="28">
@@ -32387,7 +32384,7 @@
         <v>1722</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>1696</v>
@@ -32401,7 +32398,7 @@
       <c r="L61" s="26"/>
       <c r="M61" s="22"/>
       <c r="N61" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O61" s="24" t="s">
         <v>1682</v>
@@ -32427,7 +32424,7 @@
         <v>1722</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>1696</v>
@@ -32441,7 +32438,7 @@
       <c r="L62" s="21"/>
       <c r="M62" s="22"/>
       <c r="N62" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O62" s="24" t="s">
         <v>1650</v>
@@ -32467,7 +32464,7 @@
         <v>1694</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>1696</v>
@@ -32479,7 +32476,7 @@
       <c r="L63" s="26"/>
       <c r="M63" s="22"/>
       <c r="N63" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O63" s="24"/>
       <c r="P63" s="28">
@@ -32503,7 +32500,7 @@
         <v>1722</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>1652</v>
@@ -32517,7 +32514,7 @@
       <c r="L64" s="26"/>
       <c r="M64" s="22"/>
       <c r="N64" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O64" s="24" t="s">
         <v>1653</v>
@@ -32543,7 +32540,7 @@
         <v>1722</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>1652</v>
@@ -32557,7 +32554,7 @@
       <c r="L65" s="21"/>
       <c r="M65" s="22"/>
       <c r="N65" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O65" s="24" t="s">
         <v>1650</v>
@@ -32583,7 +32580,7 @@
         <v>1695</v>
       </c>
       <c r="F66" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G66" s="26" t="s">
         <v>1652</v>
@@ -32595,7 +32592,7 @@
       <c r="L66" s="21"/>
       <c r="M66" s="22"/>
       <c r="N66" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O66" s="20"/>
       <c r="P66" s="28">
@@ -32619,7 +32616,7 @@
         <v>1694</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>1652</v>
@@ -32631,7 +32628,7 @@
       <c r="L67" s="26"/>
       <c r="M67" s="22"/>
       <c r="N67" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O67" s="24"/>
       <c r="P67" s="28">
@@ -32655,7 +32652,7 @@
         <v>1694</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>1652</v>
@@ -32667,7 +32664,7 @@
       <c r="L68" s="21"/>
       <c r="M68" s="22"/>
       <c r="N68" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O68" s="20"/>
       <c r="P68" s="28">
@@ -32691,7 +32688,7 @@
         <v>1722</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>1652</v>
@@ -32705,7 +32702,7 @@
       <c r="L69" s="26"/>
       <c r="M69" s="22"/>
       <c r="N69" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O69" s="24" t="s">
         <v>1653</v>
@@ -32731,7 +32728,7 @@
         <v>1722</v>
       </c>
       <c r="F70" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>1652</v>
@@ -32745,7 +32742,7 @@
       <c r="L70" s="21"/>
       <c r="M70" s="22"/>
       <c r="N70" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O70" s="24" t="s">
         <v>1650</v>
@@ -32771,7 +32768,7 @@
         <v>1695</v>
       </c>
       <c r="F71" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>1652</v>
@@ -32783,7 +32780,7 @@
       <c r="L71" s="21"/>
       <c r="M71" s="22"/>
       <c r="N71" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O71" s="20"/>
       <c r="P71" s="28">
@@ -32807,7 +32804,7 @@
         <v>1694</v>
       </c>
       <c r="F72" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>1652</v>
@@ -32819,7 +32816,7 @@
       <c r="L72" s="26"/>
       <c r="M72" s="22"/>
       <c r="N72" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O72" s="24"/>
       <c r="P72" s="28">
@@ -32843,7 +32840,7 @@
         <v>1694</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>1652</v>
@@ -32855,7 +32852,7 @@
       <c r="L73" s="21"/>
       <c r="M73" s="22"/>
       <c r="N73" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O73" s="20"/>
       <c r="P73" s="28">
@@ -32879,7 +32876,7 @@
         <v>1722</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>1652</v>
@@ -32893,7 +32890,7 @@
       <c r="L74" s="26"/>
       <c r="M74" s="22"/>
       <c r="N74" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O74" s="24" t="s">
         <v>1653</v>
@@ -32919,7 +32916,7 @@
         <v>1722</v>
       </c>
       <c r="F75" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>1652</v>
@@ -32933,7 +32930,7 @@
       <c r="L75" s="21"/>
       <c r="M75" s="22"/>
       <c r="N75" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O75" s="24" t="s">
         <v>1650</v>
@@ -32959,7 +32956,7 @@
         <v>1695</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>1652</v>
@@ -32971,7 +32968,7 @@
       <c r="L76" s="21"/>
       <c r="M76" s="22"/>
       <c r="N76" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O76" s="20"/>
       <c r="P76" s="28">
@@ -32995,7 +32992,7 @@
         <v>1694</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>1652</v>
@@ -33007,7 +33004,7 @@
       <c r="L77" s="26"/>
       <c r="M77" s="22"/>
       <c r="N77" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O77" s="24"/>
       <c r="P77" s="28">
@@ -33028,10 +33025,10 @@
         <v>1665</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>1652</v>
@@ -33047,7 +33044,7 @@
         <v>1343</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O78" s="24" t="s">
         <v>1653</v>
@@ -33070,10 +33067,10 @@
         <v>1665</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>1652</v>
@@ -33089,7 +33086,7 @@
         <v>1344</v>
       </c>
       <c r="N79" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O79" s="24" t="s">
         <v>1650</v>
@@ -33112,10 +33109,10 @@
         <v>1664</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>1652</v>
@@ -33131,7 +33128,7 @@
         <v>1343</v>
       </c>
       <c r="N80" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O80" s="24" t="s">
         <v>1653</v>
@@ -33154,10 +33151,10 @@
         <v>1664</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>1652</v>
@@ -33173,7 +33170,7 @@
         <v>1344</v>
       </c>
       <c r="N81" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O81" s="24" t="s">
         <v>1650</v>
@@ -33196,10 +33193,10 @@
         <v>1663</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>1652</v>
@@ -33215,7 +33212,7 @@
         <v>1343</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O82" s="24" t="s">
         <v>1653</v>
@@ -33238,10 +33235,10 @@
         <v>1663</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>1652</v>
@@ -33257,7 +33254,7 @@
         <v>1344</v>
       </c>
       <c r="N83" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O83" s="24" t="s">
         <v>1650</v>
@@ -33280,10 +33277,10 @@
         <v>1662</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G84" s="26" t="s">
         <v>1652</v>
@@ -33299,7 +33296,7 @@
         <v>1343</v>
       </c>
       <c r="N84" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O84" s="24" t="s">
         <v>1653</v>
@@ -33322,10 +33319,10 @@
         <v>1662</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F85" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>1652</v>
@@ -33341,7 +33338,7 @@
         <v>1344</v>
       </c>
       <c r="N85" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O85" s="24" t="s">
         <v>1650</v>
@@ -33364,10 +33361,10 @@
         <v>1661</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F86" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G86" s="26" t="s">
         <v>1652</v>
@@ -33383,7 +33380,7 @@
         <v>1355</v>
       </c>
       <c r="N86" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O86" s="24" t="s">
         <v>1653</v>
@@ -33406,10 +33403,10 @@
         <v>1661</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G87" s="26" t="s">
         <v>1652</v>
@@ -33425,7 +33422,7 @@
         <v>1356</v>
       </c>
       <c r="N87" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O87" s="24" t="s">
         <v>1650</v>
@@ -33448,10 +33445,10 @@
         <v>1660</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>1652</v>
@@ -33467,7 +33464,7 @@
         <v>1355</v>
       </c>
       <c r="N88" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O88" s="24" t="s">
         <v>1653</v>
@@ -33490,10 +33487,10 @@
         <v>1660</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>1652</v>
@@ -33509,7 +33506,7 @@
         <v>1356</v>
       </c>
       <c r="N89" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O89" s="24" t="s">
         <v>1650</v>
@@ -33532,10 +33529,10 @@
         <v>1659</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>1652</v>
@@ -33551,7 +33548,7 @@
         <v>1363</v>
       </c>
       <c r="N90" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O90" s="24" t="s">
         <v>1653</v>
@@ -33574,10 +33571,10 @@
         <v>1659</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F91" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>1652</v>
@@ -33593,7 +33590,7 @@
         <v>1364</v>
       </c>
       <c r="N91" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O91" s="24" t="s">
         <v>1650</v>
@@ -33616,10 +33613,10 @@
         <v>1658</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F92" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G92" s="26" t="s">
         <v>1652</v>
@@ -33635,7 +33632,7 @@
         <v>1363</v>
       </c>
       <c r="N92" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O92" s="24" t="s">
         <v>1653</v>
@@ -33658,10 +33655,10 @@
         <v>1658</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F93" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G93" s="26" t="s">
         <v>1652</v>
@@ -33677,7 +33674,7 @@
         <v>1364</v>
       </c>
       <c r="N93" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O93" s="24" t="s">
         <v>1650</v>
@@ -33700,10 +33697,10 @@
         <v>1657</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F94" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>1652</v>
@@ -33719,7 +33716,7 @@
         <v>1371</v>
       </c>
       <c r="N94" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O94" s="24" t="s">
         <v>1653</v>
@@ -33742,10 +33739,10 @@
         <v>1657</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F95" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>1652</v>
@@ -33761,7 +33758,7 @@
         <v>1372</v>
       </c>
       <c r="N95" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O95" s="24" t="s">
         <v>1650</v>
@@ -33784,10 +33781,10 @@
         <v>1656</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G96" s="26" t="s">
         <v>1652</v>
@@ -33803,7 +33800,7 @@
         <v>1371</v>
       </c>
       <c r="N96" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O96" s="24" t="s">
         <v>1653</v>
@@ -33826,10 +33823,10 @@
         <v>1656</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>1652</v>
@@ -33845,7 +33842,7 @@
         <v>1372</v>
       </c>
       <c r="N97" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O97" s="24" t="s">
         <v>1650</v>
@@ -33868,10 +33865,10 @@
         <v>1382</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>1652</v>
@@ -33887,7 +33884,7 @@
         <v>1655</v>
       </c>
       <c r="N98" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O98" s="24" t="s">
         <v>1653</v>
@@ -33910,10 +33907,10 @@
         <v>1382</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>1652</v>
@@ -33929,7 +33926,7 @@
         <v>1655</v>
       </c>
       <c r="N99" s="25" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="O99" s="24" t="s">
         <v>1650</v>
@@ -43416,7 +43413,7 @@
       <c r="K323" s="21"/>
       <c r="L323" s="21"/>
       <c r="M323" s="22" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="N323" s="21" t="s">
         <v>1693</v>

--- a/HE_Database_PRO_FINAL.xlsx
+++ b/HE_Database_PRO_FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7358DEBA-9627-4413-87E6-6A7F82E4D318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A8CDC7-60D1-4B70-B1F3-A3E274A34719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7506" uniqueCount="2132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7506" uniqueCount="2134">
   <si>
     <t>Description</t>
   </si>
@@ -6494,6 +6494,12 @@
   </si>
   <si>
     <t>Tube Spec</t>
+  </si>
+  <si>
+    <t>U-Tube</t>
+  </si>
+  <si>
+    <t>EQ_2</t>
   </si>
 </sst>
 </file>
@@ -6669,7 +6675,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6767,6 +6773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{1349ADF5-E515-4D3F-9155-9418A0285C0F}"/>
@@ -8334,8 +8341,8 @@
       <c r="A16" s="16">
         <v>2.0000000000000001E-203</v>
       </c>
-      <c r="B16" t="s">
-        <v>1759</v>
+      <c r="B16" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>206</v>
@@ -8464,8 +8471,8 @@
       <c r="A18" s="16">
         <v>2E-132</v>
       </c>
-      <c r="B18" t="s">
-        <v>1759</v>
+      <c r="B18" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>188</v>
@@ -8594,8 +8601,8 @@
       <c r="A20" s="16">
         <v>2.0000000000000002E-130</v>
       </c>
-      <c r="B20" t="s">
-        <v>1759</v>
+      <c r="B20" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>174</v>
@@ -10860,8 +10867,8 @@
       <c r="A55" s="16" t="s">
         <v>1960</v>
       </c>
-      <c r="B55" t="s">
-        <v>1759</v>
+      <c r="B55" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>326</v>
@@ -11247,8 +11254,8 @@
       <c r="A61" s="16" t="s">
         <v>2047</v>
       </c>
-      <c r="B61" t="s">
-        <v>1759</v>
+      <c r="B61" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>198</v>
@@ -11312,8 +11319,8 @@
       <c r="A62" s="16" t="s">
         <v>2048</v>
       </c>
-      <c r="B62" t="s">
-        <v>1759</v>
+      <c r="B62" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>198</v>
@@ -11377,8 +11384,8 @@
       <c r="A63" s="16" t="s">
         <v>2037</v>
       </c>
-      <c r="B63" t="s">
-        <v>1759</v>
+      <c r="B63" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>221</v>
@@ -11442,8 +11449,8 @@
       <c r="A64" s="16" t="s">
         <v>2013</v>
       </c>
-      <c r="B64" t="s">
-        <v>1759</v>
+      <c r="B64" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>226</v>
@@ -11767,8 +11774,8 @@
       <c r="A69" s="16" t="s">
         <v>1945</v>
       </c>
-      <c r="B69" t="s">
-        <v>1759</v>
+      <c r="B69" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>362</v>
@@ -12222,8 +12229,8 @@
       <c r="A76" s="16" t="s">
         <v>1994</v>
       </c>
-      <c r="B76" t="s">
-        <v>1759</v>
+      <c r="B76" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>395</v>
@@ -12733,8 +12740,8 @@
       <c r="A84" s="16" t="s">
         <v>1995</v>
       </c>
-      <c r="B84" t="s">
-        <v>1759</v>
+      <c r="B84" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>395</v>
@@ -12922,8 +12929,8 @@
       <c r="A87" s="16" t="s">
         <v>1907</v>
       </c>
-      <c r="B87" t="s">
-        <v>1759</v>
+      <c r="B87" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>419</v>
@@ -12987,8 +12994,8 @@
       <c r="A88" s="16" t="s">
         <v>1963</v>
       </c>
-      <c r="B88" t="s">
-        <v>1759</v>
+      <c r="B88" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>429</v>
@@ -13052,8 +13059,8 @@
       <c r="A89" s="16" t="s">
         <v>1971</v>
       </c>
-      <c r="B89" t="s">
-        <v>1759</v>
+      <c r="B89" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>436</v>
@@ -13235,8 +13242,8 @@
       <c r="A92" s="16" t="s">
         <v>1970</v>
       </c>
-      <c r="B92" t="s">
-        <v>1759</v>
+      <c r="B92" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>458</v>
@@ -13300,8 +13307,8 @@
       <c r="A93" s="16" t="s">
         <v>1987</v>
       </c>
-      <c r="B93" t="s">
-        <v>1759</v>
+      <c r="B93" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>465</v>
@@ -13365,8 +13372,8 @@
       <c r="A94" s="16" t="s">
         <v>1964</v>
       </c>
-      <c r="B94" t="s">
-        <v>1759</v>
+      <c r="B94" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>473</v>
@@ -13430,8 +13437,8 @@
       <c r="A95" s="16" t="s">
         <v>1894</v>
       </c>
-      <c r="B95" t="s">
-        <v>1644</v>
+      <c r="B95" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>479</v>
@@ -13495,8 +13502,8 @@
       <c r="A96" s="16" t="s">
         <v>1988</v>
       </c>
-      <c r="B96" t="s">
-        <v>1759</v>
+      <c r="B96" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>482</v>
@@ -13560,8 +13567,8 @@
       <c r="A97" s="16" t="s">
         <v>1952</v>
       </c>
-      <c r="B97" t="s">
-        <v>1759</v>
+      <c r="B97" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>490</v>
@@ -13690,8 +13697,8 @@
       <c r="A99" s="16" t="s">
         <v>1953</v>
       </c>
-      <c r="B99" t="s">
-        <v>1759</v>
+      <c r="B99" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>503</v>
@@ -14015,8 +14022,8 @@
       <c r="A104" s="16" t="s">
         <v>1917</v>
       </c>
-      <c r="B104" t="s">
-        <v>1759</v>
+      <c r="B104" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>508</v>
@@ -14080,8 +14087,8 @@
       <c r="A105" s="16" t="s">
         <v>1918</v>
       </c>
-      <c r="B105" t="s">
-        <v>1759</v>
+      <c r="B105" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>508</v>
@@ -14145,8 +14152,8 @@
       <c r="A106" s="16" t="s">
         <v>1919</v>
       </c>
-      <c r="B106" t="s">
-        <v>1759</v>
+      <c r="B106" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>508</v>
@@ -14210,8 +14217,8 @@
       <c r="A107" s="16" t="s">
         <v>1924</v>
       </c>
-      <c r="B107" t="s">
-        <v>1759</v>
+      <c r="B107" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>515</v>
@@ -14275,8 +14282,8 @@
       <c r="A108" s="16" t="s">
         <v>1925</v>
       </c>
-      <c r="B108" t="s">
-        <v>1759</v>
+      <c r="B108" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>515</v>
@@ -14340,8 +14347,8 @@
       <c r="A109" s="16" t="s">
         <v>1926</v>
       </c>
-      <c r="B109" t="s">
-        <v>1759</v>
+      <c r="B109" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>515</v>
@@ -15145,8 +15152,8 @@
       <c r="A123" s="16" t="s">
         <v>2019</v>
       </c>
-      <c r="B123" t="s">
-        <v>1759</v>
+      <c r="B123" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>315</v>
@@ -15275,8 +15282,8 @@
       <c r="A125" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="B125" t="s">
-        <v>1759</v>
+      <c r="B125" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>315</v>
@@ -15340,8 +15347,8 @@
       <c r="A126" s="16">
         <v>2.9999999999999999E-307</v>
       </c>
-      <c r="B126" t="s">
-        <v>1759</v>
+      <c r="B126" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>827</v>
@@ -15535,8 +15542,8 @@
       <c r="A129" s="16">
         <v>3.0000000000000003E-303</v>
       </c>
-      <c r="B129" t="s">
-        <v>1759</v>
+      <c r="B129" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>802</v>
@@ -16001,8 +16008,8 @@
       <c r="A137" s="16">
         <v>2.9999999999999999E-125</v>
       </c>
-      <c r="B137" t="s">
-        <v>1759</v>
+      <c r="B137" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>712</v>
@@ -16586,8 +16593,8 @@
       <c r="A146" s="16">
         <v>3.0000000000000002E-114</v>
       </c>
-      <c r="B146" t="s">
-        <v>1759</v>
+      <c r="B146" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>656</v>
@@ -17171,8 +17178,8 @@
       <c r="A155" s="17" t="s">
         <v>2064</v>
       </c>
-      <c r="B155" t="s">
-        <v>1759</v>
+      <c r="B155" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>576</v>
@@ -19316,8 +19323,8 @@
       <c r="A188" s="16" t="s">
         <v>2029</v>
       </c>
-      <c r="B188" t="s">
-        <v>1759</v>
+      <c r="B188" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>731</v>
@@ -19381,8 +19388,8 @@
       <c r="A189" s="16" t="s">
         <v>2030</v>
       </c>
-      <c r="B189" t="s">
-        <v>1759</v>
+      <c r="B189" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>731</v>
@@ -19446,8 +19453,8 @@
       <c r="A190" s="16" t="s">
         <v>2024</v>
       </c>
-      <c r="B190" t="s">
-        <v>1759</v>
+      <c r="B190" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>739</v>
@@ -19511,8 +19518,8 @@
       <c r="A191" s="16" t="s">
         <v>2025</v>
       </c>
-      <c r="B191" t="s">
-        <v>1759</v>
+      <c r="B191" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>739</v>
@@ -20356,8 +20363,8 @@
       <c r="A204" s="16" t="s">
         <v>1989</v>
       </c>
-      <c r="B204" t="s">
-        <v>1759</v>
+      <c r="B204" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>796</v>
@@ -20421,8 +20428,8 @@
       <c r="A205" s="16" t="s">
         <v>1990</v>
       </c>
-      <c r="B205" t="s">
-        <v>1759</v>
+      <c r="B205" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>796</v>
@@ -20757,8 +20764,8 @@
       <c r="A211" s="16" t="s">
         <v>1927</v>
       </c>
-      <c r="B211" t="s">
-        <v>1759</v>
+      <c r="B211" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>957</v>
@@ -20822,8 +20829,8 @@
       <c r="A212" s="16" t="s">
         <v>1928</v>
       </c>
-      <c r="B212" t="s">
-        <v>1759</v>
+      <c r="B212" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>957</v>
@@ -20887,8 +20894,8 @@
       <c r="A213" s="16" t="s">
         <v>1929</v>
       </c>
-      <c r="B213" t="s">
-        <v>1759</v>
+      <c r="B213" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>965</v>
@@ -20952,8 +20959,8 @@
       <c r="A214" s="16" t="s">
         <v>1921</v>
       </c>
-      <c r="B214" t="s">
-        <v>1759</v>
+      <c r="B214" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>966</v>
@@ -21017,8 +21024,8 @@
       <c r="A215" s="16" t="s">
         <v>1920</v>
       </c>
-      <c r="B215" t="s">
-        <v>1759</v>
+      <c r="B215" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>974</v>
@@ -22452,8 +22459,8 @@
       <c r="A238" s="16" t="s">
         <v>2027</v>
       </c>
-      <c r="B238" t="s">
-        <v>1759</v>
+      <c r="B238" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>858</v>
@@ -23025,8 +23032,8 @@
       <c r="A247" s="16" t="s">
         <v>1901</v>
       </c>
-      <c r="B247" t="s">
-        <v>1759</v>
+      <c r="B247" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>886</v>
@@ -23090,8 +23097,8 @@
       <c r="A248" s="16" t="s">
         <v>1997</v>
       </c>
-      <c r="B248" t="s">
-        <v>1759</v>
+      <c r="B248" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>315</v>
@@ -23220,8 +23227,8 @@
       <c r="A250" s="16" t="s">
         <v>1961</v>
       </c>
-      <c r="B250" t="s">
-        <v>1759</v>
+      <c r="B250" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>900</v>
@@ -23285,8 +23292,8 @@
       <c r="A251" s="16" t="s">
         <v>1962</v>
       </c>
-      <c r="B251" t="s">
-        <v>1759</v>
+      <c r="B251" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>906</v>
@@ -23350,8 +23357,8 @@
       <c r="A252" s="16">
         <v>3.9999999999999999E-121</v>
       </c>
-      <c r="B252" t="s">
-        <v>1759</v>
+      <c r="B252" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>1188</v>
@@ -23415,8 +23422,8 @@
       <c r="A253" s="16">
         <v>3.9999999999999999E-120</v>
       </c>
-      <c r="B253" t="s">
-        <v>1759</v>
+      <c r="B253" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>1182</v>
@@ -23480,8 +23487,8 @@
       <c r="A254" s="16">
         <v>4.0000000000000001E-119</v>
       </c>
-      <c r="B254" t="s">
-        <v>1759</v>
+      <c r="B254" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>1175</v>
@@ -23545,8 +23552,8 @@
       <c r="A255" s="16">
         <v>3.9999999999999999E-118</v>
       </c>
-      <c r="B255" t="s">
-        <v>1759</v>
+      <c r="B255" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>1168</v>
@@ -23610,8 +23617,8 @@
       <c r="A256" s="16">
         <v>4.0000000000000001E-117</v>
       </c>
-      <c r="B256" t="s">
-        <v>1759</v>
+      <c r="B256" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>1162</v>
@@ -23675,8 +23682,8 @@
       <c r="A257" s="16">
         <v>4E-116</v>
       </c>
-      <c r="B257" t="s">
-        <v>1759</v>
+      <c r="B257" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>1154</v>
@@ -23740,8 +23747,8 @@
       <c r="A258" s="16">
         <v>4.0000000000000002E-115</v>
       </c>
-      <c r="B258" t="s">
-        <v>1759</v>
+      <c r="B258" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>1147</v>
@@ -23870,8 +23877,8 @@
       <c r="A260" s="16">
         <v>3.9999999999999999E-113</v>
       </c>
-      <c r="B260" t="s">
-        <v>1759</v>
+      <c r="B260" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>188</v>
@@ -23935,8 +23942,8 @@
       <c r="A261" s="16">
         <v>3.9999999999999998E-112</v>
       </c>
-      <c r="B261" t="s">
-        <v>1759</v>
+      <c r="B261" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>1131</v>
@@ -24000,8 +24007,8 @@
       <c r="A262" s="16">
         <v>4.0000000000000004E-111</v>
       </c>
-      <c r="B262" t="s">
-        <v>1759</v>
+      <c r="B262" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>1120</v>
@@ -24065,8 +24072,8 @@
       <c r="A263" s="16">
         <v>4.0000000000000002E-110</v>
       </c>
-      <c r="B263" t="s">
-        <v>1759</v>
+      <c r="B263" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>1113</v>
@@ -24520,8 +24527,8 @@
       <c r="A270" s="16">
         <v>3.9999999999999997E-102</v>
       </c>
-      <c r="B270" t="s">
-        <v>1759</v>
+      <c r="B270" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>1056</v>
@@ -25560,8 +25567,8 @@
       <c r="A286" s="16" t="s">
         <v>1285</v>
       </c>
-      <c r="B286" t="s">
-        <v>1759</v>
+      <c r="B286" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>1286</v>
@@ -25950,8 +25957,8 @@
       <c r="A292" s="16" t="s">
         <v>1314</v>
       </c>
-      <c r="B292" t="s">
-        <v>1759</v>
+      <c r="B292" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>1315</v>
@@ -26015,8 +26022,8 @@
       <c r="A293" s="16" t="s">
         <v>1320</v>
       </c>
-      <c r="B293" t="s">
-        <v>1759</v>
+      <c r="B293" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>1321</v>
@@ -26080,8 +26087,8 @@
       <c r="A294" s="16" t="s">
         <v>1322</v>
       </c>
-      <c r="B294" t="s">
-        <v>1759</v>
+      <c r="B294" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>1323</v>
@@ -26857,8 +26864,8 @@
       <c r="A306" s="16" t="s">
         <v>1375</v>
       </c>
-      <c r="B306" t="s">
-        <v>1759</v>
+      <c r="B306" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>1376</v>
@@ -26922,8 +26929,8 @@
       <c r="A307" s="16" t="s">
         <v>1381</v>
       </c>
-      <c r="B307" t="s">
-        <v>1759</v>
+      <c r="B307" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>1376</v>
@@ -27182,8 +27189,8 @@
       <c r="A311" s="16" t="s">
         <v>1395</v>
       </c>
-      <c r="B311" t="s">
-        <v>1759</v>
+      <c r="B311" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>1396</v>
@@ -27247,8 +27254,8 @@
       <c r="A312" s="16" t="s">
         <v>1402</v>
       </c>
-      <c r="B312" t="s">
-        <v>1759</v>
+      <c r="B312" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>1403</v>
@@ -27312,8 +27319,8 @@
       <c r="A313" s="16" t="s">
         <v>1413</v>
       </c>
-      <c r="B313" t="s">
-        <v>1759</v>
+      <c r="B313" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>1414</v>
@@ -27377,8 +27384,8 @@
       <c r="A314" s="16" t="s">
         <v>1419</v>
       </c>
-      <c r="B314" t="s">
-        <v>1759</v>
+      <c r="B314" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>1414</v>
@@ -27442,8 +27449,8 @@
       <c r="A315" s="16" t="s">
         <v>1420</v>
       </c>
-      <c r="B315" t="s">
-        <v>1759</v>
+      <c r="B315" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1414</v>
@@ -27507,8 +27514,8 @@
       <c r="A316" s="16" t="s">
         <v>1421</v>
       </c>
-      <c r="B316" t="s">
-        <v>1759</v>
+      <c r="B316" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>1422</v>
@@ -27702,8 +27709,8 @@
       <c r="A319" s="16" t="s">
         <v>1436</v>
       </c>
-      <c r="B319" t="s">
-        <v>1759</v>
+      <c r="B319" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>1437</v>
@@ -27767,8 +27774,8 @@
       <c r="A320" s="16" t="s">
         <v>1449</v>
       </c>
-      <c r="B320" t="s">
-        <v>1759</v>
+      <c r="B320" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>1437</v>
@@ -27832,8 +27839,8 @@
       <c r="A321" s="16" t="s">
         <v>1450</v>
       </c>
-      <c r="B321" t="s">
-        <v>1759</v>
+      <c r="B321" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>1451</v>
@@ -27894,8 +27901,8 @@
       <c r="A322" s="16" t="s">
         <v>1459</v>
       </c>
-      <c r="B322" t="s">
-        <v>1759</v>
+      <c r="B322" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>1460</v>
@@ -27959,8 +27966,8 @@
       <c r="A323" s="16" t="s">
         <v>1469</v>
       </c>
-      <c r="B323" t="s">
-        <v>1759</v>
+      <c r="B323" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1470</v>
@@ -28024,8 +28031,8 @@
       <c r="A324" s="16" t="s">
         <v>1477</v>
       </c>
-      <c r="B324" t="s">
-        <v>1759</v>
+      <c r="B324" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>1478</v>
@@ -28089,8 +28096,8 @@
       <c r="A325" s="16" t="s">
         <v>1488</v>
       </c>
-      <c r="B325" t="s">
-        <v>1759</v>
+      <c r="B325" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>1478</v>
@@ -28154,8 +28161,8 @@
       <c r="A326" s="16" t="s">
         <v>1489</v>
       </c>
-      <c r="B326" t="s">
-        <v>1759</v>
+      <c r="B326" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>1490</v>
@@ -28219,8 +28226,8 @@
       <c r="A327" s="16" t="s">
         <v>1501</v>
       </c>
-      <c r="B327" t="s">
-        <v>1759</v>
+      <c r="B327" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>1502</v>
@@ -28284,8 +28291,8 @@
       <c r="A328" s="16" t="s">
         <v>1511</v>
       </c>
-      <c r="B328" t="s">
-        <v>1759</v>
+      <c r="B328" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>1512</v>
@@ -28349,8 +28356,8 @@
       <c r="A329" s="16" t="s">
         <v>1521</v>
       </c>
-      <c r="B329" t="s">
-        <v>1759</v>
+      <c r="B329" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>1522</v>
@@ -28414,8 +28421,8 @@
       <c r="A330" s="16" t="s">
         <v>1530</v>
       </c>
-      <c r="B330" t="s">
-        <v>1759</v>
+      <c r="B330" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>1522</v>
@@ -28479,8 +28486,8 @@
       <c r="A331" s="16" t="s">
         <v>1533</v>
       </c>
-      <c r="B331" t="s">
-        <v>1759</v>
+      <c r="B331" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>1534</v>
@@ -28544,8 +28551,8 @@
       <c r="A332" s="16" t="s">
         <v>1542</v>
       </c>
-      <c r="B332" t="s">
-        <v>1759</v>
+      <c r="B332" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>1543</v>
@@ -28609,8 +28616,8 @@
       <c r="A333" s="16" t="s">
         <v>1549</v>
       </c>
-      <c r="B333" t="s">
-        <v>1759</v>
+      <c r="B333" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>1550</v>
@@ -28674,8 +28681,8 @@
       <c r="A334" s="16" t="s">
         <v>1560</v>
       </c>
-      <c r="B334" t="s">
-        <v>1759</v>
+      <c r="B334" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>1550</v>
@@ -28739,8 +28746,8 @@
       <c r="A335" s="16" t="s">
         <v>1561</v>
       </c>
-      <c r="B335" t="s">
-        <v>1759</v>
+      <c r="B335" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>1562</v>
@@ -28795,8 +28802,8 @@
       <c r="A336" s="16" t="s">
         <v>1568</v>
       </c>
-      <c r="B336" t="s">
-        <v>1759</v>
+      <c r="B336" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>1888</v>
@@ -28860,8 +28867,8 @@
       <c r="A337" s="16" t="s">
         <v>1575</v>
       </c>
-      <c r="B337" t="s">
-        <v>1759</v>
+      <c r="B337" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1576</v>
@@ -28925,8 +28932,8 @@
       <c r="A338" s="16" t="s">
         <v>1588</v>
       </c>
-      <c r="B338" t="s">
-        <v>1759</v>
+      <c r="B338" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>1589</v>
@@ -28990,8 +28997,8 @@
       <c r="A339" s="16" t="s">
         <v>1599</v>
       </c>
-      <c r="B339" t="s">
-        <v>1759</v>
+      <c r="B339" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>1600</v>
@@ -29055,8 +29062,8 @@
       <c r="A340" s="16" t="s">
         <v>1606</v>
       </c>
-      <c r="B340" t="s">
-        <v>1759</v>
+      <c r="B340" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1607</v>
@@ -29120,8 +29127,8 @@
       <c r="A341" s="16" t="s">
         <v>1611</v>
       </c>
-      <c r="B341" t="s">
-        <v>1759</v>
+      <c r="B341" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>1612</v>
@@ -29185,8 +29192,8 @@
       <c r="A342" s="16" t="s">
         <v>1617</v>
       </c>
-      <c r="B342" t="s">
-        <v>1759</v>
+      <c r="B342" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1618</v>
@@ -29250,8 +29257,8 @@
       <c r="A343" s="16" t="s">
         <v>1625</v>
       </c>
-      <c r="B343" t="s">
-        <v>1759</v>
+      <c r="B343" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>1203</v>
@@ -29315,8 +29322,8 @@
       <c r="A344" s="16" t="s">
         <v>1630</v>
       </c>
-      <c r="B344" t="s">
-        <v>1759</v>
+      <c r="B344" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>1203</v>
@@ -29380,8 +29387,8 @@
       <c r="A345" s="16" t="s">
         <v>1194</v>
       </c>
-      <c r="B345" t="s">
-        <v>1759</v>
+      <c r="B345" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>1195</v>
@@ -29445,8 +29452,8 @@
       <c r="A346" s="16" t="s">
         <v>1895</v>
       </c>
-      <c r="B346" t="s">
-        <v>1644</v>
+      <c r="B346" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>3</v>
@@ -29486,8 +29493,8 @@
       <c r="A347" s="16" t="s">
         <v>1896</v>
       </c>
-      <c r="B347" t="s">
-        <v>1644</v>
+      <c r="B347" s="35" t="s">
+        <v>2132</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>3</v>
@@ -29848,7 +29855,7 @@
         <v>2123</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1642</v>
+        <v>1886</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>1646</v>
@@ -29869,7 +29876,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>1886</v>
+        <v>2133</v>
       </c>
       <c r="L1" s="12" t="s">
         <v>1885</v>

--- a/HE_Database_PRO_FINAL.xlsx
+++ b/HE_Database_PRO_FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795BE033-9EDC-42E7-A5A7-38E606545CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9919167-CDA0-4D55-A214-649D684512EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7521" uniqueCount="2123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7521" uniqueCount="2122">
   <si>
     <t>Description</t>
   </si>
@@ -6305,9 +6305,6 @@
   </si>
   <si>
     <t>x</t>
-  </si>
-  <si>
-    <t>24 hr</t>
   </si>
   <si>
     <t>Pull &amp; Clean</t>
@@ -7407,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="O1" s="15" t="s">
         <v>1854</v>
@@ -7501,7 +7498,7 @@
         <v>2.9999999999999999E-307</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>827</v>
@@ -7956,7 +7953,7 @@
         <v>3.0000000000000003E-303</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>802</v>
@@ -8931,7 +8928,7 @@
         <v>2.0000000000000001E-203</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>206</v>
@@ -9072,7 +9069,7 @@
         <v>2E-132</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>188</v>
@@ -9202,7 +9199,7 @@
         <v>2.0000000000000002E-130</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>174</v>
@@ -9657,7 +9654,7 @@
         <v>2.9999999999999999E-125</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>712</v>
@@ -9982,7 +9979,7 @@
         <v>3.9999999999999999E-121</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>1188</v>
@@ -10177,7 +10174,7 @@
         <v>3.9999999999999999E-120</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>1182</v>
@@ -10372,7 +10369,7 @@
         <v>4.0000000000000001E-119</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>1175</v>
@@ -10567,7 +10564,7 @@
         <v>3.9999999999999999E-118</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>1168</v>
@@ -10762,7 +10759,7 @@
         <v>4.0000000000000001E-117</v>
       </c>
       <c r="B54" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>1162</v>
@@ -10957,7 +10954,7 @@
         <v>4E-116</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>1154</v>
@@ -11152,7 +11149,7 @@
         <v>4.0000000000000002E-115</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>1147</v>
@@ -11282,7 +11279,7 @@
         <v>3.0000000000000002E-114</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>656</v>
@@ -11542,7 +11539,7 @@
         <v>3.9999999999999999E-113</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>188</v>
@@ -11672,7 +11669,7 @@
         <v>3.9999999999999998E-112</v>
       </c>
       <c r="B68" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>1131</v>
@@ -11802,7 +11799,7 @@
         <v>4.0000000000000004E-111</v>
       </c>
       <c r="B70" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>1120</v>
@@ -11932,7 +11929,7 @@
         <v>4.0000000000000002E-110</v>
       </c>
       <c r="B72" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>1113</v>
@@ -12972,7 +12969,7 @@
         <v>3.9999999999999997E-102</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>1056</v>
@@ -13743,7 +13740,7 @@
         <v>1920</v>
       </c>
       <c r="B100" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>326</v>
@@ -14130,7 +14127,7 @@
         <v>2000</v>
       </c>
       <c r="B106" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>198</v>
@@ -14195,7 +14192,7 @@
         <v>2001</v>
       </c>
       <c r="B107" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>198</v>
@@ -14257,10 +14254,10 @@
     </row>
     <row r="108" spans="1:21">
       <c r="A108" s="16" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="B108" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>221</v>
@@ -14325,7 +14322,7 @@
         <v>1654</v>
       </c>
       <c r="B109" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>226</v>
@@ -14650,7 +14647,7 @@
         <v>1905</v>
       </c>
       <c r="B114" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>362</v>
@@ -15105,7 +15102,7 @@
         <v>1952</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>395</v>
@@ -15616,7 +15613,7 @@
         <v>1953</v>
       </c>
       <c r="B129" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>395</v>
@@ -15805,7 +15802,7 @@
         <v>1867</v>
       </c>
       <c r="B132" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>419</v>
@@ -15870,7 +15867,7 @@
         <v>1923</v>
       </c>
       <c r="B133" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>429</v>
@@ -15935,7 +15932,7 @@
         <v>1929</v>
       </c>
       <c r="B134" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>436</v>
@@ -16118,7 +16115,7 @@
         <v>1928</v>
       </c>
       <c r="B137" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>458</v>
@@ -16183,7 +16180,7 @@
         <v>1945</v>
       </c>
       <c r="B138" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>465</v>
@@ -16248,7 +16245,7 @@
         <v>1924</v>
       </c>
       <c r="B139" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>473</v>
@@ -16313,7 +16310,7 @@
         <v>1859</v>
       </c>
       <c r="B140" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>479</v>
@@ -16378,7 +16375,7 @@
         <v>1946</v>
       </c>
       <c r="B141" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>482</v>
@@ -16443,7 +16440,7 @@
         <v>1912</v>
       </c>
       <c r="B142" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>490</v>
@@ -16573,7 +16570,7 @@
         <v>1913</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>503</v>
@@ -16898,7 +16895,7 @@
         <v>1877</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>508</v>
@@ -16963,7 +16960,7 @@
         <v>1878</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>508</v>
@@ -17028,7 +17025,7 @@
         <v>1879</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>508</v>
@@ -17093,7 +17090,7 @@
         <v>1884</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>515</v>
@@ -17158,7 +17155,7 @@
         <v>1885</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>515</v>
@@ -17223,7 +17220,7 @@
         <v>1886</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>515</v>
@@ -17929,7 +17926,7 @@
     </row>
     <row r="165" spans="1:21">
       <c r="A165" s="40" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B165" t="s">
         <v>1724</v>
@@ -17970,7 +17967,7 @@
     </row>
     <row r="166" spans="1:21">
       <c r="A166" s="40" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="B166" t="s">
         <v>1724</v>
@@ -18028,7 +18025,7 @@
         <v>1975</v>
       </c>
       <c r="B168" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>315</v>
@@ -18158,7 +18155,7 @@
         <v>321</v>
       </c>
       <c r="B170" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>315</v>
@@ -18483,7 +18480,7 @@
         <v>2015</v>
       </c>
       <c r="B175" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>576</v>
@@ -20628,7 +20625,7 @@
         <v>1983</v>
       </c>
       <c r="B208" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>731</v>
@@ -20693,7 +20690,7 @@
         <v>1984</v>
       </c>
       <c r="B209" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>731</v>
@@ -20758,7 +20755,7 @@
         <v>1978</v>
       </c>
       <c r="B210" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>739</v>
@@ -20823,7 +20820,7 @@
         <v>1979</v>
       </c>
       <c r="B211" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>739</v>
@@ -20885,7 +20882,7 @@
     </row>
     <row r="212" spans="1:21">
       <c r="A212" s="16" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="B212" t="s">
         <v>1724</v>
@@ -20950,7 +20947,7 @@
     </row>
     <row r="213" spans="1:21">
       <c r="A213" s="16" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B213" t="s">
         <v>1724</v>
@@ -21668,7 +21665,7 @@
         <v>1947</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>796</v>
@@ -21733,7 +21730,7 @@
         <v>1948</v>
       </c>
       <c r="B225" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>796</v>
@@ -22069,7 +22066,7 @@
         <v>1887</v>
       </c>
       <c r="B231" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>957</v>
@@ -22134,7 +22131,7 @@
         <v>1888</v>
       </c>
       <c r="B232" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>957</v>
@@ -22199,7 +22196,7 @@
         <v>1889</v>
       </c>
       <c r="B233" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>965</v>
@@ -22264,7 +22261,7 @@
         <v>1881</v>
       </c>
       <c r="B234" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>966</v>
@@ -22329,7 +22326,7 @@
         <v>1880</v>
       </c>
       <c r="B235" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>974</v>
@@ -23764,7 +23761,7 @@
         <v>1981</v>
       </c>
       <c r="B258" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>858</v>
@@ -24021,7 +24018,7 @@
     </row>
     <row r="262" spans="1:21">
       <c r="A262" s="40" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B262" t="s">
         <v>1724</v>
@@ -24337,7 +24334,7 @@
         <v>1861</v>
       </c>
       <c r="B267" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>886</v>
@@ -24402,7 +24399,7 @@
         <v>1955</v>
       </c>
       <c r="B268" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>315</v>
@@ -24532,7 +24529,7 @@
         <v>1921</v>
       </c>
       <c r="B270" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>900</v>
@@ -24597,7 +24594,7 @@
         <v>1922</v>
       </c>
       <c r="B271" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>906</v>
@@ -24919,7 +24916,7 @@
     </row>
     <row r="276" spans="1:21">
       <c r="A276" s="40" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="B276" t="s">
         <v>1724</v>
@@ -24984,7 +24981,7 @@
     </row>
     <row r="277" spans="1:21">
       <c r="A277" s="40" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B277" t="s">
         <v>1724</v>
@@ -25179,7 +25176,7 @@
     </row>
     <row r="280" spans="1:21">
       <c r="A280" s="40" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B280" t="s">
         <v>1724</v>
@@ -25244,7 +25241,7 @@
     </row>
     <row r="281" spans="1:21">
       <c r="A281" s="40" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="B281" t="s">
         <v>1724</v>
@@ -25309,7 +25306,7 @@
     </row>
     <row r="282" spans="1:21">
       <c r="A282" s="40" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B282" t="s">
         <v>1724</v>
@@ -25374,7 +25371,7 @@
     </row>
     <row r="283" spans="1:21">
       <c r="A283" s="40" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="B283" t="s">
         <v>1724</v>
@@ -25439,7 +25436,7 @@
     </row>
     <row r="284" spans="1:21">
       <c r="A284" s="40" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="B284" t="s">
         <v>1724</v>
@@ -25504,7 +25501,7 @@
     </row>
     <row r="285" spans="1:21">
       <c r="A285" s="40" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="B285" t="s">
         <v>1724</v>
@@ -25572,7 +25569,7 @@
         <v>1277</v>
       </c>
       <c r="B286" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>1278</v>
@@ -25962,7 +25959,7 @@
         <v>1306</v>
       </c>
       <c r="B292" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>1307</v>
@@ -26027,7 +26024,7 @@
         <v>1312</v>
       </c>
       <c r="B293" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>1313</v>
@@ -26092,7 +26089,7 @@
         <v>1314</v>
       </c>
       <c r="B294" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>1315</v>
@@ -26866,10 +26863,10 @@
     </row>
     <row r="306" spans="1:21">
       <c r="A306" s="40" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B306" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>1357</v>
@@ -26931,10 +26928,10 @@
     </row>
     <row r="307" spans="1:21">
       <c r="A307" s="40" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B307" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>1357</v>
@@ -27194,7 +27191,7 @@
         <v>1375</v>
       </c>
       <c r="B311" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>1376</v>
@@ -27259,7 +27256,7 @@
         <v>1382</v>
       </c>
       <c r="B312" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>1383</v>
@@ -27321,10 +27318,10 @@
     </row>
     <row r="313" spans="1:21">
       <c r="A313" s="40" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B313" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>1393</v>
@@ -27386,10 +27383,10 @@
     </row>
     <row r="314" spans="1:21">
       <c r="A314" s="40" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="B314" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>1393</v>
@@ -27451,10 +27448,10 @@
     </row>
     <row r="315" spans="1:21">
       <c r="A315" s="40" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B315" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>1393</v>
@@ -27519,7 +27516,7 @@
         <v>1398</v>
       </c>
       <c r="B316" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>1399</v>
@@ -27581,7 +27578,7 @@
     </row>
     <row r="317" spans="1:21">
       <c r="A317" s="40" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="B317" t="s">
         <v>1724</v>
@@ -27646,7 +27643,7 @@
     </row>
     <row r="318" spans="1:21">
       <c r="A318" s="40" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B318" t="s">
         <v>1724</v>
@@ -27711,10 +27708,10 @@
     </row>
     <row r="319" spans="1:21">
       <c r="A319" s="40" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B319" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>1411</v>
@@ -27776,10 +27773,10 @@
     </row>
     <row r="320" spans="1:21">
       <c r="A320" s="40" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B320" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>1411</v>
@@ -27844,7 +27841,7 @@
         <v>1423</v>
       </c>
       <c r="B321" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>1424</v>
@@ -27906,7 +27903,7 @@
         <v>1432</v>
       </c>
       <c r="B322" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>1433</v>
@@ -27971,7 +27968,7 @@
         <v>1442</v>
       </c>
       <c r="B323" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>1443</v>
@@ -28033,10 +28030,10 @@
     </row>
     <row r="324" spans="1:21">
       <c r="A324" s="40" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B324" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>1450</v>
@@ -28098,10 +28095,10 @@
     </row>
     <row r="325" spans="1:21">
       <c r="A325" s="40" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="B325" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>1450</v>
@@ -28166,7 +28163,7 @@
         <v>1460</v>
       </c>
       <c r="B326" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>1461</v>
@@ -28231,7 +28228,7 @@
         <v>1472</v>
       </c>
       <c r="B327" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>1473</v>
@@ -28296,7 +28293,7 @@
         <v>1482</v>
       </c>
       <c r="B328" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>1483</v>
@@ -28358,10 +28355,10 @@
     </row>
     <row r="329" spans="1:21">
       <c r="A329" s="40" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B329" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>1492</v>
@@ -28423,10 +28420,10 @@
     </row>
     <row r="330" spans="1:21">
       <c r="A330" s="40" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="B330" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>1492</v>
@@ -28491,7 +28488,7 @@
         <v>1502</v>
       </c>
       <c r="B331" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>1503</v>
@@ -28556,7 +28553,7 @@
         <v>1511</v>
       </c>
       <c r="B332" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>1512</v>
@@ -28621,7 +28618,7 @@
         <v>1518</v>
       </c>
       <c r="B333" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>1519</v>
@@ -28686,7 +28683,7 @@
         <v>1529</v>
       </c>
       <c r="B334" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>1519</v>
@@ -28751,7 +28748,7 @@
         <v>1530</v>
       </c>
       <c r="B335" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>1531</v>
@@ -28807,7 +28804,7 @@
         <v>1537</v>
       </c>
       <c r="B336" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>1853</v>
@@ -28872,7 +28869,7 @@
         <v>1544</v>
       </c>
       <c r="B337" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>1545</v>
@@ -28937,7 +28934,7 @@
         <v>1557</v>
       </c>
       <c r="B338" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>1558</v>
@@ -29002,7 +28999,7 @@
         <v>1568</v>
       </c>
       <c r="B339" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>1569</v>
@@ -29067,7 +29064,7 @@
         <v>1575</v>
       </c>
       <c r="B340" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>1576</v>
@@ -29132,7 +29129,7 @@
         <v>1580</v>
       </c>
       <c r="B341" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>1581</v>
@@ -29197,7 +29194,7 @@
         <v>1586</v>
       </c>
       <c r="B342" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>1587</v>
@@ -29259,10 +29256,10 @@
     </row>
     <row r="343" spans="1:21">
       <c r="A343" s="40" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="B343" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>1203</v>
@@ -29324,10 +29321,10 @@
     </row>
     <row r="344" spans="1:21">
       <c r="A344" s="40" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="B344" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>1203</v>
@@ -29392,7 +29389,7 @@
         <v>1194</v>
       </c>
       <c r="B345" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>1195</v>
@@ -29454,10 +29451,10 @@
     </row>
     <row r="346" spans="1:21">
       <c r="A346" s="16" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="B346" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>3</v>
@@ -29495,10 +29492,10 @@
     </row>
     <row r="347" spans="1:21">
       <c r="A347" s="16" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B347" s="35" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>3</v>
@@ -29536,7 +29533,7 @@
     </row>
     <row r="348" spans="1:21">
       <c r="A348" s="16" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="B348" t="s">
         <v>1724</v>
@@ -29547,7 +29544,7 @@
     </row>
     <row r="349" spans="1:21">
       <c r="A349" s="16" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="B349" t="s">
         <v>1724</v>
@@ -29558,7 +29555,7 @@
     </row>
     <row r="350" spans="1:21">
       <c r="A350" s="16" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B350" t="s">
         <v>1611</v>
@@ -29596,7 +29593,7 @@
     </row>
     <row r="351" spans="1:21">
       <c r="A351" s="16" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B351" t="s">
         <v>1611</v>
@@ -29634,7 +29631,7 @@
     </row>
     <row r="352" spans="1:21">
       <c r="A352" s="16" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B352" t="s">
         <v>1611</v>
@@ -29728,7 +29725,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15">
       <c r="A1" s="15" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>1613</v>
@@ -29746,10 +29743,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="B2" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -29763,7 +29760,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="B3" t="s">
         <v>1687</v>
@@ -29779,11 +29776,11 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B4" t="s">
         <v>2069</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2070</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -29796,8 +29793,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>2069</v>
+      <c r="A5" s="1" t="s">
+        <v>2084</v>
       </c>
       <c r="B5" t="s">
         <v>1687</v>
@@ -29819,7 +29816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA192F2-38CE-40C8-9D37-82946077C67C}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W330"/>
@@ -29850,25 +29847,25 @@
   <sheetData>
     <row r="1" spans="1:23" ht="38.25" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>1851</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>1610</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>1852</v>
@@ -29880,7 +29877,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="L1" s="12" t="s">
         <v>1850</v>
@@ -29889,16 +29886,16 @@
         <v>0</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="O1" s="11" t="s">
         <v>1657</v>
       </c>
       <c r="P1" s="31" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" s="7" customFormat="1" hidden="1">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="7" customFormat="1">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -29912,17 +29909,17 @@
         <v>2.0000000000000001E-101</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H2" s="26"/>
       <c r="I2" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J2" s="21"/>
       <c r="K2" s="21"/>
@@ -29931,7 +29928,7 @@
         <v>21</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>1617</v>
@@ -29945,7 +29942,7 @@
       <c r="U2" s="5"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:23" hidden="1">
+    <row r="3" spans="1:23">
       <c r="A3" s="21">
         <v>2</v>
       </c>
@@ -29959,17 +29956,17 @@
         <v>1656</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H3" s="26"/>
       <c r="I3" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
@@ -29978,7 +29975,7 @@
         <v>27</v>
       </c>
       <c r="N3" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O3" s="24" t="s">
         <v>1636</v>
@@ -29987,7 +29984,7 @@
         <v>539240</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1">
+    <row r="4" spans="1:23">
       <c r="A4" s="21">
         <v>3</v>
       </c>
@@ -30001,17 +29998,17 @@
         <v>1653</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -30020,7 +30017,7 @@
         <v>72</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>1636</v>
@@ -30030,7 +30027,7 @@
       </c>
       <c r="W4" s="7"/>
     </row>
-    <row r="5" spans="1:23" hidden="1">
+    <row r="5" spans="1:23">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -30044,17 +30041,17 @@
         <v>1652</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -30063,7 +30060,7 @@
         <v>72</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>1636</v>
@@ -30072,7 +30069,7 @@
         <v>354768.58</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1">
+    <row r="6" spans="1:23">
       <c r="A6" s="21">
         <v>5</v>
       </c>
@@ -30086,17 +30083,17 @@
         <v>1651</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H6" s="25"/>
       <c r="I6" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -30105,7 +30102,7 @@
         <v>77</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>1636</v>
@@ -30114,7 +30111,7 @@
         <v>396427.26</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1">
+    <row r="7" spans="1:23">
       <c r="A7" s="21">
         <v>6</v>
       </c>
@@ -30128,17 +30125,17 @@
         <v>1650</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
@@ -30147,7 +30144,7 @@
         <v>77</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>1636</v>
@@ -30156,7 +30153,7 @@
         <v>396427.26</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1">
+    <row r="8" spans="1:23">
       <c r="A8" s="25">
         <v>7</v>
       </c>
@@ -30170,17 +30167,17 @@
         <v>1649</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H8" s="26"/>
       <c r="I8" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
@@ -30189,7 +30186,7 @@
         <v>120</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>1636</v>
@@ -30198,7 +30195,7 @@
         <v>359308.5</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1">
+    <row r="9" spans="1:23">
       <c r="A9" s="21">
         <v>8</v>
       </c>
@@ -30212,17 +30209,17 @@
         <v>1648</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H9" s="26"/>
       <c r="I9" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J9" s="21"/>
       <c r="K9" s="21"/>
@@ -30231,7 +30228,7 @@
         <v>123</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O9" s="24" t="s">
         <v>1617</v>
@@ -30240,7 +30237,7 @@
         <v>342532.29999999993</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1">
+    <row r="10" spans="1:23">
       <c r="A10" s="21">
         <v>9</v>
       </c>
@@ -30254,17 +30251,17 @@
         <v>1654</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H10" s="26"/>
       <c r="I10" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J10" s="21"/>
       <c r="K10" s="21"/>
@@ -30273,7 +30270,7 @@
         <v>231</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>1636</v>
@@ -30282,7 +30279,7 @@
         <v>369126.39999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1">
+    <row r="11" spans="1:23">
       <c r="A11" s="25">
         <v>10</v>
       </c>
@@ -30296,17 +30293,17 @@
         <v>1655</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H11" s="26"/>
       <c r="I11" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J11" s="21"/>
       <c r="K11" s="21"/>
@@ -30315,7 +30312,7 @@
         <v>187</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O11" s="24" t="s">
         <v>1636</v>
@@ -30324,7 +30321,7 @@
         <v>301263.31299999997</v>
       </c>
     </row>
-    <row r="12" spans="1:23" hidden="1">
+    <row r="12" spans="1:23">
       <c r="A12" s="21">
         <v>11</v>
       </c>
@@ -30341,21 +30338,21 @@
         <v>1687</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H12" s="26"/>
       <c r="I12" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
       <c r="M12" s="22"/>
       <c r="N12" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O12" s="24" t="s">
         <v>1617</v>
@@ -30364,7 +30361,7 @@
         <v>715794.3</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1">
+    <row r="13" spans="1:23">
       <c r="A13" s="21">
         <v>12</v>
       </c>
@@ -30381,21 +30378,21 @@
         <v>1687</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G13" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H13" s="26"/>
       <c r="I13" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
       <c r="M13" s="22"/>
       <c r="N13" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O13" s="24" t="s">
         <v>1636</v>
@@ -30404,7 +30401,7 @@
         <v>116861.16</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="4" customFormat="1" hidden="1">
+    <row r="14" spans="1:23" s="4" customFormat="1">
       <c r="A14" s="25">
         <v>13</v>
       </c>
@@ -30421,21 +30418,21 @@
         <v>1687</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
       <c r="L14" s="21"/>
       <c r="M14" s="22"/>
       <c r="N14" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>1665</v>
@@ -30445,7 +30442,7 @@
       </c>
       <c r="U14" s="5"/>
     </row>
-    <row r="15" spans="1:23" hidden="1">
+    <row r="15" spans="1:23">
       <c r="A15" s="21">
         <v>14</v>
       </c>
@@ -30462,21 +30459,21 @@
         <v>1687</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="22"/>
       <c r="N15" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>1636</v>
@@ -30485,7 +30482,7 @@
         <v>116861.16</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1">
+    <row r="16" spans="1:23">
       <c r="A16" s="21">
         <v>15</v>
       </c>
@@ -30499,17 +30496,17 @@
         <v>1646</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G16" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
@@ -30518,7 +30515,7 @@
         <v>628</v>
       </c>
       <c r="N16" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O16" s="8" t="s">
         <v>1617</v>
@@ -30527,7 +30524,7 @@
         <v>349232.69999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="4" customFormat="1" hidden="1">
+    <row r="17" spans="1:22" s="4" customFormat="1">
       <c r="A17" s="25">
         <v>16</v>
       </c>
@@ -30541,17 +30538,17 @@
         <v>1645</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G17" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H17" s="25"/>
       <c r="I17" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
@@ -30560,7 +30557,7 @@
         <v>628</v>
       </c>
       <c r="N17" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O17" s="8" t="s">
         <v>1617</v>
@@ -30570,7 +30567,7 @@
       </c>
       <c r="U17" s="5"/>
     </row>
-    <row r="18" spans="1:22" hidden="1">
+    <row r="18" spans="1:22">
       <c r="A18" s="21">
         <v>17</v>
       </c>
@@ -30584,17 +30581,17 @@
         <v>1644</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H18" s="26"/>
       <c r="I18" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
@@ -30603,7 +30600,7 @@
         <v>649</v>
       </c>
       <c r="N18" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O18" s="24" t="s">
         <v>1617</v>
@@ -30612,7 +30609,7 @@
         <v>485807.5</v>
       </c>
     </row>
-    <row r="19" spans="1:22" hidden="1">
+    <row r="19" spans="1:22">
       <c r="A19" s="21">
         <v>18</v>
       </c>
@@ -30626,17 +30623,17 @@
         <v>1643</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H19" s="26"/>
       <c r="I19" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -30645,7 +30642,7 @@
         <v>649</v>
       </c>
       <c r="N19" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O19" s="24" t="s">
         <v>1617</v>
@@ -30654,7 +30651,7 @@
         <v>485807.5</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="4" customFormat="1" hidden="1">
+    <row r="20" spans="1:22" s="4" customFormat="1">
       <c r="A20" s="25">
         <v>19</v>
       </c>
@@ -30668,17 +30665,17 @@
         <v>1642</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G20" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
@@ -30687,7 +30684,7 @@
         <v>1640</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O20" s="8" t="s">
         <v>1636</v>
@@ -30697,7 +30694,7 @@
       </c>
       <c r="U20" s="5"/>
     </row>
-    <row r="21" spans="1:22" hidden="1">
+    <row r="21" spans="1:22">
       <c r="A21" s="21">
         <v>20</v>
       </c>
@@ -30711,17 +30708,17 @@
         <v>1639</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G21" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="9" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -30730,7 +30727,7 @@
         <v>655</v>
       </c>
       <c r="N21" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O21" s="8" t="s">
         <v>1617</v>
@@ -30739,7 +30736,7 @@
         <v>820525.29999999993</v>
       </c>
     </row>
-    <row r="22" spans="1:22" hidden="1">
+    <row r="22" spans="1:22">
       <c r="A22" s="21">
         <v>21</v>
       </c>
@@ -30753,17 +30750,17 @@
         <v>1638</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G22" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H22" s="25"/>
       <c r="I22" s="25" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J22" s="25"/>
       <c r="K22" s="25"/>
@@ -30772,7 +30769,7 @@
         <v>688</v>
       </c>
       <c r="N22" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O22" s="8" t="s">
         <v>1636</v>
@@ -30781,7 +30778,7 @@
         <v>264404.59999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:22" s="4" customFormat="1" hidden="1">
+    <row r="23" spans="1:22" s="4" customFormat="1">
       <c r="A23" s="25">
         <v>22</v>
       </c>
@@ -30795,17 +30792,17 @@
         <v>1635</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G23" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H23" s="25"/>
       <c r="I23" s="25" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J23" s="25"/>
       <c r="K23" s="25"/>
@@ -30814,7 +30811,7 @@
         <v>693</v>
       </c>
       <c r="N23" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>1617</v>
@@ -30824,7 +30821,7 @@
       </c>
       <c r="U23" s="5"/>
     </row>
-    <row r="24" spans="1:22" hidden="1">
+    <row r="24" spans="1:22">
       <c r="A24" s="21">
         <v>23</v>
       </c>
@@ -30838,17 +30835,17 @@
         <v>1631</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G24" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J24" s="25"/>
       <c r="K24" s="25"/>
@@ -30857,7 +30854,7 @@
         <v>927</v>
       </c>
       <c r="N24" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O24" s="8" t="s">
         <v>1617</v>
@@ -30866,7 +30863,7 @@
         <v>371908.5</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1">
+    <row r="25" spans="1:22">
       <c r="A25" s="21">
         <v>24</v>
       </c>
@@ -30880,17 +30877,17 @@
         <v>1634</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H25" s="26"/>
       <c r="I25" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
@@ -30899,7 +30896,7 @@
         <v>867</v>
       </c>
       <c r="N25" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O25" s="24" t="s">
         <v>1617</v>
@@ -30908,7 +30905,7 @@
         <v>448062.19999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:22" hidden="1">
+    <row r="26" spans="1:22">
       <c r="A26" s="25">
         <v>25</v>
       </c>
@@ -30922,17 +30919,17 @@
         <v>1633</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H26" s="26"/>
       <c r="I26" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
@@ -30941,7 +30938,7 @@
         <v>867</v>
       </c>
       <c r="N26" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O26" s="24" t="s">
         <v>1617</v>
@@ -30950,7 +30947,7 @@
         <v>448062.19999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:22" hidden="1">
+    <row r="27" spans="1:22">
       <c r="A27" s="21">
         <v>26</v>
       </c>
@@ -30964,17 +30961,17 @@
         <v>1632</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H27" s="26"/>
       <c r="I27" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
@@ -30983,7 +30980,7 @@
         <v>48</v>
       </c>
       <c r="N27" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O27" s="8" t="s">
         <v>1617</v>
@@ -30992,7 +30989,7 @@
         <v>399632.69999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1">
+    <row r="28" spans="1:22">
       <c r="A28" s="21">
         <v>27</v>
       </c>
@@ -31009,21 +31006,21 @@
         <v>1687</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>1661</v>
       </c>
       <c r="H28" s="26"/>
       <c r="I28" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
       <c r="M28" s="22"/>
       <c r="N28" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O28" s="24" t="s">
         <v>1617</v>
@@ -31032,7 +31029,7 @@
         <v>448175.52</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1">
+    <row r="29" spans="1:22">
       <c r="A29" s="25">
         <v>28</v>
       </c>
@@ -31049,21 +31046,21 @@
         <v>1687</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>1661</v>
       </c>
       <c r="H29" s="26"/>
       <c r="I29" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
       <c r="L29" s="21"/>
       <c r="M29" s="22"/>
       <c r="N29" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O29" s="24" t="s">
         <v>1617</v>
@@ -31072,7 +31069,7 @@
         <v>490831.38</v>
       </c>
     </row>
-    <row r="30" spans="1:22" hidden="1">
+    <row r="30" spans="1:22">
       <c r="A30" s="21">
         <v>29</v>
       </c>
@@ -31089,21 +31086,21 @@
         <v>1687</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H30" s="26"/>
       <c r="I30" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="22"/>
       <c r="N30" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O30" s="24" t="s">
         <v>1617</v>
@@ -31112,7 +31109,7 @@
         <v>185636.1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" hidden="1">
+    <row r="31" spans="1:22">
       <c r="A31" s="21">
         <v>30</v>
       </c>
@@ -31129,21 +31126,21 @@
         <v>1687</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H31" s="26"/>
       <c r="I31" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="22"/>
       <c r="N31" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O31" s="24" t="s">
         <v>1617</v>
@@ -31169,21 +31166,21 @@
         <v>1687</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H32" s="26"/>
       <c r="I32" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
       <c r="N32" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O32" s="24" t="s">
         <v>1617</v>
@@ -31194,7 +31191,7 @@
       <c r="U32" s="5"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="33" spans="1:22" s="7" customFormat="1">
       <c r="A33" s="21">
         <v>32</v>
       </c>
@@ -31208,17 +31205,17 @@
         <v>1630</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H33" s="26"/>
       <c r="I33" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
@@ -31227,7 +31224,7 @@
         <v>1335</v>
       </c>
       <c r="N33" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O33" s="24" t="s">
         <v>1617</v>
@@ -31242,7 +31239,7 @@
       <c r="U33" s="5"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="34" spans="1:22" s="7" customFormat="1">
       <c r="A34" s="21">
         <v>33</v>
       </c>
@@ -31256,17 +31253,17 @@
         <v>1629</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H34" s="26"/>
       <c r="I34" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
@@ -31275,7 +31272,7 @@
         <v>1335</v>
       </c>
       <c r="N34" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O34" s="24" t="s">
         <v>1617</v>
@@ -31290,7 +31287,7 @@
       <c r="U34" s="5"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="35" spans="1:22" s="7" customFormat="1">
       <c r="A35" s="25">
         <v>34</v>
       </c>
@@ -31304,17 +31301,17 @@
         <v>1628</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H35" s="26"/>
       <c r="I35" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
@@ -31323,7 +31320,7 @@
         <v>1335</v>
       </c>
       <c r="N35" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O35" s="24" t="s">
         <v>1617</v>
@@ -31334,7 +31331,7 @@
       <c r="U35" s="5"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="36" spans="1:22" s="7" customFormat="1">
       <c r="A36" s="21">
         <v>35</v>
       </c>
@@ -31348,17 +31345,17 @@
         <v>1627</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H36" s="26"/>
       <c r="I36" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
@@ -31367,7 +31364,7 @@
         <v>1335</v>
       </c>
       <c r="N36" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O36" s="24" t="s">
         <v>1617</v>
@@ -31382,7 +31379,7 @@
       <c r="U36" s="5"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="37" spans="1:22" s="7" customFormat="1">
       <c r="A37" s="21">
         <v>36</v>
       </c>
@@ -31396,17 +31393,17 @@
         <v>1626</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H37" s="26"/>
       <c r="I37" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
@@ -31415,7 +31412,7 @@
         <v>1343</v>
       </c>
       <c r="N37" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O37" s="24" t="s">
         <v>1617</v>
@@ -31430,7 +31427,7 @@
       <c r="U37" s="5"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" spans="1:22" hidden="1">
+    <row r="38" spans="1:22">
       <c r="A38" s="25">
         <v>37</v>
       </c>
@@ -31444,17 +31441,17 @@
         <v>1625</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G38" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H38" s="26"/>
       <c r="I38" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
@@ -31463,7 +31460,7 @@
         <v>1343</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O38" s="24" t="s">
         <v>1617</v>
@@ -31472,7 +31469,7 @@
         <v>710045.29999999993</v>
       </c>
     </row>
-    <row r="39" spans="1:22" hidden="1">
+    <row r="39" spans="1:22">
       <c r="A39" s="21">
         <v>38</v>
       </c>
@@ -31486,17 +31483,17 @@
         <v>1624</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H39" s="26"/>
       <c r="I39" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
@@ -31505,7 +31502,7 @@
         <v>1349</v>
       </c>
       <c r="N39" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O39" s="24" t="s">
         <v>1617</v>
@@ -31514,7 +31511,7 @@
         <v>480689.20000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:22" hidden="1">
+    <row r="40" spans="1:22">
       <c r="A40" s="21">
         <v>39</v>
       </c>
@@ -31528,17 +31525,17 @@
         <v>1623</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H40" s="26"/>
       <c r="I40" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -31547,7 +31544,7 @@
         <v>1349</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O40" s="24" t="s">
         <v>1617</v>
@@ -31556,7 +31553,7 @@
         <v>480689.20000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:22" hidden="1">
+    <row r="41" spans="1:22">
       <c r="A41" s="25">
         <v>40</v>
       </c>
@@ -31570,17 +31567,17 @@
         <v>1622</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H41" s="26"/>
       <c r="I41" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
@@ -31589,7 +31586,7 @@
         <v>1355</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O41" s="24" t="s">
         <v>1617</v>
@@ -31598,7 +31595,7 @@
         <v>485807.5</v>
       </c>
     </row>
-    <row r="42" spans="1:22" hidden="1">
+    <row r="42" spans="1:22">
       <c r="A42" s="21">
         <v>41</v>
       </c>
@@ -31612,17 +31609,17 @@
         <v>1621</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H42" s="26"/>
       <c r="I42" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
@@ -31631,7 +31628,7 @@
         <v>1355</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O42" s="24" t="s">
         <v>1617</v>
@@ -31640,7 +31637,7 @@
         <v>485807.5</v>
       </c>
     </row>
-    <row r="43" spans="1:22" hidden="1">
+    <row r="43" spans="1:22">
       <c r="A43" s="21">
         <v>42</v>
       </c>
@@ -31654,17 +31651,17 @@
         <v>1362</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H43" s="26"/>
       <c r="I43" s="21" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="J43" s="21"/>
       <c r="K43" s="21"/>
@@ -31673,7 +31670,7 @@
         <v>1620</v>
       </c>
       <c r="N43" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O43" s="24" t="s">
         <v>1617</v>
@@ -31682,7 +31679,7 @@
         <v>1006485.0599999999</v>
       </c>
     </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="44" spans="1:22" s="7" customFormat="1">
       <c r="A44" s="25">
         <v>43</v>
       </c>
@@ -31696,17 +31693,17 @@
         <v>2.0000000000000001E-101</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H44" s="26"/>
       <c r="I44" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J44" s="26"/>
       <c r="K44" s="26"/>
@@ -31715,7 +31712,7 @@
         <v>20</v>
       </c>
       <c r="N44" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O44" s="24" t="s">
         <v>1647</v>
@@ -31726,7 +31723,7 @@
       <c r="U44" s="5"/>
       <c r="V44" s="4"/>
     </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="45" spans="1:22" s="7" customFormat="1">
       <c r="A45" s="21">
         <v>44</v>
       </c>
@@ -31740,17 +31737,17 @@
         <v>1656</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H45" s="26"/>
       <c r="I45" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J45" s="26"/>
       <c r="K45" s="26"/>
@@ -31759,7 +31756,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O45" s="24" t="s">
         <v>1619</v>
@@ -31772,7 +31769,7 @@
       <c r="U45" s="5"/>
       <c r="V45" s="4"/>
     </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="46" spans="1:22" s="7" customFormat="1">
       <c r="A46" s="21">
         <v>45</v>
       </c>
@@ -31786,17 +31783,17 @@
         <v>1653</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G46" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H46" s="25"/>
       <c r="I46" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J46" s="25"/>
       <c r="K46" s="25"/>
@@ -31805,7 +31802,7 @@
         <v>70</v>
       </c>
       <c r="N46" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O46" s="8" t="s">
         <v>1619</v>
@@ -31818,7 +31815,7 @@
       <c r="U46" s="5"/>
       <c r="V46" s="4"/>
     </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="47" spans="1:22" s="7" customFormat="1">
       <c r="A47" s="25">
         <v>46</v>
       </c>
@@ -31832,17 +31829,17 @@
         <v>1652</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G47" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H47" s="25"/>
       <c r="I47" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J47" s="25"/>
       <c r="K47" s="25"/>
@@ -31851,7 +31848,7 @@
         <v>70</v>
       </c>
       <c r="N47" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O47" s="8" t="s">
         <v>1619</v>
@@ -31862,7 +31859,7 @@
       <c r="U47" s="5"/>
       <c r="V47" s="4"/>
     </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="48" spans="1:22" s="7" customFormat="1">
       <c r="A48" s="21">
         <v>47</v>
       </c>
@@ -31876,17 +31873,17 @@
         <v>1651</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G48" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H48" s="25"/>
       <c r="I48" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J48" s="25"/>
       <c r="K48" s="25"/>
@@ -31895,7 +31892,7 @@
         <v>75</v>
       </c>
       <c r="N48" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O48" s="8" t="s">
         <v>1619</v>
@@ -31908,7 +31905,7 @@
       <c r="U48" s="5"/>
       <c r="V48" s="4"/>
     </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" hidden="1">
+    <row r="49" spans="1:22" s="7" customFormat="1">
       <c r="A49" s="21">
         <v>48</v>
       </c>
@@ -31922,17 +31919,17 @@
         <v>1650</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G49" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H49" s="25"/>
       <c r="I49" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J49" s="25"/>
       <c r="K49" s="25"/>
@@ -31941,7 +31938,7 @@
         <v>75</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O49" s="8" t="s">
         <v>1619</v>
@@ -31954,7 +31951,7 @@
       <c r="U49" s="5"/>
       <c r="V49" s="4"/>
     </row>
-    <row r="50" spans="1:22" hidden="1">
+    <row r="50" spans="1:22">
       <c r="A50" s="25">
         <v>49</v>
       </c>
@@ -31968,17 +31965,17 @@
         <v>1649</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H50" s="26"/>
       <c r="I50" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J50" s="26"/>
       <c r="K50" s="26"/>
@@ -31987,7 +31984,7 @@
         <v>119</v>
       </c>
       <c r="N50" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O50" s="24" t="s">
         <v>1619</v>
@@ -31996,7 +31993,7 @@
         <v>334108.5</v>
       </c>
     </row>
-    <row r="51" spans="1:22" hidden="1">
+    <row r="51" spans="1:22">
       <c r="A51" s="21">
         <v>50</v>
       </c>
@@ -32010,17 +32007,17 @@
         <v>1648</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H51" s="26"/>
       <c r="I51" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J51" s="26"/>
       <c r="K51" s="26"/>
@@ -32029,7 +32026,7 @@
         <v>122</v>
       </c>
       <c r="N51" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O51" s="24" t="s">
         <v>1647</v>
@@ -32039,7 +32036,7 @@
       </c>
       <c r="Q51" s="7"/>
     </row>
-    <row r="52" spans="1:22" hidden="1">
+    <row r="52" spans="1:22">
       <c r="A52" s="21">
         <v>51</v>
       </c>
@@ -32053,17 +32050,17 @@
         <v>1654</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H52" s="26"/>
       <c r="I52" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J52" s="26"/>
       <c r="K52" s="26"/>
@@ -32072,7 +32069,7 @@
         <v>230</v>
       </c>
       <c r="N52" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O52" s="8" t="s">
         <v>1619</v>
@@ -32082,7 +32079,7 @@
       </c>
       <c r="Q52" s="7"/>
     </row>
-    <row r="53" spans="1:22" hidden="1">
+    <row r="53" spans="1:22">
       <c r="A53" s="25">
         <v>52</v>
       </c>
@@ -32096,17 +32093,17 @@
         <v>1655</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H53" s="26"/>
       <c r="I53" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J53" s="26"/>
       <c r="K53" s="26"/>
@@ -32115,7 +32112,7 @@
         <v>236</v>
       </c>
       <c r="N53" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O53" s="24" t="s">
         <v>1619</v>
@@ -32124,7 +32121,7 @@
         <v>276063.31299999997</v>
       </c>
     </row>
-    <row r="54" spans="1:22" hidden="1">
+    <row r="54" spans="1:22">
       <c r="A54" s="21">
         <v>53</v>
       </c>
@@ -32141,21 +32138,21 @@
         <v>1687</v>
       </c>
       <c r="F54" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H54" s="26"/>
       <c r="I54" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J54" s="26"/>
       <c r="K54" s="26"/>
       <c r="L54" s="26"/>
       <c r="M54" s="22"/>
       <c r="N54" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O54" s="24" t="s">
         <v>1647</v>
@@ -32164,7 +32161,7 @@
         <v>609324.30000000005</v>
       </c>
     </row>
-    <row r="55" spans="1:22" hidden="1">
+    <row r="55" spans="1:22">
       <c r="A55" s="21">
         <v>54</v>
       </c>
@@ -32181,21 +32178,21 @@
         <v>1687</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H55" s="26"/>
       <c r="I55" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J55" s="26"/>
       <c r="K55" s="26"/>
       <c r="L55" s="26"/>
       <c r="M55" s="22"/>
       <c r="N55" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O55" s="24" t="s">
         <v>1619</v>
@@ -32204,7 +32201,7 @@
         <v>97751.16</v>
       </c>
     </row>
-    <row r="56" spans="1:22" hidden="1">
+    <row r="56" spans="1:22">
       <c r="A56" s="25">
         <v>55</v>
       </c>
@@ -32221,21 +32218,21 @@
         <v>1687</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H56" s="26"/>
       <c r="I56" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J56" s="26"/>
       <c r="K56" s="26"/>
       <c r="L56" s="26"/>
       <c r="M56" s="22"/>
       <c r="N56" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O56" s="24" t="s">
         <v>1636</v>
@@ -32244,7 +32241,7 @@
         <v>459174.3</v>
       </c>
     </row>
-    <row r="57" spans="1:22" hidden="1">
+    <row r="57" spans="1:22">
       <c r="A57" s="21">
         <v>56</v>
       </c>
@@ -32261,21 +32258,21 @@
         <v>1687</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H57" s="26"/>
       <c r="I57" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J57" s="26"/>
       <c r="K57" s="26"/>
       <c r="L57" s="26"/>
       <c r="M57" s="22"/>
       <c r="N57" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O57" s="24" t="s">
         <v>1619</v>
@@ -32284,7 +32281,7 @@
         <v>97751.16</v>
       </c>
     </row>
-    <row r="58" spans="1:22" hidden="1">
+    <row r="58" spans="1:22">
       <c r="A58" s="21">
         <v>57</v>
       </c>
@@ -32298,17 +32295,17 @@
         <v>1646</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G58" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H58" s="25"/>
       <c r="I58" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J58" s="25"/>
       <c r="K58" s="25"/>
@@ -32317,7 +32314,7 @@
         <v>627</v>
       </c>
       <c r="N58" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O58" s="8" t="s">
         <v>1619</v>
@@ -32326,7 +32323,7 @@
         <v>330332.69999999995</v>
       </c>
     </row>
-    <row r="59" spans="1:22" hidden="1">
+    <row r="59" spans="1:22">
       <c r="A59" s="25">
         <v>58</v>
       </c>
@@ -32340,17 +32337,17 @@
         <v>1645</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G59" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H59" s="25"/>
       <c r="I59" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J59" s="25"/>
       <c r="K59" s="25"/>
@@ -32359,7 +32356,7 @@
         <v>627</v>
       </c>
       <c r="N59" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O59" s="8" t="s">
         <v>1619</v>
@@ -32368,7 +32365,7 @@
         <v>330332.69999999995</v>
       </c>
     </row>
-    <row r="60" spans="1:22" hidden="1">
+    <row r="60" spans="1:22">
       <c r="A60" s="21">
         <v>59</v>
       </c>
@@ -32382,17 +32379,17 @@
         <v>1644</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H60" s="26"/>
       <c r="I60" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J60" s="26"/>
       <c r="K60" s="26"/>
@@ -32401,7 +32398,7 @@
         <v>648</v>
       </c>
       <c r="N60" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O60" s="24" t="s">
         <v>1619</v>
@@ -32410,7 +32407,7 @@
         <v>506827.5</v>
       </c>
     </row>
-    <row r="61" spans="1:22" hidden="1">
+    <row r="61" spans="1:22">
       <c r="A61" s="21">
         <v>60</v>
       </c>
@@ -32424,17 +32421,17 @@
         <v>1643</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H61" s="26"/>
       <c r="I61" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J61" s="26"/>
       <c r="K61" s="26"/>
@@ -32443,7 +32440,7 @@
         <v>648</v>
       </c>
       <c r="N61" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O61" s="24" t="s">
         <v>1619</v>
@@ -32452,7 +32449,7 @@
         <v>506827.5</v>
       </c>
     </row>
-    <row r="62" spans="1:22" hidden="1">
+    <row r="62" spans="1:22">
       <c r="A62" s="25">
         <v>61</v>
       </c>
@@ -32466,17 +32463,17 @@
         <v>1642</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G62" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H62" s="25"/>
       <c r="I62" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J62" s="25"/>
       <c r="K62" s="25"/>
@@ -32485,7 +32482,7 @@
         <v>1641</v>
       </c>
       <c r="N62" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O62" s="8" t="s">
         <v>1637</v>
@@ -32494,7 +32491,7 @@
         <v>891513.00000000012</v>
       </c>
     </row>
-    <row r="63" spans="1:22" hidden="1">
+    <row r="63" spans="1:22">
       <c r="A63" s="21">
         <v>62</v>
       </c>
@@ -32508,17 +32505,17 @@
         <v>1639</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G63" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H63" s="25"/>
       <c r="I63" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J63" s="25"/>
       <c r="K63" s="25"/>
@@ -32527,7 +32524,7 @@
         <v>653</v>
       </c>
       <c r="N63" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O63" s="8" t="s">
         <v>1619</v>
@@ -32536,7 +32533,7 @@
         <v>773065.29999999993</v>
       </c>
     </row>
-    <row r="64" spans="1:22" hidden="1">
+    <row r="64" spans="1:22">
       <c r="A64" s="21">
         <v>63</v>
       </c>
@@ -32550,17 +32547,17 @@
         <v>1638</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G64" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H64" s="25"/>
       <c r="I64" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J64" s="25"/>
       <c r="K64" s="25"/>
@@ -32569,7 +32566,7 @@
         <v>686</v>
       </c>
       <c r="N64" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O64" s="8" t="s">
         <v>1637</v>
@@ -32578,7 +32575,7 @@
         <v>226604.59999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1">
+    <row r="65" spans="1:16">
       <c r="A65" s="25">
         <v>64</v>
       </c>
@@ -32592,17 +32589,17 @@
         <v>1635</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G65" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H65" s="25"/>
       <c r="I65" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J65" s="25"/>
       <c r="K65" s="25"/>
@@ -32611,7 +32608,7 @@
         <v>692</v>
       </c>
       <c r="N65" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O65" s="8" t="s">
         <v>1619</v>
@@ -32620,7 +32617,7 @@
         <v>276063.31299999997</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1">
+    <row r="66" spans="1:16">
       <c r="A66" s="21">
         <v>65</v>
       </c>
@@ -32634,17 +32631,17 @@
         <v>1631</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F66" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G66" s="25" t="s">
         <v>1618</v>
       </c>
       <c r="H66" s="25"/>
       <c r="I66" s="25" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J66" s="25"/>
       <c r="K66" s="25"/>
@@ -32653,7 +32650,7 @@
         <v>926</v>
       </c>
       <c r="N66" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O66" s="8" t="s">
         <v>1619</v>
@@ -32662,7 +32659,7 @@
         <v>334108.5</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1">
+    <row r="67" spans="1:16">
       <c r="A67" s="21">
         <v>66</v>
       </c>
@@ -32676,17 +32673,17 @@
         <v>1634</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H67" s="26"/>
       <c r="I67" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J67" s="26"/>
       <c r="K67" s="26"/>
@@ -32695,7 +32692,7 @@
         <v>866</v>
       </c>
       <c r="N67" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O67" s="24" t="s">
         <v>1619</v>
@@ -32704,7 +32701,7 @@
         <v>490102.19999999995</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1">
+    <row r="68" spans="1:16">
       <c r="A68" s="25">
         <v>67</v>
       </c>
@@ -32718,17 +32715,17 @@
         <v>1633</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H68" s="26"/>
       <c r="I68" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J68" s="26"/>
       <c r="K68" s="26"/>
@@ -32737,7 +32734,7 @@
         <v>869</v>
       </c>
       <c r="N68" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O68" s="24" t="s">
         <v>1619</v>
@@ -32746,7 +32743,7 @@
         <v>490102.19999999995</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1">
+    <row r="69" spans="1:16">
       <c r="A69" s="21">
         <v>68</v>
       </c>
@@ -32760,17 +32757,17 @@
         <v>1632</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H69" s="26"/>
       <c r="I69" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J69" s="26"/>
       <c r="K69" s="26"/>
@@ -32779,7 +32776,7 @@
         <v>870</v>
       </c>
       <c r="N69" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O69" s="8" t="s">
         <v>1619</v>
@@ -32788,7 +32785,7 @@
         <v>361832.69999999995</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1">
+    <row r="70" spans="1:16">
       <c r="A70" s="21">
         <v>69</v>
       </c>
@@ -32805,21 +32802,21 @@
         <v>1687</v>
       </c>
       <c r="F70" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>1661</v>
       </c>
       <c r="H70" s="26"/>
       <c r="I70" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J70" s="26"/>
       <c r="K70" s="26"/>
       <c r="L70" s="26"/>
       <c r="M70" s="22"/>
       <c r="N70" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O70" s="24" t="s">
         <v>1647</v>
@@ -32828,7 +32825,7 @@
         <v>387335.52</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1">
+    <row r="71" spans="1:16">
       <c r="A71" s="25">
         <v>70</v>
       </c>
@@ -32845,21 +32842,21 @@
         <v>1687</v>
       </c>
       <c r="F71" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>1661</v>
       </c>
       <c r="H71" s="26"/>
       <c r="I71" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J71" s="26"/>
       <c r="K71" s="26"/>
       <c r="L71" s="26"/>
       <c r="M71" s="22"/>
       <c r="N71" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O71" s="24" t="s">
         <v>1647</v>
@@ -32868,7 +32865,7 @@
         <v>429991.38</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1">
+    <row r="72" spans="1:16">
       <c r="A72" s="21">
         <v>71</v>
       </c>
@@ -32885,21 +32882,21 @@
         <v>1687</v>
       </c>
       <c r="F72" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H72" s="26"/>
       <c r="I72" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J72" s="26"/>
       <c r="K72" s="26"/>
       <c r="L72" s="26"/>
       <c r="M72" s="22"/>
       <c r="N72" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O72" s="24" t="s">
         <v>1619</v>
@@ -32908,7 +32905,7 @@
         <v>156971.1</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1">
+    <row r="73" spans="1:16">
       <c r="A73" s="21">
         <v>72</v>
       </c>
@@ -32925,21 +32922,21 @@
         <v>1687</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H73" s="26"/>
       <c r="I73" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J73" s="26"/>
       <c r="K73" s="26"/>
       <c r="L73" s="26"/>
       <c r="M73" s="22"/>
       <c r="N73" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O73" s="24" t="s">
         <v>1619</v>
@@ -32965,21 +32962,21 @@
         <v>1687</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H74" s="26"/>
       <c r="I74" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J74" s="26"/>
       <c r="K74" s="26"/>
       <c r="L74" s="26"/>
       <c r="M74" s="22"/>
       <c r="N74" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O74" s="24" t="s">
         <v>1619</v>
@@ -32988,7 +32985,7 @@
         <v>156971.1</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1">
+    <row r="75" spans="1:16">
       <c r="A75" s="21">
         <v>74</v>
       </c>
@@ -33002,17 +32999,17 @@
         <v>1630</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F75" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H75" s="26"/>
       <c r="I75" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J75" s="26"/>
       <c r="K75" s="26"/>
@@ -33021,7 +33018,7 @@
         <v>1334</v>
       </c>
       <c r="N75" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O75" s="24" t="s">
         <v>1619</v>
@@ -33030,7 +33027,7 @@
         <v>547345</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1">
+    <row r="76" spans="1:16">
       <c r="A76" s="21">
         <v>75</v>
       </c>
@@ -33044,17 +33041,17 @@
         <v>1629</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H76" s="26"/>
       <c r="I76" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J76" s="26"/>
       <c r="K76" s="26"/>
@@ -33063,7 +33060,7 @@
         <v>1334</v>
       </c>
       <c r="N76" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O76" s="24" t="s">
         <v>1619</v>
@@ -33072,7 +33069,7 @@
         <v>547345</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1">
+    <row r="77" spans="1:16">
       <c r="A77" s="25">
         <v>76</v>
       </c>
@@ -33086,17 +33083,17 @@
         <v>1628</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H77" s="26"/>
       <c r="I77" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J77" s="26"/>
       <c r="K77" s="26"/>
@@ -33105,7 +33102,7 @@
         <v>1334</v>
       </c>
       <c r="N77" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O77" s="24" t="s">
         <v>1619</v>
@@ -33114,7 +33111,7 @@
         <v>547345</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1">
+    <row r="78" spans="1:16">
       <c r="A78" s="21">
         <v>77</v>
       </c>
@@ -33128,17 +33125,17 @@
         <v>1627</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H78" s="26"/>
       <c r="I78" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J78" s="26"/>
       <c r="K78" s="26"/>
@@ -33147,7 +33144,7 @@
         <v>1334</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O78" s="24" t="s">
         <v>1619</v>
@@ -33156,7 +33153,7 @@
         <v>547345</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1">
+    <row r="79" spans="1:16">
       <c r="A79" s="21">
         <v>78</v>
       </c>
@@ -33170,17 +33167,17 @@
         <v>1626</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H79" s="26"/>
       <c r="I79" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J79" s="26"/>
       <c r="K79" s="26"/>
@@ -33189,7 +33186,7 @@
         <v>1342</v>
       </c>
       <c r="N79" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O79" s="24" t="s">
         <v>1619</v>
@@ -33198,7 +33195,7 @@
         <v>686315.29999999993</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1">
+    <row r="80" spans="1:16">
       <c r="A80" s="25">
         <v>79</v>
       </c>
@@ -33212,17 +33209,17 @@
         <v>1625</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H80" s="26"/>
       <c r="I80" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J80" s="26"/>
       <c r="K80" s="26"/>
@@ -33231,7 +33228,7 @@
         <v>1342</v>
       </c>
       <c r="N80" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O80" s="24" t="s">
         <v>1619</v>
@@ -33240,7 +33237,7 @@
         <v>686315.29999999993</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1">
+    <row r="81" spans="1:16">
       <c r="A81" s="21">
         <v>80</v>
       </c>
@@ -33254,17 +33251,17 @@
         <v>1624</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H81" s="26"/>
       <c r="I81" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J81" s="26"/>
       <c r="K81" s="26"/>
@@ -33273,7 +33270,7 @@
         <v>1348</v>
       </c>
       <c r="N81" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O81" s="24" t="s">
         <v>1619</v>
@@ -33282,7 +33279,7 @@
         <v>501709.20000000007</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1">
+    <row r="82" spans="1:16">
       <c r="A82" s="21">
         <v>81</v>
       </c>
@@ -33296,17 +33293,17 @@
         <v>1623</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H82" s="26"/>
       <c r="I82" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J82" s="26"/>
       <c r="K82" s="26"/>
@@ -33315,7 +33312,7 @@
         <v>1348</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O82" s="24" t="s">
         <v>1619</v>
@@ -33324,7 +33321,7 @@
         <v>501709.20000000007</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1">
+    <row r="83" spans="1:16">
       <c r="A83" s="25">
         <v>82</v>
       </c>
@@ -33338,17 +33335,17 @@
         <v>1622</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H83" s="26"/>
       <c r="I83" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J83" s="26"/>
       <c r="K83" s="26"/>
@@ -33357,7 +33354,7 @@
         <v>1354</v>
       </c>
       <c r="N83" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O83" s="24" t="s">
         <v>1619</v>
@@ -33366,7 +33363,7 @@
         <v>506827.5</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1">
+    <row r="84" spans="1:16">
       <c r="A84" s="21">
         <v>83</v>
       </c>
@@ -33380,17 +33377,17 @@
         <v>1621</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G84" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H84" s="26"/>
       <c r="I84" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J84" s="26"/>
       <c r="K84" s="26"/>
@@ -33399,7 +33396,7 @@
         <v>1354</v>
       </c>
       <c r="N84" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O84" s="24" t="s">
         <v>1619</v>
@@ -33408,7 +33405,7 @@
         <v>506827.5</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1">
+    <row r="85" spans="1:16">
       <c r="A85" s="21">
         <v>84</v>
       </c>
@@ -33422,17 +33419,17 @@
         <v>1362</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F85" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>1618</v>
       </c>
       <c r="H85" s="26"/>
       <c r="I85" s="26" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J85" s="26"/>
       <c r="K85" s="26"/>
@@ -33441,7 +33438,7 @@
         <v>1620</v>
       </c>
       <c r="N85" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O85" s="24" t="s">
         <v>1619</v>
@@ -33450,7 +33447,7 @@
         <v>949365.05999999994</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1">
+    <row r="86" spans="1:16">
       <c r="A86" s="25">
         <v>85</v>
       </c>
@@ -33476,7 +33473,7 @@
         <v>19.05</v>
       </c>
       <c r="I86" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J86" s="21" t="s">
         <v>1810</v>
@@ -33498,7 +33495,7 @@
         <v>93181.9</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1">
+    <row r="87" spans="1:16">
       <c r="A87" s="21">
         <v>86</v>
       </c>
@@ -33524,7 +33521,7 @@
         <v>19.05</v>
       </c>
       <c r="I87" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J87" s="21" t="s">
         <v>1807</v>
@@ -33546,7 +33543,7 @@
         <v>119688.31299999999</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1">
+    <row r="88" spans="1:16">
       <c r="A88" s="21">
         <v>87</v>
       </c>
@@ -33572,7 +33569,7 @@
         <v>19.05</v>
       </c>
       <c r="I88" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J88" s="21" t="s">
         <v>1802</v>
@@ -33594,7 +33591,7 @@
         <v>145597.9</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1">
+    <row r="89" spans="1:16">
       <c r="A89" s="25">
         <v>88</v>
       </c>
@@ -33620,7 +33617,7 @@
         <v>19.05</v>
       </c>
       <c r="I89" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J89" s="21" t="s">
         <v>1801</v>
@@ -33642,7 +33639,7 @@
         <v>171805.19999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1">
+    <row r="90" spans="1:16">
       <c r="A90" s="21">
         <v>89</v>
       </c>
@@ -33668,7 +33665,7 @@
         <v>19.05</v>
       </c>
       <c r="I90" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J90" s="21" t="s">
         <v>1792</v>
@@ -33690,7 +33687,7 @@
         <v>195883.8</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1">
+    <row r="91" spans="1:16">
       <c r="A91" s="21">
         <v>90</v>
       </c>
@@ -33716,7 +33713,7 @@
         <v>19.05</v>
       </c>
       <c r="I91" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J91" s="21" t="s">
         <v>1787</v>
@@ -33738,7 +33735,7 @@
         <v>219961.69999999998</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1">
+    <row r="92" spans="1:16">
       <c r="A92" s="25">
         <v>91</v>
       </c>
@@ -33764,7 +33761,7 @@
         <v>19.05</v>
       </c>
       <c r="I92" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J92" s="21" t="s">
         <v>1840</v>
@@ -33786,7 +33783,7 @@
         <v>248343.9</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1">
+    <row r="93" spans="1:16">
       <c r="A93" s="21">
         <v>92</v>
       </c>
@@ -33812,7 +33809,7 @@
         <v>19.05</v>
       </c>
       <c r="I93" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J93" s="21" t="s">
         <v>1838</v>
@@ -33834,7 +33831,7 @@
         <v>276725.39999999997</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1">
+    <row r="94" spans="1:16">
       <c r="A94" s="21">
         <v>93</v>
       </c>
@@ -33860,7 +33857,7 @@
         <v>19.05</v>
       </c>
       <c r="I94" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J94" s="21" t="s">
         <v>1834</v>
@@ -33882,7 +33879,7 @@
         <v>286526.09999999998</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1">
+    <row r="95" spans="1:16">
       <c r="A95" s="25">
         <v>94</v>
       </c>
@@ -33908,7 +33905,7 @@
         <v>19.05</v>
       </c>
       <c r="I95" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J95" s="21" t="s">
         <v>1833</v>
@@ -33930,7 +33927,7 @@
         <v>296327.5</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1">
+    <row r="96" spans="1:16">
       <c r="A96" s="21">
         <v>95</v>
       </c>
@@ -33956,7 +33953,7 @@
         <v>19.05</v>
       </c>
       <c r="I96" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J96" s="21" t="s">
         <v>1831</v>
@@ -33978,7 +33975,7 @@
         <v>320948.59999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1">
+    <row r="97" spans="1:16">
       <c r="A97" s="21">
         <v>96</v>
       </c>
@@ -34004,7 +34001,7 @@
         <v>19.05</v>
       </c>
       <c r="I97" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J97" s="21" t="s">
         <v>1829</v>
@@ -34026,7 +34023,7 @@
         <v>345569</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1">
+    <row r="98" spans="1:16">
       <c r="A98" s="25">
         <v>97</v>
       </c>
@@ -34052,7 +34049,7 @@
         <v>19.05</v>
       </c>
       <c r="I98" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J98" s="21" t="s">
         <v>1827</v>
@@ -34074,7 +34071,7 @@
         <v>459918.89999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1">
+    <row r="99" spans="1:16">
       <c r="A99" s="21">
         <v>98</v>
       </c>
@@ -34100,7 +34097,7 @@
         <v>19.05</v>
       </c>
       <c r="I99" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J99" s="21"/>
       <c r="K99" s="21" t="s">
@@ -34120,7 +34117,7 @@
         <v>599860.1</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1">
+    <row r="100" spans="1:16">
       <c r="A100" s="21"/>
       <c r="B100" s="21">
         <v>1</v>
@@ -34144,7 +34141,7 @@
         <v>19.05</v>
       </c>
       <c r="I100" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J100" s="21" t="s">
         <v>1824</v>
@@ -34166,7 +34163,7 @@
         <v>132655.6</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1">
+    <row r="101" spans="1:16">
       <c r="A101" s="21"/>
       <c r="B101" s="21">
         <v>2</v>
@@ -34190,7 +34187,7 @@
         <v>19.05</v>
       </c>
       <c r="I101" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J101" s="21" t="s">
         <v>1823</v>
@@ -34212,7 +34209,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1">
+    <row r="102" spans="1:16">
       <c r="A102" s="21"/>
       <c r="B102" s="21">
         <v>3</v>
@@ -34236,7 +34233,7 @@
         <v>19.05</v>
       </c>
       <c r="I102" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J102" s="21" t="s">
         <v>1821</v>
@@ -34258,7 +34255,7 @@
         <v>244402.19999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1">
+    <row r="103" spans="1:16">
       <c r="A103" s="21"/>
       <c r="B103" s="21">
         <v>4</v>
@@ -34282,7 +34279,7 @@
         <v>19.05</v>
       </c>
       <c r="I103" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J103" s="21" t="s">
         <v>1809</v>
@@ -34304,7 +34301,7 @@
         <v>307472.89999999997</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1">
+    <row r="104" spans="1:16">
       <c r="A104" s="21"/>
       <c r="B104" s="21">
         <v>5</v>
@@ -34328,7 +34325,7 @@
         <v>19.05</v>
       </c>
       <c r="I104" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J104" s="21" t="s">
         <v>1796</v>
@@ -34350,7 +34347,7 @@
         <v>329253.39999999997</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1">
+    <row r="105" spans="1:16">
       <c r="A105" s="21"/>
       <c r="B105" s="21">
         <v>6</v>
@@ -34374,7 +34371,7 @@
         <v>19.05</v>
       </c>
       <c r="I105" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J105" s="21" t="s">
         <v>1813</v>
@@ -34396,7 +34393,7 @@
         <v>383966.1</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1">
+    <row r="106" spans="1:16">
       <c r="A106" s="21"/>
       <c r="B106" s="21">
         <v>7</v>
@@ -34420,7 +34417,7 @@
         <v>25.4</v>
       </c>
       <c r="I106" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J106" s="21" t="s">
         <v>1810</v>
@@ -34442,7 +34439,7 @@
         <v>134596</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1">
+    <row r="107" spans="1:16">
       <c r="A107" s="21"/>
       <c r="B107" s="21">
         <v>8</v>
@@ -34466,7 +34463,7 @@
         <v>25.4</v>
       </c>
       <c r="I107" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J107" s="21" t="s">
         <v>1807</v>
@@ -34488,7 +34485,7 @@
         <v>172452</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1">
+    <row r="108" spans="1:16">
       <c r="A108" s="21"/>
       <c r="B108" s="21">
         <v>9</v>
@@ -34512,7 +34509,7 @@
         <v>25.4</v>
       </c>
       <c r="I108" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J108" s="21" t="s">
         <v>1802</v>
@@ -34534,7 +34531,7 @@
         <v>210307.3</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1">
+    <row r="109" spans="1:16">
       <c r="A109" s="21"/>
       <c r="B109" s="21">
         <v>10</v>
@@ -34558,7 +34555,7 @@
         <v>25.4</v>
       </c>
       <c r="I109" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J109" s="21" t="s">
         <v>1801</v>
@@ -34580,7 +34577,7 @@
         <v>248163.3</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1">
+    <row r="110" spans="1:16">
       <c r="A110" s="21"/>
       <c r="B110" s="21">
         <v>11</v>
@@ -34604,7 +34601,7 @@
         <v>25.4</v>
       </c>
       <c r="I110" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J110" s="21" t="s">
         <v>1800</v>
@@ -34626,7 +34623,7 @@
         <v>362700.79999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1">
+    <row r="111" spans="1:16">
       <c r="A111" s="21"/>
       <c r="B111" s="21">
         <v>12</v>
@@ -34650,7 +34647,7 @@
         <v>25.4</v>
       </c>
       <c r="I111" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J111" s="21" t="s">
         <v>1787</v>
@@ -34672,7 +34669,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1">
+    <row r="112" spans="1:16">
       <c r="A112" s="21"/>
       <c r="B112" s="21">
         <v>13</v>
@@ -34696,7 +34693,7 @@
         <v>25.4</v>
       </c>
       <c r="I112" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J112" s="21"/>
       <c r="K112" s="21" t="s">
@@ -34716,7 +34713,7 @@
         <v>599860.1</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1">
+    <row r="113" spans="1:16">
       <c r="A113" s="21"/>
       <c r="B113" s="21">
         <v>14</v>
@@ -34740,7 +34737,7 @@
         <v>19.05</v>
       </c>
       <c r="I113" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J113" s="21" t="s">
         <v>1810</v>
@@ -34762,7 +34759,7 @@
         <v>82829.599999999991</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1">
+    <row r="114" spans="1:16">
       <c r="A114" s="21"/>
       <c r="B114" s="21">
         <v>15</v>
@@ -34786,7 +34783,7 @@
         <v>19.05</v>
       </c>
       <c r="I114" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J114" s="21" t="s">
         <v>1807</v>
@@ -34808,7 +34805,7 @@
         <v>106124.9</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1">
+    <row r="115" spans="1:16">
       <c r="A115" s="21"/>
       <c r="B115" s="21">
         <v>16</v>
@@ -34832,7 +34829,7 @@
         <v>19.05</v>
       </c>
       <c r="I115" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J115" s="21" t="s">
         <v>1802</v>
@@ -34854,7 +34851,7 @@
         <v>129420.2</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1">
+    <row r="116" spans="1:16">
       <c r="A116" s="21"/>
       <c r="B116" s="21">
         <v>17</v>
@@ -34878,7 +34875,7 @@
         <v>19.05</v>
       </c>
       <c r="I116" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J116" s="21" t="s">
         <v>1801</v>
@@ -34900,7 +34897,7 @@
         <v>152716.19999999998</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1">
+    <row r="117" spans="1:16">
       <c r="A117" s="21"/>
       <c r="B117" s="21">
         <v>18</v>
@@ -34924,7 +34921,7 @@
         <v>19.05</v>
       </c>
       <c r="I117" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J117" s="21" t="s">
         <v>1792</v>
@@ -34946,7 +34943,7 @@
         <v>174119.4</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1">
+    <row r="118" spans="1:16">
       <c r="A118" s="21"/>
       <c r="B118" s="21">
         <v>19</v>
@@ -34970,7 +34967,7 @@
         <v>19.05</v>
       </c>
       <c r="I118" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J118" s="21" t="s">
         <v>1810</v>
@@ -34992,7 +34989,7 @@
         <v>82829.599999999991</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1">
+    <row r="119" spans="1:16">
       <c r="A119" s="21"/>
       <c r="B119" s="21">
         <v>20</v>
@@ -35016,7 +35013,7 @@
         <v>19.05</v>
       </c>
       <c r="I119" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J119" s="21" t="s">
         <v>1807</v>
@@ -35038,7 +35035,7 @@
         <v>106124.9</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1">
+    <row r="120" spans="1:16">
       <c r="A120" s="21"/>
       <c r="B120" s="21">
         <v>21</v>
@@ -35062,7 +35059,7 @@
         <v>19.05</v>
       </c>
       <c r="I120" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J120" s="21" t="s">
         <v>1802</v>
@@ -35084,7 +35081,7 @@
         <v>129420.2</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1">
+    <row r="121" spans="1:16">
       <c r="A121" s="21"/>
       <c r="B121" s="21">
         <v>22</v>
@@ -35108,7 +35105,7 @@
         <v>19.05</v>
       </c>
       <c r="I121" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J121" s="21" t="s">
         <v>1801</v>
@@ -35130,7 +35127,7 @@
         <v>152716.19999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1">
+    <row r="122" spans="1:16">
       <c r="A122" s="21"/>
       <c r="B122" s="21">
         <v>23</v>
@@ -35154,7 +35151,7 @@
         <v>19.05</v>
       </c>
       <c r="I122" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J122" s="21" t="s">
         <v>1792</v>
@@ -35176,7 +35173,7 @@
         <v>174119.4</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1">
+    <row r="123" spans="1:16">
       <c r="A123" s="21"/>
       <c r="B123" s="21">
         <v>24</v>
@@ -35200,7 +35197,7 @@
         <v>19.05</v>
       </c>
       <c r="I123" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J123" s="21" t="s">
         <v>1787</v>
@@ -35222,7 +35219,7 @@
         <v>195521.19999999998</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1">
+    <row r="124" spans="1:16">
       <c r="A124" s="21"/>
       <c r="B124" s="21">
         <v>25</v>
@@ -35246,7 +35243,7 @@
         <v>19.05</v>
       </c>
       <c r="I124" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J124" s="21" t="s">
         <v>1840</v>
@@ -35268,7 +35265,7 @@
         <v>220750.59999999998</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1">
+    <row r="125" spans="1:16">
       <c r="A125" s="21"/>
       <c r="B125" s="21">
         <v>26</v>
@@ -35292,7 +35289,7 @@
         <v>19.05</v>
       </c>
       <c r="I125" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J125" s="21" t="s">
         <v>1838</v>
@@ -35314,7 +35311,7 @@
         <v>245978.59999999998</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1">
+    <row r="126" spans="1:16">
       <c r="A126" s="21"/>
       <c r="B126" s="21">
         <v>27</v>
@@ -35338,7 +35335,7 @@
         <v>19.05</v>
       </c>
       <c r="I126" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J126" s="21" t="s">
         <v>1834</v>
@@ -35360,7 +35357,7 @@
         <v>254690.8</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1">
+    <row r="127" spans="1:16">
       <c r="A127" s="21"/>
       <c r="B127" s="21">
         <v>28</v>
@@ -35384,7 +35381,7 @@
         <v>19.05</v>
       </c>
       <c r="I127" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J127" s="21" t="s">
         <v>1833</v>
@@ -35406,7 +35403,7 @@
         <v>263402.3</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1">
+    <row r="128" spans="1:16">
       <c r="A128" s="21"/>
       <c r="B128" s="21">
         <v>29</v>
@@ -35430,7 +35427,7 @@
         <v>19.05</v>
       </c>
       <c r="I128" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J128" s="21" t="s">
         <v>1831</v>
@@ -35452,7 +35449,7 @@
         <v>285287.8</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1">
+    <row r="129" spans="1:16">
       <c r="A129" s="21"/>
       <c r="B129" s="21">
         <v>30</v>
@@ -35476,7 +35473,7 @@
         <v>19.05</v>
       </c>
       <c r="I129" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J129" s="21" t="s">
         <v>1829</v>
@@ -35498,7 +35495,7 @@
         <v>307172.59999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1">
+    <row r="130" spans="1:16">
       <c r="A130" s="21"/>
       <c r="B130" s="21">
         <v>31</v>
@@ -35522,7 +35519,7 @@
         <v>19.05</v>
       </c>
       <c r="I130" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J130" s="21" t="s">
         <v>1827</v>
@@ -35544,7 +35541,7 @@
         <v>408817.5</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1">
+    <row r="131" spans="1:16">
       <c r="A131" s="21"/>
       <c r="B131" s="21">
         <v>32</v>
@@ -35568,7 +35565,7 @@
         <v>19.05</v>
       </c>
       <c r="I131" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J131" s="21"/>
       <c r="K131" s="21" t="s">
@@ -35590,7 +35587,7 @@
         <v>505209.59999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1">
+    <row r="132" spans="1:16">
       <c r="A132" s="21"/>
       <c r="B132" s="21">
         <v>33</v>
@@ -35614,7 +35611,7 @@
         <v>19.05</v>
       </c>
       <c r="I132" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J132" s="21" t="s">
         <v>1824</v>
@@ -35636,7 +35633,7 @@
         <v>106124.9</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1">
+    <row r="133" spans="1:16">
       <c r="A133" s="21"/>
       <c r="B133" s="21">
         <v>34</v>
@@ -35660,7 +35657,7 @@
         <v>19.05</v>
       </c>
       <c r="I133" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J133" s="21" t="s">
         <v>1823</v>
@@ -35682,7 +35679,7 @@
         <v>152716.19999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1">
+    <row r="134" spans="1:16">
       <c r="A134" s="21"/>
       <c r="B134" s="21">
         <v>35</v>
@@ -35706,7 +35703,7 @@
         <v>19.05</v>
       </c>
       <c r="I134" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J134" s="21" t="s">
         <v>1821</v>
@@ -35728,7 +35725,7 @@
         <v>195521.19999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1">
+    <row r="135" spans="1:16">
       <c r="A135" s="21"/>
       <c r="B135" s="21">
         <v>36</v>
@@ -35752,7 +35749,7 @@
         <v>19.05</v>
       </c>
       <c r="I135" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J135" s="21" t="s">
         <v>1809</v>
@@ -35774,7 +35771,7 @@
         <v>245978.59999999998</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1">
+    <row r="136" spans="1:16">
       <c r="A136" s="21"/>
       <c r="B136" s="21">
         <v>37</v>
@@ -35798,7 +35795,7 @@
         <v>19.05</v>
       </c>
       <c r="I136" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J136" s="21" t="s">
         <v>1796</v>
@@ -35820,7 +35817,7 @@
         <v>263402.3</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1">
+    <row r="137" spans="1:16">
       <c r="A137" s="21"/>
       <c r="B137" s="21">
         <v>38</v>
@@ -35844,7 +35841,7 @@
         <v>19.05</v>
       </c>
       <c r="I137" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J137" s="21" t="s">
         <v>1813</v>
@@ -35866,7 +35863,7 @@
         <v>307172.59999999998</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1">
+    <row r="138" spans="1:16">
       <c r="A138" s="21"/>
       <c r="B138" s="21">
         <v>39</v>
@@ -35890,7 +35887,7 @@
         <v>25.4</v>
       </c>
       <c r="I138" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J138" s="21" t="s">
         <v>1810</v>
@@ -35912,7 +35909,7 @@
         <v>107677.5</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1">
+    <row r="139" spans="1:16">
       <c r="A139" s="21"/>
       <c r="B139" s="21">
         <v>40</v>
@@ -35936,7 +35933,7 @@
         <v>25.4</v>
       </c>
       <c r="I139" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J139" s="21" t="s">
         <v>1807</v>
@@ -35958,7 +35955,7 @@
         <v>137961.59999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1">
+    <row r="140" spans="1:16">
       <c r="A140" s="21"/>
       <c r="B140" s="21">
         <v>41</v>
@@ -35982,7 +35979,7 @@
         <v>25.4</v>
       </c>
       <c r="I140" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J140" s="21" t="s">
         <v>1802</v>
@@ -36004,7 +36001,7 @@
         <v>168246.39999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1">
+    <row r="141" spans="1:16">
       <c r="A141" s="21"/>
       <c r="B141" s="21">
         <v>42</v>
@@ -36028,7 +36025,7 @@
         <v>25.4</v>
       </c>
       <c r="I141" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J141" s="21" t="s">
         <v>1801</v>
@@ -36050,7 +36047,7 @@
         <v>198530.5</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1">
+    <row r="142" spans="1:16">
       <c r="A142" s="21"/>
       <c r="B142" s="21">
         <v>43</v>
@@ -36074,7 +36071,7 @@
         <v>25.4</v>
       </c>
       <c r="I142" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J142" s="21" t="s">
         <v>1792</v>
@@ -36096,7 +36093,7 @@
         <v>290159.8</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1">
+    <row r="143" spans="1:16">
       <c r="A143" s="21"/>
       <c r="B143" s="21">
         <v>44</v>
@@ -36120,7 +36117,7 @@
         <v>25.4</v>
       </c>
       <c r="I143" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J143" s="21" t="s">
         <v>1787</v>
@@ -36142,7 +36139,7 @@
         <v>254176.99999999997</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1">
+    <row r="144" spans="1:16">
       <c r="A144" s="21"/>
       <c r="B144" s="21">
         <v>45</v>
@@ -36166,7 +36163,7 @@
         <v>19.05</v>
       </c>
       <c r="I144" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J144" s="21" t="s">
         <v>1810</v>
@@ -36188,7 +36185,7 @@
         <v>6125</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1">
+    <row r="145" spans="1:16">
       <c r="A145" s="21"/>
       <c r="B145" s="21">
         <v>46</v>
@@ -36212,7 +36209,7 @@
         <v>19.05</v>
       </c>
       <c r="I145" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J145" s="21" t="s">
         <v>1810</v>
@@ -36234,7 +36231,7 @@
         <v>6125</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1">
+    <row r="146" spans="1:16">
       <c r="A146" s="21"/>
       <c r="B146" s="21">
         <v>47</v>
@@ -36258,7 +36255,7 @@
         <v>19.05</v>
       </c>
       <c r="I146" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J146" s="21" t="s">
         <v>1810</v>
@@ -36280,7 +36277,7 @@
         <v>6125</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1">
+    <row r="147" spans="1:16">
       <c r="A147" s="21"/>
       <c r="B147" s="21">
         <v>48</v>
@@ -36304,7 +36301,7 @@
         <v>19.05</v>
       </c>
       <c r="I147" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J147" s="21" t="s">
         <v>1807</v>
@@ -36326,7 +36323,7 @@
         <v>6125</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1">
+    <row r="148" spans="1:16">
       <c r="A148" s="21"/>
       <c r="B148" s="21">
         <v>49</v>
@@ -36350,7 +36347,7 @@
         <v>19.05</v>
       </c>
       <c r="I148" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J148" s="21" t="s">
         <v>1807</v>
@@ -36372,7 +36369,7 @@
         <v>6125</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1">
+    <row r="149" spans="1:16">
       <c r="A149" s="21"/>
       <c r="B149" s="21">
         <v>50</v>
@@ -36396,7 +36393,7 @@
         <v>19.05</v>
       </c>
       <c r="I149" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J149" s="21" t="s">
         <v>1807</v>
@@ -36418,7 +36415,7 @@
         <v>6125</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1">
+    <row r="150" spans="1:16">
       <c r="A150" s="21"/>
       <c r="B150" s="21">
         <v>51</v>
@@ -36442,7 +36439,7 @@
         <v>19.05</v>
       </c>
       <c r="I150" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J150" s="21" t="s">
         <v>1802</v>
@@ -36464,7 +36461,7 @@
         <v>7044.7999999999993</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1">
+    <row r="151" spans="1:16">
       <c r="A151" s="21"/>
       <c r="B151" s="21">
         <v>52</v>
@@ -36488,7 +36485,7 @@
         <v>19.05</v>
       </c>
       <c r="I151" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J151" s="21" t="s">
         <v>1802</v>
@@ -36510,7 +36507,7 @@
         <v>7044.7999999999993</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1">
+    <row r="152" spans="1:16">
       <c r="A152" s="21"/>
       <c r="B152" s="21">
         <v>53</v>
@@ -36534,7 +36531,7 @@
         <v>19.05</v>
       </c>
       <c r="I152" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J152" s="21" t="s">
         <v>1802</v>
@@ -36556,7 +36553,7 @@
         <v>7044.7999999999993</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1">
+    <row r="153" spans="1:16">
       <c r="A153" s="21"/>
       <c r="B153" s="21">
         <v>54</v>
@@ -36580,7 +36577,7 @@
         <v>19.05</v>
       </c>
       <c r="I153" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J153" s="21" t="s">
         <v>1801</v>
@@ -36602,7 +36599,7 @@
         <v>8101.0999999999995</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1">
+    <row r="154" spans="1:16">
       <c r="A154" s="21"/>
       <c r="B154" s="21">
         <v>55</v>
@@ -36626,7 +36623,7 @@
         <v>19.05</v>
       </c>
       <c r="I154" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J154" s="21" t="s">
         <v>1801</v>
@@ -36648,7 +36645,7 @@
         <v>8101.0999999999995</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1">
+    <row r="155" spans="1:16">
       <c r="A155" s="21"/>
       <c r="B155" s="21">
         <v>56</v>
@@ -36672,7 +36669,7 @@
         <v>19.05</v>
       </c>
       <c r="I155" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J155" s="21" t="s">
         <v>1801</v>
@@ -36694,7 +36691,7 @@
         <v>8101.0999999999995</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1">
+    <row r="156" spans="1:16">
       <c r="A156" s="21"/>
       <c r="B156" s="21">
         <v>57</v>
@@ -36718,7 +36715,7 @@
         <v>19.05</v>
       </c>
       <c r="I156" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J156" s="21" t="s">
         <v>1792</v>
@@ -36740,7 +36737,7 @@
         <v>9316.2999999999993</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1">
+    <row r="157" spans="1:16">
       <c r="A157" s="21"/>
       <c r="B157" s="21">
         <v>58</v>
@@ -36764,7 +36761,7 @@
         <v>19.05</v>
       </c>
       <c r="I157" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J157" s="21" t="s">
         <v>1792</v>
@@ -36786,7 +36783,7 @@
         <v>9316.2999999999993</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1">
+    <row r="158" spans="1:16">
       <c r="A158" s="21"/>
       <c r="B158" s="21">
         <v>59</v>
@@ -36810,7 +36807,7 @@
         <v>19.05</v>
       </c>
       <c r="I158" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J158" s="21" t="s">
         <v>1792</v>
@@ -36832,7 +36829,7 @@
         <v>9316.2999999999993</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1">
+    <row r="159" spans="1:16">
       <c r="A159" s="21"/>
       <c r="B159" s="21">
         <v>60</v>
@@ -36856,7 +36853,7 @@
         <v>19.05</v>
       </c>
       <c r="I159" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J159" s="21" t="s">
         <v>1787</v>
@@ -36878,7 +36875,7 @@
         <v>10713.5</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1">
+    <row r="160" spans="1:16">
       <c r="A160" s="21"/>
       <c r="B160" s="21">
         <v>61</v>
@@ -36902,7 +36899,7 @@
         <v>19.05</v>
       </c>
       <c r="I160" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J160" s="21" t="s">
         <v>1787</v>
@@ -36924,7 +36921,7 @@
         <v>10713.5</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1">
+    <row r="161" spans="1:16">
       <c r="A161" s="21"/>
       <c r="B161" s="21">
         <v>62</v>
@@ -36948,7 +36945,7 @@
         <v>19.05</v>
       </c>
       <c r="I161" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J161" s="21" t="s">
         <v>1787</v>
@@ -36970,7 +36967,7 @@
         <v>10713.5</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1">
+    <row r="162" spans="1:16">
       <c r="A162" s="21"/>
       <c r="B162" s="21">
         <v>63</v>
@@ -36994,7 +36991,7 @@
         <v>19.05</v>
       </c>
       <c r="I162" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J162" s="21" t="s">
         <v>1840</v>
@@ -37016,7 +37013,7 @@
         <v>12321.4</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1">
+    <row r="163" spans="1:16">
       <c r="A163" s="21"/>
       <c r="B163" s="21">
         <v>64</v>
@@ -37040,7 +37037,7 @@
         <v>19.05</v>
       </c>
       <c r="I163" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J163" s="21" t="s">
         <v>1840</v>
@@ -37062,7 +37059,7 @@
         <v>12321.4</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1">
+    <row r="164" spans="1:16">
       <c r="A164" s="21"/>
       <c r="B164" s="21">
         <v>65</v>
@@ -37086,7 +37083,7 @@
         <v>19.05</v>
       </c>
       <c r="I164" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J164" s="21" t="s">
         <v>1840</v>
@@ -37108,7 +37105,7 @@
         <v>12321.4</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1">
+    <row r="165" spans="1:16">
       <c r="A165" s="21"/>
       <c r="B165" s="21">
         <v>66</v>
@@ -37132,7 +37129,7 @@
         <v>19.05</v>
       </c>
       <c r="I165" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J165" s="21" t="s">
         <v>1838</v>
@@ -37154,7 +37151,7 @@
         <v>14168</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1">
+    <row r="166" spans="1:16">
       <c r="A166" s="21"/>
       <c r="B166" s="21">
         <v>67</v>
@@ -37178,7 +37175,7 @@
         <v>19.05</v>
       </c>
       <c r="I166" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J166" s="21" t="s">
         <v>1838</v>
@@ -37200,7 +37197,7 @@
         <v>14168</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1">
+    <row r="167" spans="1:16">
       <c r="A167" s="21"/>
       <c r="B167" s="21">
         <v>68</v>
@@ -37224,7 +37221,7 @@
         <v>19.05</v>
       </c>
       <c r="I167" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J167" s="21" t="s">
         <v>1838</v>
@@ -37246,7 +37243,7 @@
         <v>14168</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1">
+    <row r="168" spans="1:16">
       <c r="A168" s="21"/>
       <c r="B168" s="21">
         <v>69</v>
@@ -37270,7 +37267,7 @@
         <v>19.05</v>
       </c>
       <c r="I168" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J168" s="21" t="s">
         <v>1834</v>
@@ -37292,7 +37289,7 @@
         <v>16293.9</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1">
+    <row r="169" spans="1:16">
       <c r="A169" s="21"/>
       <c r="B169" s="21">
         <v>70</v>
@@ -37316,7 +37313,7 @@
         <v>19.05</v>
       </c>
       <c r="I169" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J169" s="21" t="s">
         <v>1834</v>
@@ -37338,7 +37335,7 @@
         <v>16293.9</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1">
+    <row r="170" spans="1:16">
       <c r="A170" s="21"/>
       <c r="B170" s="21">
         <v>71</v>
@@ -37362,7 +37359,7 @@
         <v>19.05</v>
       </c>
       <c r="I170" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J170" s="21" t="s">
         <v>1834</v>
@@ -37384,7 +37381,7 @@
         <v>16293.9</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1">
+    <row r="171" spans="1:16">
       <c r="A171" s="21"/>
       <c r="B171" s="21">
         <v>72</v>
@@ -37408,7 +37405,7 @@
         <v>19.05</v>
       </c>
       <c r="I171" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J171" s="21" t="s">
         <v>1833</v>
@@ -37430,7 +37427,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1">
+    <row r="172" spans="1:16">
       <c r="A172" s="21"/>
       <c r="B172" s="21">
         <v>73</v>
@@ -37454,7 +37451,7 @@
         <v>19.05</v>
       </c>
       <c r="I172" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J172" s="21" t="s">
         <v>1833</v>
@@ -37476,7 +37473,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1">
+    <row r="173" spans="1:16">
       <c r="A173" s="21"/>
       <c r="B173" s="21">
         <v>74</v>
@@ -37500,7 +37497,7 @@
         <v>19.05</v>
       </c>
       <c r="I173" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J173" s="21" t="s">
         <v>1833</v>
@@ -37522,7 +37519,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1">
+    <row r="174" spans="1:16">
       <c r="A174" s="21"/>
       <c r="B174" s="21">
         <v>75</v>
@@ -37546,7 +37543,7 @@
         <v>19.05</v>
       </c>
       <c r="I174" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J174" s="21" t="s">
         <v>1831</v>
@@ -37568,7 +37565,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1">
+    <row r="175" spans="1:16">
       <c r="A175" s="21"/>
       <c r="B175" s="21">
         <v>76</v>
@@ -37592,7 +37589,7 @@
         <v>19.05</v>
       </c>
       <c r="I175" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J175" s="21" t="s">
         <v>1831</v>
@@ -37614,7 +37611,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1">
+    <row r="176" spans="1:16">
       <c r="A176" s="21"/>
       <c r="B176" s="21">
         <v>77</v>
@@ -37638,7 +37635,7 @@
         <v>19.05</v>
       </c>
       <c r="I176" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J176" s="21" t="s">
         <v>1831</v>
@@ -37660,7 +37657,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1">
+    <row r="177" spans="1:16">
       <c r="A177" s="21"/>
       <c r="B177" s="21">
         <v>78</v>
@@ -37684,7 +37681,7 @@
         <v>19.05</v>
       </c>
       <c r="I177" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J177" s="21" t="s">
         <v>1829</v>
@@ -37706,7 +37703,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1">
+    <row r="178" spans="1:16">
       <c r="A178" s="21"/>
       <c r="B178" s="21">
         <v>79</v>
@@ -37730,7 +37727,7 @@
         <v>19.05</v>
       </c>
       <c r="I178" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J178" s="21" t="s">
         <v>1829</v>
@@ -37752,7 +37749,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1">
+    <row r="179" spans="1:16">
       <c r="A179" s="21"/>
       <c r="B179" s="21">
         <v>80</v>
@@ -37776,7 +37773,7 @@
         <v>19.05</v>
       </c>
       <c r="I179" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J179" s="21" t="s">
         <v>1829</v>
@@ -37798,7 +37795,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1">
+    <row r="180" spans="1:16">
       <c r="A180" s="21"/>
       <c r="B180" s="21">
         <v>81</v>
@@ -37822,7 +37819,7 @@
         <v>19.05</v>
       </c>
       <c r="I180" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J180" s="21" t="s">
         <v>1827</v>
@@ -37844,7 +37841,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1">
+    <row r="181" spans="1:16">
       <c r="A181" s="21"/>
       <c r="B181" s="21">
         <v>82</v>
@@ -37868,7 +37865,7 @@
         <v>19.05</v>
       </c>
       <c r="I181" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J181" s="21" t="s">
         <v>1827</v>
@@ -37890,7 +37887,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1">
+    <row r="182" spans="1:16">
       <c r="A182" s="21"/>
       <c r="B182" s="21">
         <v>83</v>
@@ -37914,7 +37911,7 @@
         <v>19.05</v>
       </c>
       <c r="I182" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J182" s="21" t="s">
         <v>1827</v>
@@ -37936,7 +37933,7 @@
         <v>21548.799999999999</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1">
+    <row r="183" spans="1:16">
       <c r="A183" s="21"/>
       <c r="B183" s="21">
         <v>84</v>
@@ -37960,7 +37957,7 @@
         <v>19.05</v>
       </c>
       <c r="I183" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J183" s="21"/>
       <c r="K183" s="21" t="s">
@@ -37982,7 +37979,7 @@
         <v>30168.319999999996</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1">
+    <row r="184" spans="1:16">
       <c r="A184" s="21"/>
       <c r="B184" s="21">
         <v>85</v>
@@ -38006,7 +38003,7 @@
         <v>19.05</v>
       </c>
       <c r="I184" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J184" s="21"/>
       <c r="K184" s="21" t="s">
@@ -38028,7 +38025,7 @@
         <v>30168.319999999996</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1">
+    <row r="185" spans="1:16">
       <c r="A185" s="21"/>
       <c r="B185" s="21">
         <v>86</v>
@@ -38052,7 +38049,7 @@
         <v>19.05</v>
       </c>
       <c r="I185" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J185" s="21"/>
       <c r="K185" s="21" t="s">
@@ -38074,7 +38071,7 @@
         <v>30168.319999999996</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1">
+    <row r="186" spans="1:16">
       <c r="A186" s="21"/>
       <c r="B186" s="21">
         <v>87</v>
@@ -38098,7 +38095,7 @@
         <v>19.05</v>
       </c>
       <c r="I186" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J186" s="21" t="s">
         <v>1824</v>
@@ -38120,7 +38117,7 @@
         <v>5308.7999999999993</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1">
+    <row r="187" spans="1:16">
       <c r="A187" s="21"/>
       <c r="B187" s="21">
         <v>88</v>
@@ -38144,7 +38141,7 @@
         <v>19.05</v>
       </c>
       <c r="I187" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J187" s="21" t="s">
         <v>1824</v>
@@ -38166,7 +38163,7 @@
         <v>5308.7999999999993</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1">
+    <row r="188" spans="1:16">
       <c r="A188" s="21"/>
       <c r="B188" s="21">
         <v>89</v>
@@ -38190,7 +38187,7 @@
         <v>19.05</v>
       </c>
       <c r="I188" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J188" s="21" t="s">
         <v>1824</v>
@@ -38212,7 +38209,7 @@
         <v>5308.7999999999993</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1">
+    <row r="189" spans="1:16">
       <c r="A189" s="21"/>
       <c r="B189" s="21">
         <v>90</v>
@@ -38236,7 +38233,7 @@
         <v>19.05</v>
       </c>
       <c r="I189" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J189" s="21" t="s">
         <v>1823</v>
@@ -38258,7 +38255,7 @@
         <v>5308.7999999999993</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1">
+    <row r="190" spans="1:16">
       <c r="A190" s="21"/>
       <c r="B190" s="21">
         <v>91</v>
@@ -38282,7 +38279,7 @@
         <v>19.05</v>
       </c>
       <c r="I190" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J190" s="21" t="s">
         <v>1823</v>
@@ -38304,7 +38301,7 @@
         <v>5308.7999999999993</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1">
+    <row r="191" spans="1:16">
       <c r="A191" s="21"/>
       <c r="B191" s="21">
         <v>92</v>
@@ -38328,7 +38325,7 @@
         <v>19.05</v>
       </c>
       <c r="I191" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J191" s="21" t="s">
         <v>1823</v>
@@ -38350,7 +38347,7 @@
         <v>5308.7999999999993</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1">
+    <row r="192" spans="1:16">
       <c r="A192" s="21"/>
       <c r="B192" s="21">
         <v>93</v>
@@ -38374,7 +38371,7 @@
         <v>19.05</v>
       </c>
       <c r="I192" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J192" s="21" t="s">
         <v>1821</v>
@@ -38396,7 +38393,7 @@
         <v>6105.4</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1">
+    <row r="193" spans="1:16">
       <c r="A193" s="21"/>
       <c r="B193" s="21">
         <v>94</v>
@@ -38420,7 +38417,7 @@
         <v>19.05</v>
       </c>
       <c r="I193" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J193" s="21" t="s">
         <v>1821</v>
@@ -38442,7 +38439,7 @@
         <v>6105.4</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1">
+    <row r="194" spans="1:16">
       <c r="A194" s="21"/>
       <c r="B194" s="21">
         <v>95</v>
@@ -38466,7 +38463,7 @@
         <v>19.05</v>
       </c>
       <c r="I194" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J194" s="21" t="s">
         <v>1821</v>
@@ -38488,7 +38485,7 @@
         <v>6105.4</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1">
+    <row r="195" spans="1:16">
       <c r="A195" s="21"/>
       <c r="B195" s="21">
         <v>96</v>
@@ -38512,7 +38509,7 @@
         <v>19.05</v>
       </c>
       <c r="I195" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J195" s="21" t="s">
         <v>1809</v>
@@ -38534,7 +38531,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1">
+    <row r="196" spans="1:16">
       <c r="A196" s="21"/>
       <c r="B196" s="21">
         <v>97</v>
@@ -38558,7 +38555,7 @@
         <v>19.05</v>
       </c>
       <c r="I196" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J196" s="21" t="s">
         <v>1809</v>
@@ -38580,7 +38577,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1">
+    <row r="197" spans="1:16">
       <c r="A197" s="21"/>
       <c r="B197" s="21">
         <v>98</v>
@@ -38604,7 +38601,7 @@
         <v>19.05</v>
       </c>
       <c r="I197" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J197" s="21" t="s">
         <v>1809</v>
@@ -38626,7 +38623,7 @@
         <v>7021</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1">
+    <row r="198" spans="1:16">
       <c r="A198" s="21"/>
       <c r="B198" s="21">
         <v>99</v>
@@ -38650,7 +38647,7 @@
         <v>19.05</v>
       </c>
       <c r="I198" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J198" s="21" t="s">
         <v>1796</v>
@@ -38672,7 +38669,7 @@
         <v>8074.4999999999991</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1">
+    <row r="199" spans="1:16">
       <c r="A199" s="21"/>
       <c r="B199" s="21">
         <v>100</v>
@@ -38696,7 +38693,7 @@
         <v>19.05</v>
       </c>
       <c r="I199" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J199" s="21" t="s">
         <v>1796</v>
@@ -38718,7 +38715,7 @@
         <v>8074.4999999999991</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1">
+    <row r="200" spans="1:16">
       <c r="A200" s="21"/>
       <c r="B200" s="21">
         <v>101</v>
@@ -38742,7 +38739,7 @@
         <v>19.05</v>
       </c>
       <c r="I200" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J200" s="21" t="s">
         <v>1796</v>
@@ -38764,7 +38761,7 @@
         <v>8074.4999999999991</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1">
+    <row r="201" spans="1:16">
       <c r="A201" s="21"/>
       <c r="B201" s="21">
         <v>102</v>
@@ -38788,7 +38785,7 @@
         <v>19.05</v>
       </c>
       <c r="I201" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J201" s="21" t="s">
         <v>1813</v>
@@ -38810,7 +38807,7 @@
         <v>9285.5</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1">
+    <row r="202" spans="1:16">
       <c r="A202" s="21"/>
       <c r="B202" s="21">
         <v>103</v>
@@ -38834,7 +38831,7 @@
         <v>19.05</v>
       </c>
       <c r="I202" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J202" s="21" t="s">
         <v>1813</v>
@@ -38856,7 +38853,7 @@
         <v>9285.5</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1">
+    <row r="203" spans="1:16">
       <c r="A203" s="21"/>
       <c r="B203" s="21">
         <v>104</v>
@@ -38880,7 +38877,7 @@
         <v>19.05</v>
       </c>
       <c r="I203" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J203" s="21" t="s">
         <v>1813</v>
@@ -38902,7 +38899,7 @@
         <v>9285.5</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1">
+    <row r="204" spans="1:16">
       <c r="A204" s="21"/>
       <c r="B204" s="21">
         <v>105</v>
@@ -38926,7 +38923,7 @@
         <v>25.4</v>
       </c>
       <c r="I204" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J204" s="21" t="s">
         <v>1810</v>
@@ -38948,7 +38945,7 @@
         <v>7349.9999999999991</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1">
+    <row r="205" spans="1:16">
       <c r="A205" s="21"/>
       <c r="B205" s="21">
         <v>106</v>
@@ -38972,7 +38969,7 @@
         <v>25.4</v>
       </c>
       <c r="I205" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J205" s="21" t="s">
         <v>1810</v>
@@ -38994,7 +38991,7 @@
         <v>7349.9999999999991</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1">
+    <row r="206" spans="1:16">
       <c r="A206" s="21"/>
       <c r="B206" s="21">
         <v>107</v>
@@ -39018,7 +39015,7 @@
         <v>25.4</v>
       </c>
       <c r="I206" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J206" s="21" t="s">
         <v>1810</v>
@@ -39040,7 +39037,7 @@
         <v>7349.9999999999991</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1">
+    <row r="207" spans="1:16">
       <c r="A207" s="21"/>
       <c r="B207" s="21">
         <v>108</v>
@@ -39064,7 +39061,7 @@
         <v>25.4</v>
       </c>
       <c r="I207" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J207" s="21" t="s">
         <v>1807</v>
@@ -39086,7 +39083,7 @@
         <v>7349.9999999999991</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1">
+    <row r="208" spans="1:16">
       <c r="A208" s="21"/>
       <c r="B208" s="21">
         <v>109</v>
@@ -39110,7 +39107,7 @@
         <v>25.4</v>
       </c>
       <c r="I208" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J208" s="21" t="s">
         <v>1807</v>
@@ -39132,7 +39129,7 @@
         <v>7349.9999999999991</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1">
+    <row r="209" spans="1:16">
       <c r="A209" s="21"/>
       <c r="B209" s="21">
         <v>110</v>
@@ -39156,7 +39153,7 @@
         <v>25.4</v>
       </c>
       <c r="I209" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J209" s="21" t="s">
         <v>1807</v>
@@ -39178,7 +39175,7 @@
         <v>7349.9999999999991</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1">
+    <row r="210" spans="1:16">
       <c r="A210" s="21"/>
       <c r="B210" s="21">
         <v>111</v>
@@ -39202,7 +39199,7 @@
         <v>25.4</v>
       </c>
       <c r="I210" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J210" s="21" t="s">
         <v>1802</v>
@@ -39224,7 +39221,7 @@
         <v>8453.7599999999984</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1">
+    <row r="211" spans="1:16">
       <c r="A211" s="21"/>
       <c r="B211" s="21">
         <v>112</v>
@@ -39248,7 +39245,7 @@
         <v>25.4</v>
       </c>
       <c r="I211" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J211" s="21" t="s">
         <v>1802</v>
@@ -39270,7 +39267,7 @@
         <v>8453.7599999999984</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1">
+    <row r="212" spans="1:16">
       <c r="A212" s="21"/>
       <c r="B212" s="21">
         <v>113</v>
@@ -39294,7 +39291,7 @@
         <v>25.4</v>
       </c>
       <c r="I212" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J212" s="21" t="s">
         <v>1802</v>
@@ -39316,7 +39313,7 @@
         <v>8453.7599999999984</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1">
+    <row r="213" spans="1:16">
       <c r="A213" s="21"/>
       <c r="B213" s="21">
         <v>114</v>
@@ -39340,7 +39337,7 @@
         <v>25.4</v>
       </c>
       <c r="I213" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J213" s="21" t="s">
         <v>1801</v>
@@ -39362,7 +39359,7 @@
         <v>9721.32</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1">
+    <row r="214" spans="1:16">
       <c r="A214" s="21"/>
       <c r="B214" s="21">
         <v>115</v>
@@ -39386,7 +39383,7 @@
         <v>25.4</v>
       </c>
       <c r="I214" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J214" s="21" t="s">
         <v>1801</v>
@@ -39408,7 +39405,7 @@
         <v>9721.32</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1">
+    <row r="215" spans="1:16">
       <c r="A215" s="21"/>
       <c r="B215" s="21">
         <v>116</v>
@@ -39432,7 +39429,7 @@
         <v>25.4</v>
       </c>
       <c r="I215" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J215" s="21" t="s">
         <v>1801</v>
@@ -39454,7 +39451,7 @@
         <v>9721.32</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1">
+    <row r="216" spans="1:16">
       <c r="A216" s="21"/>
       <c r="B216" s="21">
         <v>117</v>
@@ -39478,7 +39475,7 @@
         <v>25.4</v>
       </c>
       <c r="I216" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J216" s="21" t="s">
         <v>1792</v>
@@ -39500,7 +39497,7 @@
         <v>11179.56</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1">
+    <row r="217" spans="1:16">
       <c r="A217" s="21"/>
       <c r="B217" s="21">
         <v>118</v>
@@ -39524,7 +39521,7 @@
         <v>25.4</v>
       </c>
       <c r="I217" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J217" s="21" t="s">
         <v>1792</v>
@@ -39546,7 +39543,7 @@
         <v>11179.56</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1">
+    <row r="218" spans="1:16">
       <c r="A218" s="21"/>
       <c r="B218" s="21">
         <v>119</v>
@@ -39570,7 +39567,7 @@
         <v>25.4</v>
       </c>
       <c r="I218" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J218" s="21" t="s">
         <v>1792</v>
@@ -39592,7 +39589,7 @@
         <v>11179.56</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1">
+    <row r="219" spans="1:16">
       <c r="A219" s="21"/>
       <c r="B219" s="21">
         <v>120</v>
@@ -39616,7 +39613,7 @@
         <v>25.4</v>
       </c>
       <c r="I219" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J219" s="21" t="s">
         <v>1787</v>
@@ -39638,7 +39635,7 @@
         <v>12800</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1">
+    <row r="220" spans="1:16">
       <c r="A220" s="21"/>
       <c r="B220" s="21">
         <v>121</v>
@@ -39662,7 +39659,7 @@
         <v>25.4</v>
       </c>
       <c r="I220" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J220" s="21" t="s">
         <v>1787</v>
@@ -39684,7 +39681,7 @@
         <v>12800</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1">
+    <row r="221" spans="1:16">
       <c r="A221" s="21"/>
       <c r="B221" s="21">
         <v>122</v>
@@ -39708,7 +39705,7 @@
         <v>25.4</v>
       </c>
       <c r="I221" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J221" s="21" t="s">
         <v>1787</v>
@@ -39730,7 +39727,7 @@
         <v>12800</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1">
+    <row r="222" spans="1:16">
       <c r="A222" s="21"/>
       <c r="B222" s="21">
         <v>123</v>
@@ -39754,7 +39751,7 @@
         <v>25.4</v>
       </c>
       <c r="I222" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J222" s="21"/>
       <c r="K222" s="21" t="s">
@@ -39776,7 +39773,7 @@
         <v>19284.3</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1">
+    <row r="223" spans="1:16">
       <c r="A223" s="21"/>
       <c r="B223" s="21">
         <v>124</v>
@@ -39800,7 +39797,7 @@
         <v>25.4</v>
       </c>
       <c r="I223" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J223" s="21"/>
       <c r="K223" s="21" t="s">
@@ -39822,7 +39819,7 @@
         <v>19284.3</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1">
+    <row r="224" spans="1:16">
       <c r="A224" s="21"/>
       <c r="B224" s="21">
         <v>125</v>
@@ -39846,7 +39843,7 @@
         <v>25.4</v>
       </c>
       <c r="I224" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J224" s="21"/>
       <c r="K224" s="21" t="s">
@@ -39868,7 +39865,7 @@
         <v>19284.3</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1">
+    <row r="225" spans="1:16">
       <c r="A225" s="21"/>
       <c r="B225" s="21">
         <v>126</v>
@@ -39886,7 +39883,7 @@
       </c>
       <c r="H225" s="21"/>
       <c r="I225" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J225" s="21"/>
       <c r="K225" s="21"/>
@@ -39902,7 +39899,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1">
+    <row r="226" spans="1:16">
       <c r="A226" s="21"/>
       <c r="B226" s="21">
         <v>127</v>
@@ -39922,7 +39919,7 @@
       </c>
       <c r="H226" s="21"/>
       <c r="I226" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J226" s="21"/>
       <c r="K226" s="21"/>
@@ -39938,7 +39935,7 @@
         <v>326.89999999999998</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1">
+    <row r="227" spans="1:16">
       <c r="A227" s="21"/>
       <c r="B227" s="21">
         <v>128</v>
@@ -39958,7 +39955,7 @@
       </c>
       <c r="H227" s="21"/>
       <c r="I227" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J227" s="21"/>
       <c r="K227" s="21"/>
@@ -39974,7 +39971,7 @@
         <v>816.9</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1">
+    <row r="228" spans="1:16">
       <c r="A228" s="21"/>
       <c r="B228" s="21">
         <v>129</v>
@@ -39994,7 +39991,7 @@
       </c>
       <c r="H228" s="21"/>
       <c r="I228" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J228" s="21"/>
       <c r="K228" s="21"/>
@@ -40010,7 +40007,7 @@
         <v>979.99999999999989</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1">
+    <row r="229" spans="1:16">
       <c r="A229" s="21"/>
       <c r="B229" s="21">
         <v>130</v>
@@ -40030,7 +40027,7 @@
       </c>
       <c r="H229" s="21"/>
       <c r="I229" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J229" s="21"/>
       <c r="K229" s="21"/>
@@ -40046,7 +40043,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="230" spans="1:16" hidden="1">
+    <row r="230" spans="1:16">
       <c r="A230" s="21"/>
       <c r="B230" s="21">
         <v>131</v>
@@ -40066,7 +40063,7 @@
       </c>
       <c r="H230" s="21"/>
       <c r="I230" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J230" s="21"/>
       <c r="K230" s="21"/>
@@ -40082,7 +40079,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="231" spans="1:16" hidden="1">
+    <row r="231" spans="1:16">
       <c r="A231" s="21"/>
       <c r="B231" s="21">
         <v>132</v>
@@ -40102,7 +40099,7 @@
       </c>
       <c r="H231" s="21"/>
       <c r="I231" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J231" s="21"/>
       <c r="K231" s="21"/>
@@ -40118,7 +40115,7 @@
         <v>1796.8999999999999</v>
       </c>
     </row>
-    <row r="232" spans="1:16" hidden="1">
+    <row r="232" spans="1:16">
       <c r="A232" s="21"/>
       <c r="B232" s="21">
         <v>133</v>
@@ -40138,7 +40135,7 @@
       </c>
       <c r="H232" s="21"/>
       <c r="I232" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J232" s="21"/>
       <c r="K232" s="21"/>
@@ -40154,7 +40151,7 @@
         <v>2041.8999999999999</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1">
+    <row r="233" spans="1:16">
       <c r="A233" s="21"/>
       <c r="B233" s="21">
         <v>134</v>
@@ -40174,7 +40171,7 @@
       </c>
       <c r="H233" s="21"/>
       <c r="I233" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J233" s="21"/>
       <c r="K233" s="21"/>
@@ -40190,7 +40187,7 @@
         <v>2286.8999999999996</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1">
+    <row r="234" spans="1:16">
       <c r="A234" s="21"/>
       <c r="B234" s="21">
         <v>135</v>
@@ -40210,7 +40207,7 @@
       </c>
       <c r="H234" s="21"/>
       <c r="I234" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J234" s="21"/>
       <c r="K234" s="21"/>
@@ -40226,7 +40223,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1">
+    <row r="235" spans="1:16">
       <c r="A235" s="21"/>
       <c r="B235" s="21">
         <v>136</v>
@@ -40246,7 +40243,7 @@
       </c>
       <c r="H235" s="21"/>
       <c r="I235" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J235" s="21"/>
       <c r="K235" s="21"/>
@@ -40262,7 +40259,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="236" spans="1:16" hidden="1">
+    <row r="236" spans="1:16">
       <c r="A236" s="21"/>
       <c r="B236" s="21">
         <v>137</v>
@@ -40282,7 +40279,7 @@
       </c>
       <c r="H236" s="21"/>
       <c r="I236" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J236" s="21"/>
       <c r="K236" s="21"/>
@@ -40298,7 +40295,7 @@
         <v>653.79999999999995</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1">
+    <row r="237" spans="1:16">
       <c r="A237" s="21"/>
       <c r="B237" s="21">
         <v>138</v>
@@ -40318,7 +40315,7 @@
       </c>
       <c r="H237" s="21"/>
       <c r="I237" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J237" s="21"/>
       <c r="K237" s="21"/>
@@ -40334,7 +40331,7 @@
         <v>1633.8</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1">
+    <row r="238" spans="1:16">
       <c r="A238" s="21"/>
       <c r="B238" s="21">
         <v>139</v>
@@ -40354,7 +40351,7 @@
       </c>
       <c r="H238" s="21"/>
       <c r="I238" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J238" s="21"/>
       <c r="K238" s="21"/>
@@ -40370,7 +40367,7 @@
         <v>1959.9999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1">
+    <row r="239" spans="1:16">
       <c r="A239" s="21"/>
       <c r="B239" s="21">
         <v>140</v>
@@ -40390,7 +40387,7 @@
       </c>
       <c r="H239" s="21"/>
       <c r="I239" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J239" s="21"/>
       <c r="K239" s="21"/>
@@ -40406,7 +40403,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1">
+    <row r="240" spans="1:16">
       <c r="A240" s="21"/>
       <c r="B240" s="21">
         <v>141</v>
@@ -40426,7 +40423,7 @@
       </c>
       <c r="H240" s="21"/>
       <c r="I240" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J240" s="21"/>
       <c r="K240" s="21"/>
@@ -40442,7 +40439,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1">
+    <row r="241" spans="1:16">
       <c r="A241" s="21"/>
       <c r="B241" s="21">
         <v>142</v>
@@ -40462,7 +40459,7 @@
       </c>
       <c r="H241" s="21"/>
       <c r="I241" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J241" s="21"/>
       <c r="K241" s="21"/>
@@ -40478,7 +40475,7 @@
         <v>3593.7999999999997</v>
       </c>
     </row>
-    <row r="242" spans="1:16" hidden="1">
+    <row r="242" spans="1:16">
       <c r="A242" s="21"/>
       <c r="B242" s="21">
         <v>143</v>
@@ -40498,7 +40495,7 @@
       </c>
       <c r="H242" s="21"/>
       <c r="I242" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J242" s="21"/>
       <c r="K242" s="21"/>
@@ -40514,7 +40511,7 @@
         <v>4083.7999999999997</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1">
+    <row r="243" spans="1:16">
       <c r="A243" s="21"/>
       <c r="B243" s="21">
         <v>144</v>
@@ -40534,7 +40531,7 @@
       </c>
       <c r="H243" s="21"/>
       <c r="I243" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J243" s="21"/>
       <c r="K243" s="21"/>
@@ -40550,7 +40547,7 @@
         <v>4573.7999999999993</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1">
+    <row r="244" spans="1:16">
       <c r="A244" s="21"/>
       <c r="B244" s="21">
         <v>145</v>
@@ -40570,7 +40567,7 @@
       </c>
       <c r="H244" s="21"/>
       <c r="I244" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J244" s="21"/>
       <c r="K244" s="21"/>
@@ -40586,7 +40583,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1">
+    <row r="245" spans="1:16">
       <c r="A245" s="21"/>
       <c r="B245" s="21">
         <v>146</v>
@@ -40606,7 +40603,7 @@
       </c>
       <c r="H245" s="21"/>
       <c r="I245" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J245" s="21"/>
       <c r="K245" s="21"/>
@@ -40622,7 +40619,7 @@
         <v>5880</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1">
+    <row r="246" spans="1:16">
       <c r="A246" s="21"/>
       <c r="B246" s="21">
         <v>147</v>
@@ -40642,7 +40639,7 @@
       </c>
       <c r="H246" s="21"/>
       <c r="I246" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J246" s="21"/>
       <c r="K246" s="21"/>
@@ -40658,7 +40655,7 @@
         <v>9800</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1">
+    <row r="247" spans="1:16">
       <c r="A247" s="21"/>
       <c r="B247" s="21">
         <v>148</v>
@@ -40678,7 +40675,7 @@
       </c>
       <c r="H247" s="21"/>
       <c r="I247" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J247" s="21"/>
       <c r="K247" s="21"/>
@@ -40694,7 +40691,7 @@
         <v>326.89999999999998</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1">
+    <row r="248" spans="1:16">
       <c r="A248" s="21"/>
       <c r="B248" s="21">
         <v>149</v>
@@ -40714,7 +40711,7 @@
       </c>
       <c r="H248" s="21"/>
       <c r="I248" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J248" s="21"/>
       <c r="K248" s="21"/>
@@ -40730,7 +40727,7 @@
         <v>816.9</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1">
+    <row r="249" spans="1:16">
       <c r="A249" s="21"/>
       <c r="B249" s="21">
         <v>150</v>
@@ -40750,7 +40747,7 @@
       </c>
       <c r="H249" s="21"/>
       <c r="I249" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J249" s="21"/>
       <c r="K249" s="21"/>
@@ -40766,7 +40763,7 @@
         <v>979.99999999999989</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1">
+    <row r="250" spans="1:16">
       <c r="A250" s="21"/>
       <c r="B250" s="21">
         <v>151</v>
@@ -40786,7 +40783,7 @@
       </c>
       <c r="H250" s="21"/>
       <c r="I250" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J250" s="21"/>
       <c r="K250" s="21"/>
@@ -40802,7 +40799,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1">
+    <row r="251" spans="1:16">
       <c r="A251" s="21"/>
       <c r="B251" s="21">
         <v>152</v>
@@ -40822,7 +40819,7 @@
       </c>
       <c r="H251" s="21"/>
       <c r="I251" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J251" s="21"/>
       <c r="K251" s="21"/>
@@ -40838,7 +40835,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1">
+    <row r="252" spans="1:16">
       <c r="A252" s="21"/>
       <c r="B252" s="21">
         <v>153</v>
@@ -40858,7 +40855,7 @@
       </c>
       <c r="H252" s="21"/>
       <c r="I252" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J252" s="21"/>
       <c r="K252" s="21"/>
@@ -40874,7 +40871,7 @@
         <v>1796.8999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1">
+    <row r="253" spans="1:16">
       <c r="A253" s="21"/>
       <c r="B253" s="21">
         <v>154</v>
@@ -40894,7 +40891,7 @@
       </c>
       <c r="H253" s="21"/>
       <c r="I253" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J253" s="21"/>
       <c r="K253" s="21"/>
@@ -40910,7 +40907,7 @@
         <v>2041.8999999999999</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1">
+    <row r="254" spans="1:16">
       <c r="A254" s="21"/>
       <c r="B254" s="21">
         <v>155</v>
@@ -40930,7 +40927,7 @@
       </c>
       <c r="H254" s="21"/>
       <c r="I254" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J254" s="21"/>
       <c r="K254" s="21"/>
@@ -40946,7 +40943,7 @@
         <v>2286.8999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1">
+    <row r="255" spans="1:16">
       <c r="A255" s="21"/>
       <c r="B255" s="21">
         <v>156</v>
@@ -40966,7 +40963,7 @@
       </c>
       <c r="H255" s="21"/>
       <c r="I255" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J255" s="21"/>
       <c r="K255" s="21"/>
@@ -40982,7 +40979,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1">
+    <row r="256" spans="1:16">
       <c r="A256" s="21"/>
       <c r="B256" s="21">
         <v>157</v>
@@ -41002,7 +40999,7 @@
       </c>
       <c r="H256" s="21"/>
       <c r="I256" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J256" s="21"/>
       <c r="K256" s="21"/>
@@ -41018,7 +41015,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1">
+    <row r="257" spans="1:16">
       <c r="A257" s="21"/>
       <c r="B257" s="21">
         <v>158</v>
@@ -41038,7 +41035,7 @@
       </c>
       <c r="H257" s="21"/>
       <c r="I257" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J257" s="21"/>
       <c r="K257" s="21"/>
@@ -41054,7 +41051,7 @@
         <v>653.79999999999995</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1">
+    <row r="258" spans="1:16">
       <c r="A258" s="21"/>
       <c r="B258" s="21">
         <v>159</v>
@@ -41074,7 +41071,7 @@
       </c>
       <c r="H258" s="21"/>
       <c r="I258" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J258" s="21"/>
       <c r="K258" s="21"/>
@@ -41090,7 +41087,7 @@
         <v>1633.8</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1">
+    <row r="259" spans="1:16">
       <c r="A259" s="21"/>
       <c r="B259" s="21">
         <v>160</v>
@@ -41110,7 +41107,7 @@
       </c>
       <c r="H259" s="21"/>
       <c r="I259" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J259" s="21"/>
       <c r="K259" s="21"/>
@@ -41126,7 +41123,7 @@
         <v>1959.9999999999998</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1">
+    <row r="260" spans="1:16">
       <c r="A260" s="21"/>
       <c r="B260" s="21">
         <v>161</v>
@@ -41146,7 +41143,7 @@
       </c>
       <c r="H260" s="21"/>
       <c r="I260" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J260" s="21"/>
       <c r="K260" s="21"/>
@@ -41162,7 +41159,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1">
+    <row r="261" spans="1:16">
       <c r="A261" s="21"/>
       <c r="B261" s="21">
         <v>162</v>
@@ -41182,7 +41179,7 @@
       </c>
       <c r="H261" s="21"/>
       <c r="I261" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J261" s="21"/>
       <c r="K261" s="21"/>
@@ -41198,7 +41195,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1">
+    <row r="262" spans="1:16">
       <c r="A262" s="21"/>
       <c r="B262" s="21">
         <v>163</v>
@@ -41218,7 +41215,7 @@
       </c>
       <c r="H262" s="21"/>
       <c r="I262" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J262" s="21"/>
       <c r="K262" s="21"/>
@@ -41234,7 +41231,7 @@
         <v>3593.7999999999997</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1">
+    <row r="263" spans="1:16">
       <c r="A263" s="21"/>
       <c r="B263" s="21">
         <v>164</v>
@@ -41254,7 +41251,7 @@
       </c>
       <c r="H263" s="21"/>
       <c r="I263" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J263" s="21"/>
       <c r="K263" s="21"/>
@@ -41270,7 +41267,7 @@
         <v>4083.7999999999997</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1">
+    <row r="264" spans="1:16">
       <c r="A264" s="21"/>
       <c r="B264" s="21">
         <v>165</v>
@@ -41290,7 +41287,7 @@
       </c>
       <c r="H264" s="21"/>
       <c r="I264" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J264" s="21"/>
       <c r="K264" s="21"/>
@@ -41306,7 +41303,7 @@
         <v>4573.7999999999993</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1">
+    <row r="265" spans="1:16">
       <c r="A265" s="21"/>
       <c r="B265" s="21">
         <v>166</v>
@@ -41326,7 +41323,7 @@
       </c>
       <c r="H265" s="21"/>
       <c r="I265" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J265" s="21"/>
       <c r="K265" s="21"/>
@@ -41342,7 +41339,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1">
+    <row r="266" spans="1:16">
       <c r="A266" s="21"/>
       <c r="B266" s="21">
         <v>167</v>
@@ -41362,7 +41359,7 @@
       </c>
       <c r="H266" s="21"/>
       <c r="I266" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J266" s="21"/>
       <c r="K266" s="21"/>
@@ -41378,7 +41375,7 @@
         <v>5880</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1">
+    <row r="267" spans="1:16">
       <c r="A267" s="21"/>
       <c r="B267" s="21">
         <v>168</v>
@@ -41398,7 +41395,7 @@
       </c>
       <c r="H267" s="21"/>
       <c r="I267" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J267" s="21"/>
       <c r="K267" s="21"/>
@@ -41414,7 +41411,7 @@
         <v>9800</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1">
+    <row r="268" spans="1:16">
       <c r="A268" s="21"/>
       <c r="B268" s="21">
         <v>169</v>
@@ -41436,7 +41433,7 @@
       </c>
       <c r="H268" s="21"/>
       <c r="I268" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J268" s="21"/>
       <c r="K268" s="21"/>
@@ -41452,7 +41449,7 @@
         <v>14699.999999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1">
+    <row r="269" spans="1:16">
       <c r="A269" s="21"/>
       <c r="B269" s="21">
         <v>170</v>
@@ -41474,7 +41471,7 @@
       </c>
       <c r="H269" s="21"/>
       <c r="I269" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J269" s="21"/>
       <c r="K269" s="21"/>
@@ -41490,7 +41487,7 @@
         <v>14699.999999999998</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1">
+    <row r="270" spans="1:16">
       <c r="A270" s="21"/>
       <c r="B270" s="21">
         <v>171</v>
@@ -41512,7 +41509,7 @@
       </c>
       <c r="H270" s="21"/>
       <c r="I270" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J270" s="21"/>
       <c r="K270" s="21"/>
@@ -41528,7 +41525,7 @@
         <v>22050</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1">
+    <row r="271" spans="1:16">
       <c r="A271" s="21"/>
       <c r="B271" s="21">
         <v>172</v>
@@ -41550,7 +41547,7 @@
       </c>
       <c r="H271" s="21"/>
       <c r="I271" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J271" s="21"/>
       <c r="K271" s="21"/>
@@ -41566,7 +41563,7 @@
         <v>22050</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1">
+    <row r="272" spans="1:16">
       <c r="A272" s="21"/>
       <c r="B272" s="21">
         <v>173</v>
@@ -41588,7 +41585,7 @@
       </c>
       <c r="H272" s="21"/>
       <c r="I272" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J272" s="21"/>
       <c r="K272" s="21"/>
@@ -41604,7 +41601,7 @@
         <v>36750</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1">
+    <row r="273" spans="1:16">
       <c r="A273" s="21"/>
       <c r="B273" s="21">
         <v>174</v>
@@ -41626,7 +41623,7 @@
       </c>
       <c r="H273" s="21"/>
       <c r="I273" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J273" s="21"/>
       <c r="K273" s="21"/>
@@ -41642,7 +41639,7 @@
         <v>36750</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1">
+    <row r="274" spans="1:16">
       <c r="A274" s="21"/>
       <c r="B274" s="21">
         <v>175</v>
@@ -41664,7 +41661,7 @@
       </c>
       <c r="H274" s="21"/>
       <c r="I274" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J274" s="21"/>
       <c r="K274" s="21"/>
@@ -41680,7 +41677,7 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1">
+    <row r="275" spans="1:16">
       <c r="A275" s="21"/>
       <c r="B275" s="21">
         <v>176</v>
@@ -41702,7 +41699,7 @@
       </c>
       <c r="H275" s="21"/>
       <c r="I275" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J275" s="21"/>
       <c r="K275" s="21"/>
@@ -41718,7 +41715,7 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1">
+    <row r="276" spans="1:16">
       <c r="A276" s="21"/>
       <c r="B276" s="21">
         <v>177</v>
@@ -41740,7 +41737,7 @@
       </c>
       <c r="H276" s="21"/>
       <c r="I276" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J276" s="21"/>
       <c r="K276" s="21"/>
@@ -41756,7 +41753,7 @@
         <v>49000</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1">
+    <row r="277" spans="1:16">
       <c r="A277" s="21"/>
       <c r="B277" s="21">
         <v>178</v>
@@ -41778,7 +41775,7 @@
       </c>
       <c r="H277" s="21"/>
       <c r="I277" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J277" s="21"/>
       <c r="K277" s="21"/>
@@ -41794,7 +41791,7 @@
         <v>13230</v>
       </c>
     </row>
-    <row r="278" spans="1:16" hidden="1">
+    <row r="278" spans="1:16">
       <c r="A278" s="21"/>
       <c r="B278" s="21">
         <v>179</v>
@@ -41816,7 +41813,7 @@
       </c>
       <c r="H278" s="21"/>
       <c r="I278" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J278" s="21"/>
       <c r="K278" s="21"/>
@@ -41832,7 +41829,7 @@
         <v>13230</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1">
+    <row r="279" spans="1:16">
       <c r="A279" s="21"/>
       <c r="B279" s="21">
         <v>180</v>
@@ -41854,7 +41851,7 @@
       </c>
       <c r="H279" s="21"/>
       <c r="I279" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J279" s="21"/>
       <c r="K279" s="21"/>
@@ -41870,7 +41867,7 @@
         <v>19845</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1">
+    <row r="280" spans="1:16">
       <c r="A280" s="21"/>
       <c r="B280" s="21">
         <v>181</v>
@@ -41892,7 +41889,7 @@
       </c>
       <c r="H280" s="21"/>
       <c r="I280" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J280" s="21"/>
       <c r="K280" s="21"/>
@@ -41908,7 +41905,7 @@
         <v>19845</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1">
+    <row r="281" spans="1:16">
       <c r="A281" s="21"/>
       <c r="B281" s="21">
         <v>182</v>
@@ -41930,7 +41927,7 @@
       </c>
       <c r="H281" s="21"/>
       <c r="I281" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J281" s="21"/>
       <c r="K281" s="21"/>
@@ -41946,7 +41943,7 @@
         <v>33075</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1">
+    <row r="282" spans="1:16">
       <c r="A282" s="21"/>
       <c r="B282" s="21">
         <v>183</v>
@@ -41968,7 +41965,7 @@
       </c>
       <c r="H282" s="21"/>
       <c r="I282" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J282" s="21"/>
       <c r="K282" s="21"/>
@@ -41984,7 +41981,7 @@
         <v>33075</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1">
+    <row r="283" spans="1:16">
       <c r="A283" s="21"/>
       <c r="B283" s="21">
         <v>184</v>
@@ -42006,7 +42003,7 @@
       </c>
       <c r="H283" s="21"/>
       <c r="I283" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J283" s="21"/>
       <c r="K283" s="21"/>
@@ -42022,7 +42019,7 @@
         <v>44100</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1">
+    <row r="284" spans="1:16">
       <c r="A284" s="21"/>
       <c r="B284" s="21">
         <v>185</v>
@@ -42044,7 +42041,7 @@
       </c>
       <c r="H284" s="21"/>
       <c r="I284" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J284" s="21"/>
       <c r="K284" s="21"/>
@@ -42060,7 +42057,7 @@
         <v>44100</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1">
+    <row r="285" spans="1:16">
       <c r="A285" s="21"/>
       <c r="B285" s="21">
         <v>186</v>
@@ -42082,7 +42079,7 @@
       </c>
       <c r="H285" s="21"/>
       <c r="I285" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J285" s="21"/>
       <c r="K285" s="21"/>
@@ -42098,7 +42095,7 @@
         <v>44100</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1">
+    <row r="286" spans="1:16">
       <c r="A286" s="21"/>
       <c r="B286" s="21">
         <v>187</v>
@@ -42116,7 +42113,7 @@
       </c>
       <c r="H286" s="21"/>
       <c r="I286" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J286" s="21"/>
       <c r="K286" s="21"/>
@@ -42130,7 +42127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1">
+    <row r="287" spans="1:16">
       <c r="A287" s="21"/>
       <c r="B287" s="21">
         <v>188</v>
@@ -42148,7 +42145,7 @@
       </c>
       <c r="H287" s="21"/>
       <c r="I287" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J287" s="21"/>
       <c r="K287" s="21"/>
@@ -42166,7 +42163,7 @@
         <v>38889.199999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1">
+    <row r="288" spans="1:16">
       <c r="A288" s="21"/>
       <c r="B288" s="21">
         <v>189</v>
@@ -42184,7 +42181,7 @@
       </c>
       <c r="H288" s="21"/>
       <c r="I288" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J288" s="21"/>
       <c r="K288" s="21"/>
@@ -42202,7 +42199,7 @@
         <v>22785</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1">
+    <row r="289" spans="1:16">
       <c r="A289" s="21"/>
       <c r="B289" s="21">
         <v>190</v>
@@ -42220,7 +42217,7 @@
       </c>
       <c r="H289" s="21"/>
       <c r="I289" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J289" s="21"/>
       <c r="K289" s="21"/>
@@ -42238,7 +42235,7 @@
         <v>4273.5</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1">
+    <row r="290" spans="1:16">
       <c r="A290" s="21"/>
       <c r="B290" s="21">
         <v>191</v>
@@ -42256,7 +42253,7 @@
       </c>
       <c r="H290" s="21"/>
       <c r="I290" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J290" s="21"/>
       <c r="K290" s="21"/>
@@ -42274,7 +42271,7 @@
         <v>25823</v>
       </c>
     </row>
-    <row r="291" spans="1:16" hidden="1">
+    <row r="291" spans="1:16">
       <c r="A291" s="21"/>
       <c r="B291" s="21">
         <v>192</v>
@@ -42292,7 +42289,7 @@
       </c>
       <c r="H291" s="21"/>
       <c r="I291" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J291" s="21"/>
       <c r="K291" s="21"/>
@@ -42310,7 +42307,7 @@
         <v>4842.5999999999995</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1">
+    <row r="292" spans="1:16">
       <c r="A292" s="21"/>
       <c r="B292" s="21">
         <v>193</v>
@@ -42328,7 +42325,7 @@
       </c>
       <c r="H292" s="21"/>
       <c r="I292" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J292" s="21"/>
       <c r="K292" s="21"/>
@@ -42344,7 +42341,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="293" spans="1:16" hidden="1">
+    <row r="293" spans="1:16">
       <c r="A293" s="21"/>
       <c r="B293" s="21">
         <v>194</v>
@@ -42362,7 +42359,7 @@
       </c>
       <c r="H293" s="21"/>
       <c r="I293" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J293" s="21"/>
       <c r="K293" s="21"/>
@@ -42380,7 +42377,7 @@
         <v>14699.999999999998</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1">
+    <row r="294" spans="1:16">
       <c r="A294" s="21"/>
       <c r="B294" s="21">
         <v>195</v>
@@ -42398,7 +42395,7 @@
       </c>
       <c r="H294" s="21"/>
       <c r="I294" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J294" s="21"/>
       <c r="K294" s="21"/>
@@ -42416,7 +42413,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1">
+    <row r="295" spans="1:16">
       <c r="A295" s="21"/>
       <c r="B295" s="21">
         <v>196</v>
@@ -42434,7 +42431,7 @@
       </c>
       <c r="H295" s="21"/>
       <c r="I295" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J295" s="21"/>
       <c r="K295" s="21"/>
@@ -42450,7 +42447,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1">
+    <row r="296" spans="1:16">
       <c r="A296" s="21"/>
       <c r="B296" s="21">
         <v>197</v>
@@ -42468,7 +42465,7 @@
       </c>
       <c r="H296" s="21"/>
       <c r="I296" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J296" s="21"/>
       <c r="K296" s="21"/>
@@ -42486,7 +42483,7 @@
         <v>16333.8</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1">
+    <row r="297" spans="1:16">
       <c r="A297" s="21"/>
       <c r="B297" s="21">
         <v>198</v>
@@ -42504,7 +42501,7 @@
       </c>
       <c r="H297" s="21"/>
       <c r="I297" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J297" s="21"/>
       <c r="K297" s="21"/>
@@ -42522,7 +42519,7 @@
         <v>27766.899999999998</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1">
+    <row r="298" spans="1:16">
       <c r="A298" s="21"/>
       <c r="B298" s="21">
         <v>199</v>
@@ -42540,7 +42537,7 @@
       </c>
       <c r="H298" s="21"/>
       <c r="I298" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J298" s="21"/>
       <c r="K298" s="21"/>
@@ -42558,7 +42555,7 @@
         <v>27766.899999999998</v>
       </c>
     </row>
-    <row r="299" spans="1:16" hidden="1">
+    <row r="299" spans="1:16">
       <c r="A299" s="21"/>
       <c r="B299" s="21">
         <v>200</v>
@@ -42576,7 +42573,7 @@
       </c>
       <c r="H299" s="21"/>
       <c r="I299" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J299" s="21"/>
       <c r="K299" s="21"/>
@@ -42594,7 +42591,7 @@
         <v>1633.8</v>
       </c>
     </row>
-    <row r="300" spans="1:16" hidden="1">
+    <row r="300" spans="1:16">
       <c r="A300" s="21"/>
       <c r="B300" s="21">
         <v>201</v>
@@ -42612,7 +42609,7 @@
       </c>
       <c r="H300" s="21"/>
       <c r="I300" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J300" s="21"/>
       <c r="K300" s="21"/>
@@ -42630,7 +42627,7 @@
         <v>32667.599999999999</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1">
+    <row r="301" spans="1:16">
       <c r="A301" s="21"/>
       <c r="B301" s="21">
         <v>202</v>
@@ -42648,7 +42645,7 @@
       </c>
       <c r="H301" s="21"/>
       <c r="I301" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J301" s="21"/>
       <c r="K301" s="21"/>
@@ -42666,7 +42663,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1">
+    <row r="302" spans="1:16">
       <c r="A302" s="21"/>
       <c r="B302" s="21">
         <v>203</v>
@@ -42684,7 +42681,7 @@
       </c>
       <c r="H302" s="21"/>
       <c r="I302" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J302" s="21"/>
       <c r="K302" s="21"/>
@@ -42702,7 +42699,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="303" spans="1:16" hidden="1">
+    <row r="303" spans="1:16">
       <c r="A303" s="21"/>
       <c r="B303" s="21">
         <v>204</v>
@@ -42722,7 +42719,7 @@
       </c>
       <c r="H303" s="21"/>
       <c r="I303" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J303" s="21"/>
       <c r="K303" s="21"/>
@@ -42740,7 +42737,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1">
+    <row r="304" spans="1:16">
       <c r="A304" s="21"/>
       <c r="B304" s="21">
         <v>205</v>
@@ -42760,7 +42757,7 @@
       </c>
       <c r="H304" s="21"/>
       <c r="I304" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J304" s="21"/>
       <c r="K304" s="21"/>
@@ -42778,7 +42775,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1">
+    <row r="305" spans="1:16">
       <c r="A305" s="21"/>
       <c r="B305" s="21">
         <v>206</v>
@@ -42798,7 +42795,7 @@
       </c>
       <c r="H305" s="21"/>
       <c r="I305" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J305" s="21"/>
       <c r="K305" s="21"/>
@@ -42816,7 +42813,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1">
+    <row r="306" spans="1:16">
       <c r="A306" s="21"/>
       <c r="B306" s="21">
         <v>207</v>
@@ -42836,7 +42833,7 @@
       </c>
       <c r="H306" s="21"/>
       <c r="I306" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J306" s="21"/>
       <c r="K306" s="21"/>
@@ -42854,7 +42851,7 @@
         <v>61249.999999999993</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1">
+    <row r="307" spans="1:16">
       <c r="A307" s="21"/>
       <c r="B307" s="21">
         <v>208</v>
@@ -42874,7 +42871,7 @@
       </c>
       <c r="H307" s="21"/>
       <c r="I307" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J307" s="21"/>
       <c r="K307" s="21"/>
@@ -42892,7 +42889,7 @@
         <v>81666.899999999994</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1">
+    <row r="308" spans="1:16">
       <c r="A308" s="21"/>
       <c r="B308" s="21">
         <v>209</v>
@@ -42912,7 +42909,7 @@
       </c>
       <c r="H308" s="21"/>
       <c r="I308" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J308" s="21"/>
       <c r="K308" s="21"/>
@@ -42930,7 +42927,7 @@
         <v>81666.899999999994</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1">
+    <row r="309" spans="1:16">
       <c r="A309" s="21"/>
       <c r="B309" s="21">
         <v>210</v>
@@ -42950,13 +42947,13 @@
       </c>
       <c r="H309" s="21"/>
       <c r="I309" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J309" s="21"/>
       <c r="K309" s="21"/>
       <c r="L309" s="21"/>
       <c r="M309" s="22" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="N309" s="21" t="s">
         <v>1658</v>
@@ -42968,7 +42965,7 @@
         <v>16333.8</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1">
+    <row r="310" spans="1:16">
       <c r="A310" s="21"/>
       <c r="B310" s="21">
         <v>211</v>
@@ -42988,7 +42985,7 @@
       </c>
       <c r="H310" s="21"/>
       <c r="I310" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J310" s="21"/>
       <c r="K310" s="21"/>
@@ -43006,7 +43003,7 @@
         <v>24500</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1">
+    <row r="311" spans="1:16">
       <c r="A311" s="21"/>
       <c r="B311" s="21">
         <v>212</v>
@@ -43026,7 +43023,7 @@
       </c>
       <c r="H311" s="21"/>
       <c r="I311" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J311" s="21"/>
       <c r="K311" s="21"/>
@@ -43044,7 +43041,7 @@
         <v>13883.8</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1">
+    <row r="312" spans="1:16">
       <c r="A312" s="21"/>
       <c r="B312" s="21">
         <v>213</v>
@@ -43064,7 +43061,7 @@
       </c>
       <c r="H312" s="21"/>
       <c r="I312" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J312" s="21"/>
       <c r="K312" s="21"/>
@@ -43082,7 +43079,7 @@
         <v>20416.899999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1">
+    <row r="313" spans="1:16">
       <c r="A313" s="21"/>
       <c r="B313" s="21">
         <v>214</v>
@@ -43102,7 +43099,7 @@
       </c>
       <c r="H313" s="21"/>
       <c r="I313" s="38" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J313" s="21"/>
       <c r="K313" s="21"/>
@@ -43120,7 +43117,7 @@
         <v>26950</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1">
+    <row r="314" spans="1:16">
       <c r="A314" s="21"/>
       <c r="B314" s="21">
         <v>215</v>
@@ -43140,7 +43137,7 @@
       </c>
       <c r="H314" s="21"/>
       <c r="I314" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J314" s="21"/>
       <c r="K314" s="21"/>
@@ -43158,7 +43155,7 @@
         <v>244.99999999999997</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1">
+    <row r="315" spans="1:16">
       <c r="A315" s="21"/>
       <c r="B315" s="21">
         <v>216</v>
@@ -43178,7 +43175,7 @@
       </c>
       <c r="H315" s="21"/>
       <c r="I315" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J315" s="21"/>
       <c r="K315" s="21"/>
@@ -43194,7 +43191,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1">
+    <row r="316" spans="1:16">
       <c r="A316" s="21"/>
       <c r="B316" s="21">
         <v>217</v>
@@ -43214,7 +43211,7 @@
       </c>
       <c r="H316" s="21"/>
       <c r="I316" s="21" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="J316" s="21"/>
       <c r="K316" s="21"/>
@@ -43230,7 +43227,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1">
+    <row r="317" spans="1:16">
       <c r="A317" s="21"/>
       <c r="B317" s="21">
         <v>218</v>
@@ -43245,7 +43242,7 @@
         <v>1659</v>
       </c>
       <c r="F317" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G317" s="26"/>
       <c r="H317" s="26"/>
@@ -43257,14 +43254,14 @@
       <c r="L317" s="26"/>
       <c r="M317" s="22"/>
       <c r="N317" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O317" s="24"/>
       <c r="P317" s="28">
         <v>80000</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1">
+    <row r="318" spans="1:16">
       <c r="A318" s="21"/>
       <c r="B318" s="21">
         <v>219</v>
@@ -43279,7 +43276,7 @@
         <v>1659</v>
       </c>
       <c r="F318" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G318" s="26"/>
       <c r="H318" s="26"/>
@@ -43291,14 +43288,14 @@
       <c r="L318" s="26"/>
       <c r="M318" s="22"/>
       <c r="N318" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O318" s="24"/>
       <c r="P318" s="28">
         <v>64000</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1">
+    <row r="319" spans="1:16">
       <c r="A319" s="21"/>
       <c r="B319" s="21">
         <v>220</v>
@@ -43313,7 +43310,7 @@
         <v>1659</v>
       </c>
       <c r="F319" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G319" s="26"/>
       <c r="H319" s="26"/>
@@ -43325,14 +43322,14 @@
       <c r="L319" s="26"/>
       <c r="M319" s="22"/>
       <c r="N319" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O319" s="24"/>
       <c r="P319" s="28">
         <v>80000</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1">
+    <row r="320" spans="1:16">
       <c r="A320" s="21"/>
       <c r="B320" s="21">
         <v>221</v>
@@ -43347,7 +43344,7 @@
         <v>1659</v>
       </c>
       <c r="F320" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G320" s="26"/>
       <c r="H320" s="26"/>
@@ -43359,14 +43356,14 @@
       <c r="L320" s="26"/>
       <c r="M320" s="22"/>
       <c r="N320" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O320" s="24"/>
       <c r="P320" s="28">
         <v>64000</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1">
+    <row r="321" spans="1:16">
       <c r="A321" s="21"/>
       <c r="B321" s="21">
         <v>222</v>
@@ -43381,7 +43378,7 @@
         <v>1659</v>
       </c>
       <c r="F321" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G321" s="26" t="s">
         <v>1661</v>
@@ -43395,14 +43392,14 @@
       <c r="L321" s="26"/>
       <c r="M321" s="22"/>
       <c r="N321" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O321" s="24"/>
       <c r="P321" s="28">
         <v>80000</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1">
+    <row r="322" spans="1:16">
       <c r="A322" s="21"/>
       <c r="B322" s="21">
         <v>223</v>
@@ -43417,7 +43414,7 @@
         <v>1659</v>
       </c>
       <c r="F322" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G322" s="26" t="s">
         <v>1661</v>
@@ -43431,14 +43428,14 @@
       <c r="L322" s="26"/>
       <c r="M322" s="22"/>
       <c r="N322" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O322" s="24"/>
       <c r="P322" s="28">
         <v>80000</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1">
+    <row r="323" spans="1:16">
       <c r="A323" s="21"/>
       <c r="B323" s="21">
         <v>224</v>
@@ -43453,7 +43450,7 @@
         <v>1660</v>
       </c>
       <c r="F323" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G323" s="26" t="s">
         <v>1618</v>
@@ -43467,14 +43464,14 @@
       <c r="L323" s="21"/>
       <c r="M323" s="22"/>
       <c r="N323" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O323" s="20"/>
       <c r="P323" s="28">
         <v>24000</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1">
+    <row r="324" spans="1:16">
       <c r="A324" s="21"/>
       <c r="B324" s="21">
         <v>225</v>
@@ -43489,7 +43486,7 @@
         <v>1659</v>
       </c>
       <c r="F324" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G324" s="26" t="s">
         <v>1618</v>
@@ -43503,14 +43500,14 @@
       <c r="L324" s="26"/>
       <c r="M324" s="22"/>
       <c r="N324" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O324" s="24"/>
       <c r="P324" s="28">
         <v>64000</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1">
+    <row r="325" spans="1:16">
       <c r="A325" s="21"/>
       <c r="B325" s="21">
         <v>226</v>
@@ -43525,7 +43522,7 @@
         <v>1659</v>
       </c>
       <c r="F325" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G325" s="26" t="s">
         <v>1618</v>
@@ -43539,14 +43536,14 @@
       <c r="L325" s="21"/>
       <c r="M325" s="22"/>
       <c r="N325" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O325" s="20"/>
       <c r="P325" s="28">
         <v>62400</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1">
+    <row r="326" spans="1:16">
       <c r="A326" s="21"/>
       <c r="B326" s="21">
         <v>227</v>
@@ -43561,7 +43558,7 @@
         <v>1660</v>
       </c>
       <c r="F326" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G326" s="26" t="s">
         <v>1618</v>
@@ -43575,14 +43572,14 @@
       <c r="L326" s="21"/>
       <c r="M326" s="22"/>
       <c r="N326" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O326" s="20"/>
       <c r="P326" s="28">
         <v>24000</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1">
+    <row r="327" spans="1:16">
       <c r="A327" s="21"/>
       <c r="B327" s="21">
         <v>228</v>
@@ -43597,7 +43594,7 @@
         <v>1659</v>
       </c>
       <c r="F327" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G327" s="26" t="s">
         <v>1618</v>
@@ -43611,14 +43608,14 @@
       <c r="L327" s="26"/>
       <c r="M327" s="22"/>
       <c r="N327" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O327" s="24"/>
       <c r="P327" s="28">
         <v>64000</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1">
+    <row r="328" spans="1:16">
       <c r="A328" s="21"/>
       <c r="B328" s="21">
         <v>229</v>
@@ -43633,7 +43630,7 @@
         <v>1659</v>
       </c>
       <c r="F328" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G328" s="26" t="s">
         <v>1618</v>
@@ -43647,7 +43644,7 @@
       <c r="L328" s="21"/>
       <c r="M328" s="22"/>
       <c r="N328" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O328" s="20"/>
       <c r="P328" s="28">
@@ -43669,7 +43666,7 @@
         <v>1660</v>
       </c>
       <c r="F329" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G329" s="26" t="s">
         <v>1618</v>
@@ -43683,7 +43680,7 @@
       <c r="L329" s="21"/>
       <c r="M329" s="22"/>
       <c r="N329" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O329" s="20"/>
       <c r="P329" s="28">
@@ -43705,7 +43702,7 @@
         <v>1659</v>
       </c>
       <c r="F330" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="G330" s="26" t="s">
         <v>1618</v>
@@ -43719,7 +43716,7 @@
       <c r="L330" s="26"/>
       <c r="M330" s="22"/>
       <c r="N330" s="25" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="O330" s="24"/>
       <c r="P330" s="28">
@@ -43728,11 +43725,6 @@
     </row>
   </sheetData>
   <autoFilter ref="D1:P330" xr:uid="{B7249BCB-8196-41A7-AE04-CC0472D33C99}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="4E-2709"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:P330">
       <sortCondition ref="I1:I330"/>
     </sortState>

--- a/HE_Database_PRO_FINAL.xlsx
+++ b/HE_Database_PRO_FINAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AD95C6-D64A-4476-B6CD-A4CD7320935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F46EED-CE47-4AFC-8BC4-D7388265C716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{0F496093-ED53-4580-9BCE-A3569CCA6B7A}"/>
   </bookViews>
   <sheets>
     <sheet name="SPEC" sheetId="7" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7511" uniqueCount="2119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7511" uniqueCount="2117">
   <si>
     <t>Description</t>
   </si>
@@ -6430,12 +6430,6 @@
     <t>E-1109A</t>
   </si>
   <si>
-    <t>SCOPE</t>
-  </si>
-  <si>
-    <t>he_tpye</t>
-  </si>
-  <si>
     <t>Heat Exchanger OD 19.05x6M U-Tube - Size 1001U-1200U-Tube</t>
   </si>
   <si>
@@ -6454,7 +6448,7 @@
     <t>Heat Exchanger OD 19.05x6M U-Tube - Size 801U-1000U-Tube</t>
   </si>
   <si>
-    <t>he_type</t>
+    <t>He_type</t>
   </si>
 </sst>
 </file>
@@ -7041,7 +7035,7 @@
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{2B9DC6D2-E66E-445C-99B2-2A378B8E1614}" name="Equipment No" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{2FD75069-8E36-4F4D-90CA-8C8527E128BE}" name="he_type"/>
+    <tableColumn id="2" xr3:uid="{2FD75069-8E36-4F4D-90CA-8C8527E128BE}" name="He_type"/>
     <tableColumn id="3" xr3:uid="{E354BEB2-0A6E-43E8-BCA4-9098BC17DDA1}" name="Description" dataDxfId="11"/>
     <tableColumn id="4" xr3:uid="{710BBEFA-D0B9-4DAB-ADEF-A516E13EEAE4}" name="Fluid.Shell" dataDxfId="10"/>
     <tableColumn id="5" xr3:uid="{2F13F828-20C0-4D02-8A83-EBC680158096}" name="Fluid.Tube" dataDxfId="9"/>
@@ -7382,7 +7376,7 @@
         <v>1609</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="C1" s="33" t="s">
         <v>0</v>
@@ -29872,10 +29866,10 @@
         <v>1842</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>2110</v>
+        <v>1612</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>2111</v>
+        <v>2116</v>
       </c>
       <c r="G1" s="12" t="s">
         <v>2068</v>
@@ -35445,7 +35439,7 @@
         <v>1791</v>
       </c>
       <c r="L137" s="22" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="M137" s="21" t="s">
         <v>1732</v>
@@ -35492,7 +35486,7 @@
         <v>1791</v>
       </c>
       <c r="L138" s="22" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="M138" s="21" t="s">
         <v>1732</v>
@@ -35539,7 +35533,7 @@
         <v>1791</v>
       </c>
       <c r="L139" s="22" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="M139" s="21" t="s">
         <v>1732</v>
@@ -35586,7 +35580,7 @@
         <v>1791</v>
       </c>
       <c r="L140" s="22" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="M140" s="21" t="s">
         <v>1732</v>
@@ -35633,7 +35627,7 @@
         <v>1791</v>
       </c>
       <c r="L141" s="22" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="M141" s="21" t="s">
         <v>1732</v>
@@ -35680,7 +35674,7 @@
         <v>1791</v>
       </c>
       <c r="L142" s="22" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="M142" s="21" t="s">
         <v>1732</v>
@@ -42051,7 +42045,7 @@
         <v>1791</v>
       </c>
       <c r="L283" s="22" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="M283" s="21" t="s">
         <v>1794</v>
@@ -42098,7 +42092,7 @@
         <v>1791</v>
       </c>
       <c r="L284" s="22" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="M284" s="21" t="s">
         <v>1794</v>
@@ -42145,7 +42139,7 @@
         <v>1791</v>
       </c>
       <c r="L285" s="22" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="M285" s="21" t="s">
         <v>1794</v>
@@ -42192,7 +42186,7 @@
         <v>1791</v>
       </c>
       <c r="L286" s="22" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="M286" s="21" t="s">
         <v>1794</v>
@@ -42239,7 +42233,7 @@
         <v>1791</v>
       </c>
       <c r="L287" s="22" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="M287" s="21" t="s">
         <v>1794</v>
@@ -42286,7 +42280,7 @@
         <v>1791</v>
       </c>
       <c r="L288" s="22" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="M288" s="21" t="s">
         <v>1794</v>
